--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -1946,50 +1946,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728111</v>
+        <v>125728157</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489223</v>
+        <v>489452</v>
       </c>
       <c r="R15" t="n">
-        <v>6818133</v>
+        <v>6818179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728157</v>
+        <v>125728155</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489452</v>
+        <v>489417</v>
       </c>
       <c r="R16" t="n">
-        <v>6818179</v>
+        <v>6818154</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728155</v>
+        <v>125728069</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489417</v>
+        <v>489204</v>
       </c>
       <c r="R17" t="n">
-        <v>6818154</v>
+        <v>6818104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728069</v>
+        <v>125728146</v>
       </c>
       <c r="B18" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489204</v>
+        <v>489261</v>
       </c>
       <c r="R18" t="n">
-        <v>6818104</v>
+        <v>6818155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728146</v>
+        <v>125728169</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489261</v>
+        <v>489407</v>
       </c>
       <c r="R19" t="n">
-        <v>6818155</v>
+        <v>6818356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728169</v>
+        <v>125728068</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489407</v>
+        <v>489219</v>
       </c>
       <c r="R20" t="n">
-        <v>6818356</v>
+        <v>6818134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728068</v>
+        <v>125728135</v>
       </c>
       <c r="B21" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2571,7 +2566,7 @@
         <v>489219</v>
       </c>
       <c r="R21" t="n">
-        <v>6818134</v>
+        <v>6818132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2604,6 +2599,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2630,7 +2630,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728135</v>
+        <v>125728161</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489219</v>
+        <v>489439</v>
       </c>
       <c r="R22" t="n">
-        <v>6818132</v>
+        <v>6818361</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,45 +2727,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728161</v>
+        <v>125728111</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489439</v>
+        <v>489223</v>
       </c>
       <c r="R23" t="n">
-        <v>6818361</v>
+        <v>6818133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728178</v>
+        <v>125728119</v>
       </c>
       <c r="B40" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489394</v>
+        <v>489446</v>
       </c>
       <c r="R40" t="n">
-        <v>6818362</v>
+        <v>6818191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728134</v>
+        <v>125728178</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489318</v>
+        <v>489394</v>
       </c>
       <c r="R41" t="n">
-        <v>6818135</v>
+        <v>6818362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4577,11 +4577,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4608,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728119</v>
+        <v>125728134</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489446</v>
+        <v>489318</v>
       </c>
       <c r="R42" t="n">
-        <v>6818191</v>
+        <v>6818135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4674,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728156</v>
+        <v>125728180</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,34 +4716,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489450</v>
+        <v>489407</v>
       </c>
       <c r="R43" t="n">
-        <v>6818159</v>
+        <v>6818050</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4776,6 +4780,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4802,10 +4811,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728071</v>
+        <v>125728156</v>
       </c>
       <c r="B44" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4822,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4846,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489452</v>
+        <v>489450</v>
       </c>
       <c r="R44" t="n">
-        <v>6818185</v>
+        <v>6818159</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4908,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4919,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4943,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R45" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +5005,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728072</v>
+        <v>125728159</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5016,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5040,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489446</v>
+        <v>489463</v>
       </c>
       <c r="R46" t="n">
-        <v>6818191</v>
+        <v>6818200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5102,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728154</v>
+        <v>125728072</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,21 +5113,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5128,10 +5137,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489424</v>
+        <v>489446</v>
       </c>
       <c r="R47" t="n">
-        <v>6818132</v>
+        <v>6818191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5190,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728180</v>
+        <v>125728154</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5201,38 +5210,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489407</v>
+        <v>489424</v>
       </c>
       <c r="R48" t="n">
-        <v>6818050</v>
+        <v>6818132</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5265,11 +5270,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728086</v>
+        <v>125728109</v>
       </c>
       <c r="B55" t="n">
-        <v>78999</v>
+        <v>97202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489365</v>
+        <v>489452</v>
       </c>
       <c r="R55" t="n">
-        <v>6818390</v>
+        <v>6818415</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728088</v>
+        <v>125728118</v>
       </c>
       <c r="B56" t="n">
-        <v>96577</v>
+        <v>78726</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489442</v>
+        <v>489422</v>
       </c>
       <c r="R56" t="n">
-        <v>6818350</v>
+        <v>6818130</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728165</v>
+        <v>125728086</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489432</v>
+        <v>489365</v>
       </c>
       <c r="R57" t="n">
-        <v>6818365</v>
+        <v>6818390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728163</v>
+        <v>125728088</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>96577</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489456</v>
+        <v>489442</v>
       </c>
       <c r="R58" t="n">
-        <v>6818471</v>
+        <v>6818350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728109</v>
+        <v>125728165</v>
       </c>
       <c r="B59" t="n">
-        <v>97202</v>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489452</v>
+        <v>489432</v>
       </c>
       <c r="R59" t="n">
-        <v>6818415</v>
+        <v>6818365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728118</v>
+        <v>125728163</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489422</v>
+        <v>489456</v>
       </c>
       <c r="R60" t="n">
-        <v>6818130</v>
+        <v>6818471</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728151</v>
+        <v>125728084</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489396</v>
+        <v>489414</v>
       </c>
       <c r="R67" t="n">
-        <v>6818028</v>
+        <v>6818350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728130</v>
+        <v>125728151</v>
       </c>
       <c r="B68" t="n">
-        <v>91234</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489444</v>
+        <v>489396</v>
       </c>
       <c r="R68" t="n">
-        <v>6818412</v>
+        <v>6818028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B69" t="n">
-        <v>78999</v>
+        <v>91234</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R69" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B70" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R70" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728160</v>
+        <v>125728133</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489463</v>
+        <v>489386</v>
       </c>
       <c r="R71" t="n">
-        <v>6818278</v>
+        <v>6818081</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,6 +7506,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,7 +7537,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728133</v>
+        <v>125728142</v>
       </c>
       <c r="B72" t="n">
         <v>78967</v>
@@ -7567,10 +7572,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489386</v>
+        <v>489363</v>
       </c>
       <c r="R72" t="n">
-        <v>6818081</v>
+        <v>6818235</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,11 +7608,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7634,7 +7634,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728142</v>
+        <v>125728162</v>
       </c>
       <c r="B73" t="n">
         <v>78967</v>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489363</v>
+        <v>489460</v>
       </c>
       <c r="R73" t="n">
-        <v>6818235</v>
+        <v>6818444</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728162</v>
+        <v>125728114</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489460</v>
+        <v>489364</v>
       </c>
       <c r="R74" t="n">
-        <v>6818444</v>
+        <v>6818169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728080</v>
+        <v>125728174</v>
       </c>
       <c r="B2" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489424</v>
+        <v>489338</v>
       </c>
       <c r="R2" t="n">
-        <v>6818132</v>
+        <v>6818397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125728083</v>
+        <v>125728121</v>
       </c>
       <c r="B3" t="n">
-        <v>78999</v>
+        <v>80106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489470</v>
+        <v>489306</v>
       </c>
       <c r="R3" t="n">
-        <v>6818266</v>
+        <v>6818055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728137</v>
+        <v>125728101</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489352</v>
+        <v>489357</v>
       </c>
       <c r="R5" t="n">
-        <v>6818366</v>
+        <v>6818163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728174</v>
+        <v>125728110</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>92707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489338</v>
+        <v>489380</v>
       </c>
       <c r="R6" t="n">
-        <v>6818397</v>
+        <v>6818374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728121</v>
+        <v>125728137</v>
       </c>
       <c r="B8" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489306</v>
+        <v>489352</v>
       </c>
       <c r="R8" t="n">
-        <v>6818055</v>
+        <v>6818366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,38 +1359,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728101</v>
+        <v>125728112</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489357</v>
+        <v>489161</v>
       </c>
       <c r="R9" t="n">
-        <v>6818163</v>
+        <v>6817982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728110</v>
+        <v>125728080</v>
       </c>
       <c r="B10" t="n">
-        <v>92700</v>
+        <v>78999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489380</v>
+        <v>489424</v>
       </c>
       <c r="R10" t="n">
-        <v>6818374</v>
+        <v>6818132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728112</v>
+        <v>125728083</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489161</v>
+        <v>489470</v>
       </c>
       <c r="R11" t="n">
-        <v>6817982</v>
+        <v>6818266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B13" t="n">
-        <v>91185</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728091</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>91192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489452</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728157</v>
+        <v>125728069</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489452</v>
+        <v>489204</v>
       </c>
       <c r="R15" t="n">
-        <v>6818179</v>
+        <v>6818104</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728155</v>
+        <v>125728146</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489417</v>
+        <v>489261</v>
       </c>
       <c r="R16" t="n">
-        <v>6818154</v>
+        <v>6818155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728069</v>
+        <v>125728157</v>
       </c>
       <c r="B17" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489204</v>
+        <v>489452</v>
       </c>
       <c r="R17" t="n">
-        <v>6818104</v>
+        <v>6818179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728146</v>
+        <v>125728169</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489261</v>
+        <v>489407</v>
       </c>
       <c r="R18" t="n">
-        <v>6818155</v>
+        <v>6818356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728169</v>
+        <v>125728155</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489407</v>
+        <v>489417</v>
       </c>
       <c r="R19" t="n">
-        <v>6818356</v>
+        <v>6818154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728124</v>
+        <v>125728166</v>
       </c>
       <c r="B24" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489468</v>
+        <v>489433</v>
       </c>
       <c r="R24" t="n">
-        <v>6818461</v>
+        <v>6818362</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728079</v>
+        <v>125728081</v>
       </c>
       <c r="B25" t="n">
         <v>78999</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489130</v>
+        <v>489450</v>
       </c>
       <c r="R25" t="n">
-        <v>6817993</v>
+        <v>6818184</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728081</v>
+        <v>125728079</v>
       </c>
       <c r="B26" t="n">
         <v>78999</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489450</v>
+        <v>489130</v>
       </c>
       <c r="R26" t="n">
-        <v>6818184</v>
+        <v>6817993</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728167</v>
+        <v>125728095</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,34 +3228,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489417</v>
+        <v>489341</v>
       </c>
       <c r="R28" t="n">
-        <v>6818347</v>
+        <v>6818044</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3288,6 +3296,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3314,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728147</v>
+        <v>125728108</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3325,34 +3338,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489255</v>
+        <v>489429</v>
       </c>
       <c r="R29" t="n">
-        <v>6818162</v>
+        <v>6818150</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3385,6 +3403,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3411,32 +3434,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728141</v>
+        <v>125728124</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489363</v>
+        <v>489468</v>
       </c>
       <c r="R30" t="n">
-        <v>6818242</v>
+        <v>6818461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728166</v>
+        <v>125728147</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3543,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489433</v>
+        <v>489255</v>
       </c>
       <c r="R31" t="n">
-        <v>6818362</v>
+        <v>6818162</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,7 +3628,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728164</v>
+        <v>125728167</v>
       </c>
       <c r="B32" t="n">
         <v>78967</v>
@@ -3640,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489432</v>
+        <v>489417</v>
       </c>
       <c r="R32" t="n">
-        <v>6818370</v>
+        <v>6818347</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728141</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,42 +3736,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489363</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6818242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3796,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3812,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728108</v>
+        <v>125728164</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3823,39 +3833,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489429</v>
+        <v>489432</v>
       </c>
       <c r="R34" t="n">
-        <v>6818150</v>
+        <v>6818370</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3888,11 +3893,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4113,45 +4113,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728082</v>
+        <v>125728181</v>
       </c>
       <c r="B37" t="n">
-        <v>78999</v>
+        <v>5176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489448</v>
+        <v>489399</v>
       </c>
       <c r="R37" t="n">
-        <v>6818191</v>
+        <v>6818343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4210,50 +4215,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728181</v>
+        <v>125728082</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>78999</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489399</v>
+        <v>489448</v>
       </c>
       <c r="R38" t="n">
-        <v>6818343</v>
+        <v>6818191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728089</v>
+        <v>125728134</v>
       </c>
       <c r="B39" t="n">
-        <v>96577</v>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489455</v>
+        <v>489318</v>
       </c>
       <c r="R39" t="n">
-        <v>6818449</v>
+        <v>6818135</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,6 +4383,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728119</v>
+        <v>125728178</v>
       </c>
       <c r="B40" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4425,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489446</v>
+        <v>489394</v>
       </c>
       <c r="R40" t="n">
-        <v>6818191</v>
+        <v>6818362</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728178</v>
+        <v>125728089</v>
       </c>
       <c r="B41" t="n">
-        <v>78634</v>
+        <v>96584</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4517,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4541,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489394</v>
+        <v>489455</v>
       </c>
       <c r="R41" t="n">
-        <v>6818362</v>
+        <v>6818449</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4603,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728134</v>
+        <v>125728119</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489318</v>
+        <v>489446</v>
       </c>
       <c r="R42" t="n">
-        <v>6818135</v>
+        <v>6818191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728180</v>
+        <v>125728156</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,38 +4716,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489407</v>
+        <v>489450</v>
       </c>
       <c r="R43" t="n">
-        <v>6818050</v>
+        <v>6818159</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4780,11 +4776,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4811,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728156</v>
+        <v>125728071</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4822,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4846,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489450</v>
+        <v>489452</v>
       </c>
       <c r="R44" t="n">
-        <v>6818159</v>
+        <v>6818185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4908,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728071</v>
+        <v>125728159</v>
       </c>
       <c r="B45" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4919,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4943,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489452</v>
+        <v>489463</v>
       </c>
       <c r="R45" t="n">
-        <v>6818185</v>
+        <v>6818200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5005,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728159</v>
+        <v>125728072</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5016,21 +5007,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5040,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489463</v>
+        <v>489446</v>
       </c>
       <c r="R46" t="n">
-        <v>6818200</v>
+        <v>6818191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728072</v>
+        <v>125728154</v>
       </c>
       <c r="B47" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5113,21 +5104,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489446</v>
+        <v>489424</v>
       </c>
       <c r="R47" t="n">
-        <v>6818191</v>
+        <v>6818132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5199,10 +5190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728154</v>
+        <v>125728180</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5210,34 +5201,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489424</v>
+        <v>489407</v>
       </c>
       <c r="R48" t="n">
-        <v>6818132</v>
+        <v>6818050</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5270,6 +5265,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728075</v>
+        <v>125728085</v>
       </c>
       <c r="B53" t="n">
-        <v>91142</v>
+        <v>78999</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489292</v>
+        <v>489411</v>
       </c>
       <c r="R53" t="n">
-        <v>6818151</v>
+        <v>6818380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728085</v>
+        <v>125728075</v>
       </c>
       <c r="B54" t="n">
-        <v>78999</v>
+        <v>91149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489411</v>
+        <v>489292</v>
       </c>
       <c r="R54" t="n">
-        <v>6818380</v>
+        <v>6818151</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
         <v>125728109</v>
       </c>
       <c r="B55" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728118</v>
+        <v>125728163</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489422</v>
+        <v>489456</v>
       </c>
       <c r="R56" t="n">
-        <v>6818130</v>
+        <v>6818471</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728086</v>
+        <v>125728165</v>
       </c>
       <c r="B57" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489365</v>
+        <v>489432</v>
       </c>
       <c r="R57" t="n">
-        <v>6818390</v>
+        <v>6818365</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728088</v>
+        <v>125728086</v>
       </c>
       <c r="B58" t="n">
-        <v>96577</v>
+        <v>78999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489442</v>
+        <v>489365</v>
       </c>
       <c r="R58" t="n">
-        <v>6818350</v>
+        <v>6818390</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728165</v>
+        <v>125728088</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>96584</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489432</v>
+        <v>489442</v>
       </c>
       <c r="R59" t="n">
-        <v>6818365</v>
+        <v>6818350</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728163</v>
+        <v>125728118</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489456</v>
+        <v>489422</v>
       </c>
       <c r="R60" t="n">
-        <v>6818471</v>
+        <v>6818130</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728115</v>
+        <v>125728153</v>
       </c>
       <c r="B63" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489204</v>
+        <v>489420</v>
       </c>
       <c r="R63" t="n">
-        <v>6818104</v>
+        <v>6818126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B64" t="n">
         <v>78967</v>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R64" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6822,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6848,10 +6853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6859,21 +6864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R65" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,11 +6924,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>78999</v>
+        <v>78726</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728084</v>
+        <v>125728151</v>
       </c>
       <c r="B67" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489414</v>
+        <v>489396</v>
       </c>
       <c r="R67" t="n">
-        <v>6818350</v>
+        <v>6818028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728151</v>
+        <v>125728130</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>91241</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489396</v>
+        <v>489444</v>
       </c>
       <c r="R68" t="n">
-        <v>6818028</v>
+        <v>6818412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B69" t="n">
-        <v>91234</v>
+        <v>78999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R69" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8216,45 +8216,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728179</v>
+        <v>125728100</v>
       </c>
       <c r="B79" t="n">
-        <v>95176</v>
+        <v>57648</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2383</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489412</v>
+        <v>489327</v>
       </c>
       <c r="R79" t="n">
-        <v>6818351</v>
+        <v>6818047</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8313,50 +8318,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728100</v>
+        <v>125728179</v>
       </c>
       <c r="B80" t="n">
-        <v>57648</v>
+        <v>95183</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>2383</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489327</v>
+        <v>489412</v>
       </c>
       <c r="R80" t="n">
-        <v>6818047</v>
+        <v>6818351</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9094,10 +9094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728087</v>
+        <v>125728152</v>
       </c>
       <c r="B88" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489343</v>
+        <v>489415</v>
       </c>
       <c r="R88" t="n">
-        <v>6818374</v>
+        <v>6818087</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,50 +9191,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728107</v>
+        <v>125728105</v>
       </c>
       <c r="B89" t="n">
-        <v>57651</v>
+        <v>79974</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489359</v>
+        <v>489306</v>
       </c>
       <c r="R89" t="n">
-        <v>6818332</v>
+        <v>6818062</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9267,11 +9262,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9298,45 +9288,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728094</v>
+        <v>125728107</v>
       </c>
       <c r="B90" t="n">
-        <v>91185</v>
+        <v>57651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489357</v>
+        <v>489359</v>
       </c>
       <c r="R90" t="n">
-        <v>6818380</v>
+        <v>6818332</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9369,6 +9364,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9395,32 +9395,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728152</v>
+        <v>125728094</v>
       </c>
       <c r="B91" t="n">
-        <v>78967</v>
+        <v>91192</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489415</v>
+        <v>489357</v>
       </c>
       <c r="R91" t="n">
-        <v>6818087</v>
+        <v>6818380</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9492,32 +9492,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728105</v>
+        <v>125728087</v>
       </c>
       <c r="B92" t="n">
-        <v>79974</v>
+        <v>78999</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489306</v>
+        <v>489343</v>
       </c>
       <c r="R92" t="n">
-        <v>6818062</v>
+        <v>6818374</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B94" t="n">
-        <v>78634</v>
+        <v>91590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R94" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728126</v>
+        <v>125728177</v>
       </c>
       <c r="B95" t="n">
-        <v>91583</v>
+        <v>78634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2064</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489439</v>
+        <v>489452</v>
       </c>
       <c r="R95" t="n">
-        <v>6818162</v>
+        <v>6818167</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9880,32 +9880,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728090</v>
+        <v>125728143</v>
       </c>
       <c r="B96" t="n">
-        <v>91185</v>
+        <v>78967</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489418</v>
+        <v>489366</v>
       </c>
       <c r="R96" t="n">
-        <v>6818094</v>
+        <v>6818215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728143</v>
+        <v>125728090</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>91192</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489366</v>
+        <v>489418</v>
       </c>
       <c r="R97" t="n">
-        <v>6818215</v>
+        <v>6818094</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10171,7 +10171,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728172</v>
+        <v>125728139</v>
       </c>
       <c r="B99" t="n">
         <v>78967</v>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489366</v>
+        <v>489360</v>
       </c>
       <c r="R99" t="n">
-        <v>6818389</v>
+        <v>6818301</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728127</v>
+        <v>125728173</v>
       </c>
       <c r="B100" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489267</v>
+        <v>489340</v>
       </c>
       <c r="R100" t="n">
-        <v>6818149</v>
+        <v>6818386</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728139</v>
+        <v>125728172</v>
       </c>
       <c r="B101" t="n">
         <v>78967</v>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489360</v>
+        <v>489366</v>
       </c>
       <c r="R101" t="n">
-        <v>6818301</v>
+        <v>6818389</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728173</v>
+        <v>125728127</v>
       </c>
       <c r="B102" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10473,21 +10473,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489340</v>
+        <v>489267</v>
       </c>
       <c r="R102" t="n">
-        <v>6818386</v>
+        <v>6818149</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10562,7 +10562,7 @@
         <v>125728129</v>
       </c>
       <c r="B103" t="n">
-        <v>91838</v>
+        <v>91845</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,34 +10773,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R105" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10833,6 +10838,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10859,10 +10869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10870,39 +10880,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R106" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10935,11 +10940,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728174</v>
+        <v>125728150</v>
       </c>
       <c r="B2" t="n">
         <v>78967</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489338</v>
+        <v>489356</v>
       </c>
       <c r="R2" t="n">
-        <v>6818397</v>
+        <v>6818016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125728121</v>
+        <v>125728137</v>
       </c>
       <c r="B3" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489306</v>
+        <v>489352</v>
       </c>
       <c r="R3" t="n">
-        <v>6818055</v>
+        <v>6818366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728150</v>
+        <v>125728101</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489356</v>
+        <v>489357</v>
       </c>
       <c r="R4" t="n">
-        <v>6818016</v>
+        <v>6818163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728101</v>
+        <v>125728080</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,39 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489357</v>
+        <v>489424</v>
       </c>
       <c r="R5" t="n">
-        <v>6818163</v>
+        <v>6818132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728110</v>
+        <v>125728083</v>
       </c>
       <c r="B6" t="n">
-        <v>92707</v>
+        <v>78999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489380</v>
+        <v>489470</v>
       </c>
       <c r="R6" t="n">
-        <v>6818374</v>
+        <v>6818266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728120</v>
+        <v>125728110</v>
       </c>
       <c r="B7" t="n">
-        <v>80106</v>
+        <v>92707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489345</v>
+        <v>489380</v>
       </c>
       <c r="R7" t="n">
-        <v>6818246</v>
+        <v>6818374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728137</v>
+        <v>125728120</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489352</v>
+        <v>489345</v>
       </c>
       <c r="R8" t="n">
-        <v>6818366</v>
+        <v>6818246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,50 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728112</v>
+        <v>125728174</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489161</v>
+        <v>489338</v>
       </c>
       <c r="R9" t="n">
-        <v>6817982</v>
+        <v>6818397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728080</v>
+        <v>125728121</v>
       </c>
       <c r="B10" t="n">
-        <v>78999</v>
+        <v>80106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489424</v>
+        <v>489306</v>
       </c>
       <c r="R10" t="n">
-        <v>6818132</v>
+        <v>6818055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,45 +1553,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728083</v>
+        <v>125728112</v>
       </c>
       <c r="B11" t="n">
-        <v>78999</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489470</v>
+        <v>489161</v>
       </c>
       <c r="R11" t="n">
-        <v>6818266</v>
+        <v>6817982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728149</v>
+        <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>91192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489154</v>
+        <v>489452</v>
       </c>
       <c r="R13" t="n">
-        <v>6818070</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728091</v>
+        <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>91192</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489452</v>
+        <v>489363</v>
       </c>
       <c r="R14" t="n">
-        <v>6818425</v>
+        <v>6818242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728146</v>
+        <v>125728157</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489261</v>
+        <v>489452</v>
       </c>
       <c r="R16" t="n">
-        <v>6818155</v>
+        <v>6818179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728157</v>
+        <v>125728146</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489452</v>
+        <v>489261</v>
       </c>
       <c r="R17" t="n">
-        <v>6818179</v>
+        <v>6818155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728166</v>
+        <v>125728124</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489433</v>
+        <v>489468</v>
       </c>
       <c r="R24" t="n">
-        <v>6818362</v>
+        <v>6818461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728081</v>
+        <v>125728147</v>
       </c>
       <c r="B25" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489450</v>
+        <v>489255</v>
       </c>
       <c r="R25" t="n">
-        <v>6818184</v>
+        <v>6818162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728079</v>
+        <v>125728167</v>
       </c>
       <c r="B26" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489130</v>
+        <v>489417</v>
       </c>
       <c r="R26" t="n">
-        <v>6817993</v>
+        <v>6818347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728176</v>
+        <v>125728141</v>
       </c>
       <c r="B27" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489383</v>
+        <v>489363</v>
       </c>
       <c r="R27" t="n">
-        <v>6818074</v>
+        <v>6818242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728095</v>
+        <v>125728166</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,42 +3228,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489341</v>
+        <v>489433</v>
       </c>
       <c r="R28" t="n">
-        <v>6818044</v>
+        <v>6818362</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3296,11 +3288,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3327,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728108</v>
+        <v>125728164</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,39 +3325,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489429</v>
+        <v>489432</v>
       </c>
       <c r="R29" t="n">
-        <v>6818150</v>
+        <v>6818370</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3403,11 +3385,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3434,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728124</v>
+        <v>125728081</v>
       </c>
       <c r="B30" t="n">
-        <v>80106</v>
+        <v>78999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489468</v>
+        <v>489450</v>
       </c>
       <c r="R30" t="n">
-        <v>6818461</v>
+        <v>6818184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3531,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728147</v>
+        <v>125728079</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3542,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3566,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489255</v>
+        <v>489130</v>
       </c>
       <c r="R31" t="n">
-        <v>6818162</v>
+        <v>6817993</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728167</v>
+        <v>125728176</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489417</v>
+        <v>489383</v>
       </c>
       <c r="R32" t="n">
-        <v>6818347</v>
+        <v>6818074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728141</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,34 +3713,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489363</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818242</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,6 +3781,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3822,10 +3812,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728164</v>
+        <v>125728108</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,34 +3823,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489432</v>
+        <v>489429</v>
       </c>
       <c r="R34" t="n">
-        <v>6818370</v>
+        <v>6818150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,6 +3888,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728103</v>
+        <v>125728082</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>78999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489344</v>
+        <v>489448</v>
       </c>
       <c r="R35" t="n">
-        <v>6818246</v>
+        <v>6818191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728104</v>
+        <v>125728103</v>
       </c>
       <c r="B36" t="n">
         <v>80071</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489262</v>
+        <v>489344</v>
       </c>
       <c r="R36" t="n">
-        <v>6818043</v>
+        <v>6818246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,50 +4113,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728181</v>
+        <v>125728104</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>80071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489399</v>
+        <v>489262</v>
       </c>
       <c r="R37" t="n">
-        <v>6818343</v>
+        <v>6818043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,45 +4210,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728082</v>
+        <v>125728181</v>
       </c>
       <c r="B38" t="n">
-        <v>78999</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489448</v>
+        <v>489399</v>
       </c>
       <c r="R38" t="n">
-        <v>6818191</v>
+        <v>6818343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728178</v>
+        <v>125728119</v>
       </c>
       <c r="B40" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489394</v>
+        <v>489446</v>
       </c>
       <c r="R40" t="n">
-        <v>6818362</v>
+        <v>6818191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728089</v>
+        <v>125728178</v>
       </c>
       <c r="B41" t="n">
-        <v>96584</v>
+        <v>78634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489455</v>
+        <v>489394</v>
       </c>
       <c r="R41" t="n">
-        <v>6818449</v>
+        <v>6818362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728119</v>
+        <v>125728089</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>96584</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489446</v>
+        <v>489455</v>
       </c>
       <c r="R42" t="n">
-        <v>6818191</v>
+        <v>6818449</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728158</v>
+        <v>125728085</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489449</v>
+        <v>489411</v>
       </c>
       <c r="R49" t="n">
-        <v>6818184</v>
+        <v>6818380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728168</v>
+        <v>125728158</v>
       </c>
       <c r="B50" t="n">
         <v>78967</v>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489413</v>
+        <v>489449</v>
       </c>
       <c r="R50" t="n">
-        <v>6818350</v>
+        <v>6818184</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728073</v>
+        <v>125728168</v>
       </c>
       <c r="B51" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489392</v>
+        <v>489413</v>
       </c>
       <c r="R51" t="n">
-        <v>6818361</v>
+        <v>6818350</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728171</v>
+        <v>125728073</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489374</v>
+        <v>489392</v>
       </c>
       <c r="R52" t="n">
-        <v>6818387</v>
+        <v>6818361</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728085</v>
+        <v>125728171</v>
       </c>
       <c r="B53" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489411</v>
+        <v>489374</v>
       </c>
       <c r="R53" t="n">
-        <v>6818380</v>
+        <v>6818387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728151</v>
+        <v>125728084</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489396</v>
+        <v>489414</v>
       </c>
       <c r="R67" t="n">
-        <v>6818028</v>
+        <v>6818350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728084</v>
+        <v>125728151</v>
       </c>
       <c r="B69" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489414</v>
+        <v>489396</v>
       </c>
       <c r="R69" t="n">
-        <v>6818350</v>
+        <v>6818028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728117</v>
       </c>
       <c r="B85" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489409</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818054</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728102</v>
+        <v>125728125</v>
       </c>
       <c r="B86" t="n">
-        <v>80071</v>
+        <v>80070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489338</v>
+        <v>489320</v>
       </c>
       <c r="R86" t="n">
-        <v>6818240</v>
+        <v>6818042</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728117</v>
+        <v>125728102</v>
       </c>
       <c r="B87" t="n">
-        <v>78726</v>
+        <v>80071</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489409</v>
+        <v>489338</v>
       </c>
       <c r="R87" t="n">
-        <v>6818054</v>
+        <v>6818240</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728152</v>
+        <v>125728094</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>91192</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489415</v>
+        <v>489357</v>
       </c>
       <c r="R88" t="n">
-        <v>6818087</v>
+        <v>6818380</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728105</v>
+        <v>125728152</v>
       </c>
       <c r="B89" t="n">
-        <v>79974</v>
+        <v>78967</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489306</v>
+        <v>489415</v>
       </c>
       <c r="R89" t="n">
-        <v>6818062</v>
+        <v>6818087</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,50 +9288,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728107</v>
+        <v>125728105</v>
       </c>
       <c r="B90" t="n">
-        <v>57651</v>
+        <v>79974</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489359</v>
+        <v>489306</v>
       </c>
       <c r="R90" t="n">
-        <v>6818332</v>
+        <v>6818062</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9364,11 +9359,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9395,32 +9385,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728094</v>
+        <v>125728087</v>
       </c>
       <c r="B91" t="n">
-        <v>91192</v>
+        <v>78999</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9430,10 +9420,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489357</v>
+        <v>489343</v>
       </c>
       <c r="R91" t="n">
-        <v>6818380</v>
+        <v>6818374</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9492,10 +9482,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728087</v>
+        <v>125728107</v>
       </c>
       <c r="B92" t="n">
-        <v>78999</v>
+        <v>57651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9503,34 +9493,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489343</v>
+        <v>489359</v>
       </c>
       <c r="R92" t="n">
-        <v>6818374</v>
+        <v>6818332</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9563,6 +9558,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728070</v>
+        <v>125728177</v>
       </c>
       <c r="B93" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489185</v>
+        <v>489452</v>
       </c>
       <c r="R93" t="n">
-        <v>6818091</v>
+        <v>6818167</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B94" t="n">
-        <v>91590</v>
+        <v>79585</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R94" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B95" t="n">
-        <v>78634</v>
+        <v>91590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R95" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728139</v>
+        <v>125728129</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>91845</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489360</v>
+        <v>489370</v>
       </c>
       <c r="R99" t="n">
-        <v>6818301</v>
+        <v>6818176</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728129</v>
+        <v>125728139</v>
       </c>
       <c r="B103" t="n">
-        <v>91845</v>
+        <v>78967</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489370</v>
+        <v>489360</v>
       </c>
       <c r="R103" t="n">
-        <v>6818176</v>
+        <v>6818301</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,39 +10773,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R105" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,11 +10833,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10869,10 +10859,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10880,34 +10870,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R106" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10940,6 +10935,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12252,45 +12252,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B120" t="n">
-        <v>78967</v>
+        <v>57473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R120" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12349,50 +12354,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B121" t="n">
-        <v>57473</v>
+        <v>78967</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R121" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13809,6 +13809,6806 @@
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>125995667</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>489117</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6818011</v>
+      </c>
+      <c r="S135" t="n">
+        <v>15</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125996241</v>
+      </c>
+      <c r="B136" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>185</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>489437</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6818032</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>125996409</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>489377</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6818145</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>125994090</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>488989</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6817941</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>125995142</v>
+      </c>
+      <c r="B139" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>489041</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6817951</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>125995990</v>
+      </c>
+      <c r="B140" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>185</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>489201</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6818003</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>125996346</v>
+      </c>
+      <c r="B141" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>185</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>489439</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6818061</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>125996407</v>
+      </c>
+      <c r="B142" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>185</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>489391</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6818133</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>125993983</v>
+      </c>
+      <c r="B143" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>488964</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6817921</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>125993642</v>
+      </c>
+      <c r="B144" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>488965</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6817938</v>
+      </c>
+      <c r="S144" t="n">
+        <v>15</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>125994790</v>
+      </c>
+      <c r="B145" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>488932</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6818043</v>
+      </c>
+      <c r="S145" t="n">
+        <v>15</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>125996446</v>
+      </c>
+      <c r="B146" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>489329</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6818061</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>125996662</v>
+      </c>
+      <c r="B147" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>489260</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6818067</v>
+      </c>
+      <c r="S147" t="n">
+        <v>15</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>125993318</v>
+      </c>
+      <c r="B148" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>488825</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6817957</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>125995957</v>
+      </c>
+      <c r="B149" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>489236</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6817991</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>125996237</v>
+      </c>
+      <c r="B150" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>185</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>489427</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6818004</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>125996385</v>
+      </c>
+      <c r="B151" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>489458</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6818096</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>125995781</v>
+      </c>
+      <c r="B152" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>489151</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6818027</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>125996392</v>
+      </c>
+      <c r="B153" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>185</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>489380</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6818117</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>125995381</v>
+      </c>
+      <c r="B154" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>489035</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6817949</v>
+      </c>
+      <c r="S154" t="n">
+        <v>15</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>125996247</v>
+      </c>
+      <c r="B155" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>489487</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6818014</v>
+      </c>
+      <c r="S155" t="n">
+        <v>15</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>125996286</v>
+      </c>
+      <c r="B156" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>489446</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6818036</v>
+      </c>
+      <c r="S156" t="n">
+        <v>15</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>125996438</v>
+      </c>
+      <c r="B157" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>489309</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6818107</v>
+      </c>
+      <c r="S157" t="n">
+        <v>20</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>125992923</v>
+      </c>
+      <c r="B158" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>488811</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6817901</v>
+      </c>
+      <c r="S158" t="n">
+        <v>20</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>125996114</v>
+      </c>
+      <c r="B159" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>185</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>489329</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6818006</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>125996113</v>
+      </c>
+      <c r="B160" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>185</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>489312</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6817997</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>125996381</v>
+      </c>
+      <c r="B161" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>489443</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6818076</v>
+      </c>
+      <c r="S161" t="n">
+        <v>15</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>125991267</v>
+      </c>
+      <c r="B162" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>488729</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6817882</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>125991520</v>
+      </c>
+      <c r="B163" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>488720</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6817985</v>
+      </c>
+      <c r="S163" t="n">
+        <v>15</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>125992967</v>
+      </c>
+      <c r="B164" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>488808</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6817936</v>
+      </c>
+      <c r="S164" t="n">
+        <v>15</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>125996631</v>
+      </c>
+      <c r="B165" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>489259</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6818066</v>
+      </c>
+      <c r="S165" t="n">
+        <v>15</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>125995149</v>
+      </c>
+      <c r="B166" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>489055</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6818041</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>125996410</v>
+      </c>
+      <c r="B167" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>489371</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6818137</v>
+      </c>
+      <c r="S167" t="n">
+        <v>15</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>125990421</v>
+      </c>
+      <c r="B168" t="n">
+        <v>91678</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>488613</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6818174</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>125995059</v>
+      </c>
+      <c r="B169" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>489030</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6818049</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>125994323</v>
+      </c>
+      <c r="B170" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>488963</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6817966</v>
+      </c>
+      <c r="S170" t="n">
+        <v>15</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>125995740</v>
+      </c>
+      <c r="B171" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>489141</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6818047</v>
+      </c>
+      <c r="S171" t="n">
+        <v>15</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>125994504</v>
+      </c>
+      <c r="B172" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>488931</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6818012</v>
+      </c>
+      <c r="S172" t="n">
+        <v>15</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>125996284</v>
+      </c>
+      <c r="B173" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>185</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>489434</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6818042</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>125996703</v>
+      </c>
+      <c r="B174" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>489239</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6818065</v>
+      </c>
+      <c r="S174" t="n">
+        <v>15</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>125993417</v>
+      </c>
+      <c r="B175" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>488839</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6817946</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>125994342</v>
+      </c>
+      <c r="B176" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>488947</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6818000</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>125993566</v>
+      </c>
+      <c r="B177" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>488920</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6817948</v>
+      </c>
+      <c r="S177" t="n">
+        <v>15</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>125995962</v>
+      </c>
+      <c r="B178" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>185</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>489204</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6818012</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>125993829</v>
+      </c>
+      <c r="B179" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>488971</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6817935</v>
+      </c>
+      <c r="S179" t="n">
+        <v>12</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>125996288</v>
+      </c>
+      <c r="B180" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>489443</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6818073</v>
+      </c>
+      <c r="S180" t="n">
+        <v>15</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>125996386</v>
+      </c>
+      <c r="B181" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>489383</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6818097</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>125996051</v>
+      </c>
+      <c r="B182" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>185</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>489241</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6818009</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>125996069</v>
+      </c>
+      <c r="B183" t="n">
+        <v>80106</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>489255</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6818046</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>125996119</v>
+      </c>
+      <c r="B184" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>185</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>489362</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6818010</v>
+      </c>
+      <c r="S184" t="n">
+        <v>20</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>125993495</v>
+      </c>
+      <c r="B185" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>488864</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6817945</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>125993813</v>
+      </c>
+      <c r="B186" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>488933</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6817911</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>125995420</v>
+      </c>
+      <c r="B187" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>489064</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6817976</v>
+      </c>
+      <c r="S187" t="n">
+        <v>15</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>125992179</v>
+      </c>
+      <c r="B188" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>488791</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6817820</v>
+      </c>
+      <c r="S188" t="n">
+        <v>20</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>125991445</v>
+      </c>
+      <c r="B189" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>488712</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6817879</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>125996514</v>
+      </c>
+      <c r="B190" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>489277</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6818090</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>125995939</v>
+      </c>
+      <c r="B191" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>489210</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6818012</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>125996400</v>
+      </c>
+      <c r="B192" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>489414</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6818155</v>
+      </c>
+      <c r="S192" t="n">
+        <v>15</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>125996428</v>
+      </c>
+      <c r="B193" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>489349</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6818082</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>125994469</v>
+      </c>
+      <c r="B194" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>488925</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6817999</v>
+      </c>
+      <c r="S194" t="n">
+        <v>15</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>125994510</v>
+      </c>
+      <c r="B195" t="n">
+        <v>96584</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>53</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>488947</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6818000</v>
+      </c>
+      <c r="S195" t="n">
+        <v>20</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>125995904</v>
+      </c>
+      <c r="B196" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>185</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>489185</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6818003</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>125995626</v>
+      </c>
+      <c r="B197" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>489111</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6817988</v>
+      </c>
+      <c r="S197" t="n">
+        <v>15</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>125995410</v>
+      </c>
+      <c r="B198" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>489050</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6817957</v>
+      </c>
+      <c r="S198" t="n">
+        <v>15</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>125995830</v>
+      </c>
+      <c r="B199" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>185</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>489169</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6818007</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>125996064</v>
+      </c>
+      <c r="B200" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>489258</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6818035</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>125996494</v>
+      </c>
+      <c r="B201" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>489277</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6818089</v>
+      </c>
+      <c r="S201" t="n">
+        <v>15</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>125996970</v>
+      </c>
+      <c r="B202" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>489179</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6818027</v>
+      </c>
+      <c r="S202" t="n">
+        <v>15</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>125996865</v>
+      </c>
+      <c r="B203" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>185</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>489208</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6818043</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>125996240</v>
+      </c>
+      <c r="B204" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>489466</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6818007</v>
+      </c>
+      <c r="S204" t="n">
+        <v>15</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728150</v>
+        <v>125728120</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489356</v>
+        <v>489345</v>
       </c>
       <c r="R2" t="n">
-        <v>6818016</v>
+        <v>6818246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,38 +869,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728101</v>
+        <v>125728112</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489357</v>
+        <v>489161</v>
       </c>
       <c r="R4" t="n">
-        <v>6818163</v>
+        <v>6817982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728110</v>
+        <v>125728174</v>
       </c>
       <c r="B7" t="n">
-        <v>92707</v>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489380</v>
+        <v>489338</v>
       </c>
       <c r="R7" t="n">
-        <v>6818374</v>
+        <v>6818397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728120</v>
+        <v>125728121</v>
       </c>
       <c r="B8" t="n">
         <v>80106</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489345</v>
+        <v>489306</v>
       </c>
       <c r="R8" t="n">
-        <v>6818246</v>
+        <v>6818055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728174</v>
+        <v>125728150</v>
       </c>
       <c r="B9" t="n">
         <v>78967</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489338</v>
+        <v>489356</v>
       </c>
       <c r="R9" t="n">
-        <v>6818397</v>
+        <v>6818016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,45 +1456,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728121</v>
+        <v>125728101</v>
       </c>
       <c r="B10" t="n">
-        <v>80106</v>
+        <v>57648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R10" t="n">
-        <v>6818055</v>
+        <v>6818163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728112</v>
+        <v>125728110</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>92707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489161</v>
+        <v>489380</v>
       </c>
       <c r="R11" t="n">
-        <v>6817982</v>
+        <v>6818374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728082</v>
+        <v>125728103</v>
       </c>
       <c r="B35" t="n">
-        <v>78999</v>
+        <v>80071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489448</v>
+        <v>489344</v>
       </c>
       <c r="R35" t="n">
-        <v>6818191</v>
+        <v>6818246</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728103</v>
+        <v>125728104</v>
       </c>
       <c r="B36" t="n">
         <v>80071</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489344</v>
+        <v>489262</v>
       </c>
       <c r="R36" t="n">
-        <v>6818246</v>
+        <v>6818043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,45 +4113,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728104</v>
+        <v>125728181</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>5176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489262</v>
+        <v>489399</v>
       </c>
       <c r="R37" t="n">
-        <v>6818043</v>
+        <v>6818343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4210,50 +4215,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728181</v>
+        <v>125728082</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>78999</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489399</v>
+        <v>489448</v>
       </c>
       <c r="R38" t="n">
-        <v>6818343</v>
+        <v>6818191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728119</v>
+        <v>125728178</v>
       </c>
       <c r="B40" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489446</v>
+        <v>489394</v>
       </c>
       <c r="R40" t="n">
-        <v>6818191</v>
+        <v>6818362</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728178</v>
+        <v>125728089</v>
       </c>
       <c r="B41" t="n">
-        <v>78634</v>
+        <v>96584</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489394</v>
+        <v>489455</v>
       </c>
       <c r="R41" t="n">
-        <v>6818362</v>
+        <v>6818449</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728089</v>
+        <v>125728119</v>
       </c>
       <c r="B42" t="n">
-        <v>96584</v>
+        <v>78726</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489455</v>
+        <v>489446</v>
       </c>
       <c r="R42" t="n">
-        <v>6818449</v>
+        <v>6818191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728163</v>
+        <v>125728118</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489456</v>
+        <v>489422</v>
       </c>
       <c r="R56" t="n">
-        <v>6818471</v>
+        <v>6818130</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728165</v>
+        <v>125728163</v>
       </c>
       <c r="B57" t="n">
         <v>78967</v>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489432</v>
+        <v>489456</v>
       </c>
       <c r="R57" t="n">
-        <v>6818365</v>
+        <v>6818471</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728086</v>
+        <v>125728165</v>
       </c>
       <c r="B58" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489365</v>
+        <v>489432</v>
       </c>
       <c r="R58" t="n">
-        <v>6818390</v>
+        <v>6818365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728088</v>
+        <v>125728086</v>
       </c>
       <c r="B59" t="n">
-        <v>96584</v>
+        <v>78999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489442</v>
+        <v>489365</v>
       </c>
       <c r="R59" t="n">
-        <v>6818350</v>
+        <v>6818390</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728118</v>
+        <v>125728088</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>96584</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489422</v>
+        <v>489442</v>
       </c>
       <c r="R60" t="n">
-        <v>6818130</v>
+        <v>6818350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728160</v>
+        <v>125728114</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489463</v>
+        <v>489364</v>
       </c>
       <c r="R70" t="n">
-        <v>6818278</v>
+        <v>6818169</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728133</v>
+        <v>125728160</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489386</v>
+        <v>489463</v>
       </c>
       <c r="R71" t="n">
-        <v>6818081</v>
+        <v>6818278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,11 +7506,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7537,7 +7532,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728142</v>
+        <v>125728133</v>
       </c>
       <c r="B72" t="n">
         <v>78967</v>
@@ -7572,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489363</v>
+        <v>489386</v>
       </c>
       <c r="R72" t="n">
-        <v>6818235</v>
+        <v>6818081</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7608,6 +7603,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7634,7 +7634,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728162</v>
+        <v>125728142</v>
       </c>
       <c r="B73" t="n">
         <v>78967</v>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489460</v>
+        <v>489363</v>
       </c>
       <c r="R73" t="n">
-        <v>6818444</v>
+        <v>6818235</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728114</v>
+        <v>125728162</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489364</v>
+        <v>489460</v>
       </c>
       <c r="R74" t="n">
-        <v>6818169</v>
+        <v>6818444</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728117</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>78726</v>
+        <v>80070</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489409</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818054</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728125</v>
+        <v>125728102</v>
       </c>
       <c r="B86" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489320</v>
+        <v>489338</v>
       </c>
       <c r="R86" t="n">
-        <v>6818042</v>
+        <v>6818240</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728102</v>
+        <v>125728117</v>
       </c>
       <c r="B87" t="n">
-        <v>80071</v>
+        <v>78726</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489338</v>
+        <v>489409</v>
       </c>
       <c r="R87" t="n">
-        <v>6818240</v>
+        <v>6818054</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9880,32 +9880,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728143</v>
+        <v>125728090</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>91192</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489366</v>
+        <v>489418</v>
       </c>
       <c r="R96" t="n">
-        <v>6818215</v>
+        <v>6818094</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728090</v>
+        <v>125728143</v>
       </c>
       <c r="B97" t="n">
-        <v>91192</v>
+        <v>78967</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489418</v>
+        <v>489366</v>
       </c>
       <c r="R97" t="n">
-        <v>6818094</v>
+        <v>6818215</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728129</v>
+        <v>125728139</v>
       </c>
       <c r="B99" t="n">
-        <v>91845</v>
+        <v>78967</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489370</v>
+        <v>489360</v>
       </c>
       <c r="R99" t="n">
-        <v>6818176</v>
+        <v>6818301</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728139</v>
+        <v>125728129</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>91845</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489360</v>
+        <v>489370</v>
       </c>
       <c r="R103" t="n">
-        <v>6818301</v>
+        <v>6818176</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,34 +10773,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R105" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10833,6 +10838,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10859,10 +10869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10870,39 +10880,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R106" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10935,11 +10940,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10969,7 +10969,7 @@
         <v>125724254</v>
       </c>
       <c r="B107" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>125723347</v>
       </c>
       <c r="B108" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>125724786</v>
       </c>
       <c r="B110" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>125722589</v>
       </c>
       <c r="B111" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>125723050</v>
       </c>
       <c r="B112" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>125725272</v>
       </c>
       <c r="B117" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>125724536</v>
       </c>
       <c r="B118" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>125725082</v>
       </c>
       <c r="B119" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12252,50 +12252,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B120" t="n">
-        <v>57473</v>
+        <v>78968</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R120" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12354,45 +12349,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B121" t="n">
-        <v>78967</v>
+        <v>57473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R121" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125869096</v>
       </c>
       <c r="B124" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>125869097</v>
       </c>
       <c r="B125" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,48 +13811,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125995667</v>
+        <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489117</v>
+        <v>489437</v>
       </c>
       <c r="R135" t="n">
-        <v>6818011</v>
+        <v>6818032</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,22 +13896,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996241</v>
+        <v>125996409</v>
       </c>
       <c r="B136" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489437</v>
+        <v>489377</v>
       </c>
       <c r="R136" t="n">
-        <v>6818032</v>
+        <v>6818145</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78967</v>
+        <v>98332</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125994090</v>
+        <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>488989</v>
+        <v>489439</v>
       </c>
       <c r="R138" t="n">
-        <v>6817941</v>
+        <v>6818061</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,10 +14199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125995142</v>
+        <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,37 +14210,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489041</v>
+        <v>489391</v>
       </c>
       <c r="R139" t="n">
-        <v>6817951</v>
+        <v>6818133</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14284,12 +14284,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
         <v>125995990</v>
       </c>
       <c r="B140" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125996346</v>
+        <v>125994090</v>
       </c>
       <c r="B141" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,34 +14404,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489439</v>
+        <v>488989</v>
       </c>
       <c r="R141" t="n">
-        <v>6818061</v>
+        <v>6817941</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125996407</v>
+        <v>125995142</v>
       </c>
       <c r="B142" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489391</v>
+        <v>489041</v>
       </c>
       <c r="R142" t="n">
-        <v>6818133</v>
+        <v>6817951</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14689,10 +14689,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125993642</v>
+        <v>125994790</v>
       </c>
       <c r="B144" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14724,10 +14724,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>488965</v>
+        <v>488932</v>
       </c>
       <c r="R144" t="n">
-        <v>6817938</v>
+        <v>6818043</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14786,10 +14786,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125994790</v>
+        <v>125993642</v>
       </c>
       <c r="B145" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>488932</v>
+        <v>488965</v>
       </c>
       <c r="R145" t="n">
-        <v>6818043</v>
+        <v>6817938</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -14886,7 +14886,7 @@
         <v>125996446</v>
       </c>
       <c r="B146" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>125996662</v>
       </c>
       <c r="B147" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B148" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R148" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15276,10 +15276,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B150" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15287,34 +15287,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R150" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15376,7 +15376,7 @@
         <v>125996385</v>
       </c>
       <c r="B151" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B152" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R152" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B153" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R153" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
         <v>125995381</v>
       </c>
       <c r="B154" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B155" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R155" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B156" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R156" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125996438</v>
+        <v>125996286</v>
       </c>
       <c r="B157" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15990,13 +15990,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489309</v>
+        <v>489446</v>
       </c>
       <c r="R157" t="n">
-        <v>6818107</v>
+        <v>6818036</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16052,48 +16052,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125992923</v>
+        <v>125996113</v>
       </c>
       <c r="B158" t="n">
-        <v>98352</v>
+        <v>79000</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>488811</v>
+        <v>489312</v>
       </c>
       <c r="R158" t="n">
-        <v>6817901</v>
+        <v>6817997</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>125996114</v>
       </c>
       <c r="B159" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16246,48 +16246,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125996113</v>
+        <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>78999</v>
+        <v>98353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>489312</v>
+        <v>488811</v>
       </c>
       <c r="R160" t="n">
-        <v>6817997</v>
+        <v>6817901</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>125996381</v>
       </c>
       <c r="B161" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>125991267</v>
       </c>
       <c r="B162" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125991520</v>
+        <v>125996410</v>
       </c>
       <c r="B163" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16568,14 +16568,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>488720</v>
+        <v>489371</v>
       </c>
       <c r="R163" t="n">
-        <v>6817985</v>
+        <v>6818137</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -16637,7 +16637,7 @@
         <v>125992967</v>
       </c>
       <c r="B164" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16731,10 +16731,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125996631</v>
+        <v>125991520</v>
       </c>
       <c r="B165" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16742,34 +16742,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>489259</v>
+        <v>488720</v>
       </c>
       <c r="R165" t="n">
-        <v>6818066</v>
+        <v>6817985</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125995149</v>
+        <v>125996631</v>
       </c>
       <c r="B166" t="n">
-        <v>78726</v>
+        <v>57811</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,37 +16839,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>489055</v>
+        <v>489259</v>
       </c>
       <c r="R166" t="n">
-        <v>6818041</v>
+        <v>6818066</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -16913,22 +16913,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125996410</v>
+        <v>125995149</v>
       </c>
       <c r="B167" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,37 +16936,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489371</v>
+        <v>489055</v>
       </c>
       <c r="R167" t="n">
-        <v>6818137</v>
+        <v>6818041</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17010,60 +17010,60 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125990421</v>
+        <v>125995740</v>
       </c>
       <c r="B168" t="n">
-        <v>91678</v>
+        <v>78968</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>488613</v>
+        <v>489141</v>
       </c>
       <c r="R168" t="n">
-        <v>6818174</v>
+        <v>6818047</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,22 +17107,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995059</v>
+        <v>125994323</v>
       </c>
       <c r="B169" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17130,21 +17130,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17154,13 +17154,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489030</v>
+        <v>488963</v>
       </c>
       <c r="R169" t="n">
-        <v>6818049</v>
+        <v>6817966</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17204,22 +17204,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125994323</v>
+        <v>125995059</v>
       </c>
       <c r="B170" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17227,21 +17227,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488963</v>
+        <v>489030</v>
       </c>
       <c r="R170" t="n">
-        <v>6817966</v>
+        <v>6818049</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,60 +17301,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B171" t="n">
-        <v>78967</v>
+        <v>91679</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R171" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17398,12 +17398,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -17413,7 +17413,7 @@
         <v>125994504</v>
       </c>
       <c r="B172" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>125996284</v>
       </c>
       <c r="B173" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>125996703</v>
       </c>
       <c r="B174" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125993417</v>
+        <v>125996386</v>
       </c>
       <c r="B175" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17732,14 +17732,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>488839</v>
+        <v>489383</v>
       </c>
       <c r="R175" t="n">
-        <v>6817946</v>
+        <v>6818097</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,10 +17798,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125994342</v>
+        <v>125993566</v>
       </c>
       <c r="B176" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17833,13 +17833,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>488947</v>
+        <v>488920</v>
       </c>
       <c r="R176" t="n">
-        <v>6818000</v>
+        <v>6817948</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,22 +17883,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125993566</v>
+        <v>125996288</v>
       </c>
       <c r="B177" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17926,14 +17926,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>488920</v>
+        <v>489443</v>
       </c>
       <c r="R177" t="n">
-        <v>6817948</v>
+        <v>6818073</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -17992,10 +17992,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125995962</v>
+        <v>125993417</v>
       </c>
       <c r="B178" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18003,34 +18003,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>489204</v>
+        <v>488839</v>
       </c>
       <c r="R178" t="n">
-        <v>6818012</v>
+        <v>6817946</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18092,7 +18092,7 @@
         <v>125993829</v>
       </c>
       <c r="B179" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18186,10 +18186,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125996288</v>
+        <v>125994342</v>
       </c>
       <c r="B180" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18217,17 +18217,17 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>489443</v>
+        <v>488947</v>
       </c>
       <c r="R180" t="n">
-        <v>6818073</v>
+        <v>6818000</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -18271,22 +18271,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125996386</v>
+        <v>125995962</v>
       </c>
       <c r="B181" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,21 +18294,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18318,10 +18318,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>489383</v>
+        <v>489204</v>
       </c>
       <c r="R181" t="n">
-        <v>6818097</v>
+        <v>6818012</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18380,10 +18380,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125996051</v>
+        <v>125996119</v>
       </c>
       <c r="B182" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18415,13 +18415,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>489241</v>
+        <v>489362</v>
       </c>
       <c r="R182" t="n">
-        <v>6818009</v>
+        <v>6818010</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18477,32 +18477,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125996069</v>
+        <v>125996051</v>
       </c>
       <c r="B183" t="n">
-        <v>80106</v>
+        <v>79000</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18512,10 +18512,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>489255</v>
+        <v>489241</v>
       </c>
       <c r="R183" t="n">
-        <v>6818046</v>
+        <v>6818009</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18574,10 +18574,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125996119</v>
+        <v>125993495</v>
       </c>
       <c r="B184" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18585,37 +18585,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>489362</v>
+        <v>488864</v>
       </c>
       <c r="R184" t="n">
-        <v>6818010</v>
+        <v>6817945</v>
       </c>
       <c r="S184" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -18659,57 +18659,57 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125993495</v>
+        <v>125996069</v>
       </c>
       <c r="B185" t="n">
-        <v>78967</v>
+        <v>80107</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>488864</v>
+        <v>489255</v>
       </c>
       <c r="R185" t="n">
-        <v>6817945</v>
+        <v>6818046</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18756,22 +18756,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18799,14 +18799,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,22 +18853,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125995420</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>489064</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6817976</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18950,12 +18950,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -18965,7 +18965,7 @@
         <v>125992179</v>
       </c>
       <c r="B188" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19059,32 +19059,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125991445</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
-        <v>98352</v>
+        <v>78968</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488712</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6817879</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,57 +19144,57 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78967</v>
+        <v>98353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19241,22 +19241,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125995939</v>
+        <v>125996400</v>
       </c>
       <c r="B191" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19288,13 +19288,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>489210</v>
+        <v>489414</v>
       </c>
       <c r="R191" t="n">
-        <v>6818012</v>
+        <v>6818155</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19338,22 +19338,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125996400</v>
+        <v>125996428</v>
       </c>
       <c r="B192" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19385,13 +19385,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>489414</v>
+        <v>489349</v>
       </c>
       <c r="R192" t="n">
-        <v>6818155</v>
+        <v>6818082</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -19435,22 +19435,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125996428</v>
+        <v>125995939</v>
       </c>
       <c r="B193" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19482,10 +19482,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>489349</v>
+        <v>489210</v>
       </c>
       <c r="R193" t="n">
-        <v>6818082</v>
+        <v>6818012</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125994469</v>
+        <v>125995626</v>
       </c>
       <c r="B194" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19579,10 +19579,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>488925</v>
+        <v>489111</v>
       </c>
       <c r="R194" t="n">
-        <v>6817999</v>
+        <v>6817988</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125994510</v>
+        <v>125994469</v>
       </c>
       <c r="B195" t="n">
-        <v>96584</v>
+        <v>78968</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,21 +19652,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19676,13 +19676,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>488947</v>
+        <v>488925</v>
       </c>
       <c r="R195" t="n">
-        <v>6818000</v>
+        <v>6817999</v>
       </c>
       <c r="S195" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,22 +19726,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995904</v>
+        <v>125995410</v>
       </c>
       <c r="B196" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19749,37 +19749,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489185</v>
+        <v>489050</v>
       </c>
       <c r="R196" t="n">
-        <v>6818003</v>
+        <v>6817957</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -19823,22 +19823,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125995626</v>
+        <v>125994510</v>
       </c>
       <c r="B197" t="n">
-        <v>78967</v>
+        <v>96585</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,21 +19846,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19870,13 +19870,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>489111</v>
+        <v>488947</v>
       </c>
       <c r="R197" t="n">
-        <v>6817988</v>
+        <v>6818000</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995410</v>
+        <v>125995904</v>
       </c>
       <c r="B198" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489050</v>
+        <v>489185</v>
       </c>
       <c r="R198" t="n">
-        <v>6817957</v>
+        <v>6818003</v>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,22 +20017,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125995830</v>
+        <v>125996064</v>
       </c>
       <c r="B199" t="n">
-        <v>78999</v>
+        <v>80072</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20040,21 +20040,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489169</v>
+        <v>489258</v>
       </c>
       <c r="R199" t="n">
-        <v>6818007</v>
+        <v>6818035</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20126,10 +20126,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125996064</v>
+        <v>125996865</v>
       </c>
       <c r="B200" t="n">
-        <v>80071</v>
+        <v>79000</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20137,21 +20137,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489258</v>
+        <v>489208</v>
       </c>
       <c r="R200" t="n">
-        <v>6818035</v>
+        <v>6818043</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125996494</v>
+        <v>125995830</v>
       </c>
       <c r="B201" t="n">
-        <v>78726</v>
+        <v>79000</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20234,21 +20234,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489277</v>
+        <v>489169</v>
       </c>
       <c r="R201" t="n">
-        <v>6818089</v>
+        <v>6818007</v>
       </c>
       <c r="S201" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20308,12 +20308,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -20323,7 +20323,7 @@
         <v>125996970</v>
       </c>
       <c r="B202" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996865</v>
+        <v>125996240</v>
       </c>
       <c r="B203" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20428,21 +20428,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20452,13 +20452,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489208</v>
+        <v>489466</v>
       </c>
       <c r="R203" t="n">
-        <v>6818043</v>
+        <v>6818007</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20502,22 +20502,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125996240</v>
+        <v>125996494</v>
       </c>
       <c r="B204" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20525,21 +20525,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20549,10 +20549,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>489466</v>
+        <v>489277</v>
       </c>
       <c r="R204" t="n">
-        <v>6818007</v>
+        <v>6818089</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728120</v>
+        <v>125728080</v>
       </c>
       <c r="B2" t="n">
-        <v>80106</v>
+        <v>79000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489345</v>
+        <v>489424</v>
       </c>
       <c r="R2" t="n">
-        <v>6818246</v>
+        <v>6818132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125728137</v>
+        <v>125728083</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489352</v>
+        <v>489470</v>
       </c>
       <c r="R3" t="n">
-        <v>6818366</v>
+        <v>6818266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728112</v>
+        <v>125728120</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>80107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489161</v>
+        <v>489345</v>
       </c>
       <c r="R4" t="n">
-        <v>6817982</v>
+        <v>6818246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728080</v>
+        <v>125728121</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>80107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489424</v>
+        <v>489306</v>
       </c>
       <c r="R5" t="n">
-        <v>6818132</v>
+        <v>6818055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728083</v>
+        <v>125728110</v>
       </c>
       <c r="B6" t="n">
-        <v>78999</v>
+        <v>92710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489470</v>
+        <v>489380</v>
       </c>
       <c r="R6" t="n">
-        <v>6818266</v>
+        <v>6818374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728174</v>
+        <v>125728137</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489338</v>
+        <v>489352</v>
       </c>
       <c r="R7" t="n">
-        <v>6818397</v>
+        <v>6818366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728121</v>
+        <v>125728112</v>
       </c>
       <c r="B8" t="n">
-        <v>80106</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,34 +1268,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489306</v>
+        <v>489161</v>
       </c>
       <c r="R8" t="n">
-        <v>6818055</v>
+        <v>6817982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>125728150</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728101</v>
+        <v>125728174</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,39 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489357</v>
+        <v>489338</v>
       </c>
       <c r="R10" t="n">
-        <v>6818163</v>
+        <v>6818397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728110</v>
+        <v>125728101</v>
       </c>
       <c r="B11" t="n">
-        <v>92707</v>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,34 +1564,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489380</v>
+        <v>489357</v>
       </c>
       <c r="R11" t="n">
-        <v>6818374</v>
+        <v>6818163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>125728069</v>
       </c>
       <c r="B15" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728157</v>
+        <v>125728146</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489452</v>
+        <v>489261</v>
       </c>
       <c r="R16" t="n">
-        <v>6818179</v>
+        <v>6818155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728146</v>
+        <v>125728155</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489261</v>
+        <v>489417</v>
       </c>
       <c r="R17" t="n">
-        <v>6818155</v>
+        <v>6818154</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728169</v>
+        <v>125728068</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489407</v>
+        <v>489219</v>
       </c>
       <c r="R18" t="n">
-        <v>6818356</v>
+        <v>6818134</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728155</v>
+        <v>125728157</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489417</v>
+        <v>489452</v>
       </c>
       <c r="R19" t="n">
-        <v>6818154</v>
+        <v>6818179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728068</v>
+        <v>125728169</v>
       </c>
       <c r="B20" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489219</v>
+        <v>489407</v>
       </c>
       <c r="R20" t="n">
-        <v>6818134</v>
+        <v>6818356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
         <v>125728135</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125728161</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,45 +2829,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728124</v>
+        <v>125728095</v>
       </c>
       <c r="B24" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489468</v>
+        <v>489341</v>
       </c>
       <c r="R24" t="n">
-        <v>6818461</v>
+        <v>6818044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2900,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2926,10 +2939,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728147</v>
+        <v>125728108</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2950,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489255</v>
+        <v>489429</v>
       </c>
       <c r="R25" t="n">
-        <v>6818162</v>
+        <v>6818150</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2997,6 +3015,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3023,32 +3046,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728167</v>
+        <v>125728124</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>80107</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3081,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489417</v>
+        <v>489468</v>
       </c>
       <c r="R26" t="n">
-        <v>6818347</v>
+        <v>6818461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3143,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728141</v>
+        <v>125728147</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489363</v>
+        <v>489255</v>
       </c>
       <c r="R27" t="n">
-        <v>6818242</v>
+        <v>6818162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728166</v>
+        <v>125728167</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3252,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489433</v>
+        <v>489417</v>
       </c>
       <c r="R28" t="n">
-        <v>6818362</v>
+        <v>6818347</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,10 +3337,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728164</v>
+        <v>125728141</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3349,10 +3372,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489432</v>
+        <v>489363</v>
       </c>
       <c r="R29" t="n">
-        <v>6818370</v>
+        <v>6818242</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,10 +3434,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728081</v>
+        <v>125728166</v>
       </c>
       <c r="B30" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3422,21 +3445,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489450</v>
+        <v>489433</v>
       </c>
       <c r="R30" t="n">
-        <v>6818184</v>
+        <v>6818362</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3531,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728079</v>
+        <v>125728164</v>
       </c>
       <c r="B31" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3542,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489130</v>
+        <v>489432</v>
       </c>
       <c r="R31" t="n">
-        <v>6817993</v>
+        <v>6818370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3628,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728176</v>
+        <v>125728079</v>
       </c>
       <c r="B32" t="n">
-        <v>78634</v>
+        <v>79000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3640,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489383</v>
+        <v>489130</v>
       </c>
       <c r="R32" t="n">
-        <v>6818074</v>
+        <v>6817993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728176</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>78635</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,42 +3736,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489383</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6818074</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3796,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3812,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728108</v>
+        <v>125728081</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>79000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3823,39 +3833,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489429</v>
+        <v>489450</v>
       </c>
       <c r="R34" t="n">
-        <v>6818150</v>
+        <v>6818184</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3888,11 +3893,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728103</v>
+        <v>125728082</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>79000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489344</v>
+        <v>489448</v>
       </c>
       <c r="R35" t="n">
-        <v>6818246</v>
+        <v>6818191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,45 +4016,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728104</v>
+        <v>125728181</v>
       </c>
       <c r="B36" t="n">
-        <v>80071</v>
+        <v>5176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489262</v>
+        <v>489399</v>
       </c>
       <c r="R36" t="n">
-        <v>6818043</v>
+        <v>6818343</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,50 +4118,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728181</v>
+        <v>125728103</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>80072</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489399</v>
+        <v>489344</v>
       </c>
       <c r="R37" t="n">
-        <v>6818343</v>
+        <v>6818246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728082</v>
+        <v>125728104</v>
       </c>
       <c r="B38" t="n">
-        <v>78999</v>
+        <v>80072</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4226,21 +4226,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489448</v>
+        <v>489262</v>
       </c>
       <c r="R38" t="n">
-        <v>6818191</v>
+        <v>6818043</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728134</v>
+        <v>125728119</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489318</v>
+        <v>489446</v>
       </c>
       <c r="R39" t="n">
-        <v>6818135</v>
+        <v>6818191</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,11 +4383,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728178</v>
+        <v>125728089</v>
       </c>
       <c r="B40" t="n">
-        <v>78634</v>
+        <v>96587</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4425,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489394</v>
+        <v>489455</v>
       </c>
       <c r="R40" t="n">
-        <v>6818362</v>
+        <v>6818449</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728089</v>
+        <v>125728178</v>
       </c>
       <c r="B41" t="n">
-        <v>96584</v>
+        <v>78635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489455</v>
+        <v>489394</v>
       </c>
       <c r="R41" t="n">
-        <v>6818449</v>
+        <v>6818362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728119</v>
+        <v>125728134</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489446</v>
+        <v>489318</v>
       </c>
       <c r="R42" t="n">
-        <v>6818191</v>
+        <v>6818135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4674,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728156</v>
+        <v>125728071</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489450</v>
+        <v>489452</v>
       </c>
       <c r="R43" t="n">
-        <v>6818159</v>
+        <v>6818185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728071</v>
+        <v>125728072</v>
       </c>
       <c r="B44" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489452</v>
+        <v>489446</v>
       </c>
       <c r="R44" t="n">
-        <v>6818185</v>
+        <v>6818191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728159</v>
+        <v>125728154</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489463</v>
+        <v>489424</v>
       </c>
       <c r="R45" t="n">
-        <v>6818200</v>
+        <v>6818132</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728072</v>
+        <v>125728156</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489446</v>
+        <v>489450</v>
       </c>
       <c r="R46" t="n">
-        <v>6818191</v>
+        <v>6818159</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728154</v>
+        <v>125728159</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489424</v>
+        <v>489463</v>
       </c>
       <c r="R47" t="n">
-        <v>6818132</v>
+        <v>6818200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
         <v>125728085</v>
       </c>
       <c r="B49" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728158</v>
+        <v>125728075</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>91150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489449</v>
+        <v>489292</v>
       </c>
       <c r="R50" t="n">
-        <v>6818184</v>
+        <v>6818151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
         <v>125728168</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>125728073</v>
       </c>
       <c r="B52" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>125728171</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728075</v>
+        <v>125728158</v>
       </c>
       <c r="B54" t="n">
-        <v>91149</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489292</v>
+        <v>489449</v>
       </c>
       <c r="R54" t="n">
-        <v>6818151</v>
+        <v>6818184</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
         <v>125728109</v>
       </c>
       <c r="B55" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>125728118</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728163</v>
+        <v>125728086</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489456</v>
+        <v>489365</v>
       </c>
       <c r="R57" t="n">
-        <v>6818471</v>
+        <v>6818390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728165</v>
+        <v>125728088</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>96587</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489432</v>
+        <v>489442</v>
       </c>
       <c r="R58" t="n">
-        <v>6818365</v>
+        <v>6818350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728086</v>
+        <v>125728163</v>
       </c>
       <c r="B59" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489365</v>
+        <v>489456</v>
       </c>
       <c r="R59" t="n">
-        <v>6818390</v>
+        <v>6818471</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728088</v>
+        <v>125728165</v>
       </c>
       <c r="B60" t="n">
-        <v>96584</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489442</v>
+        <v>489432</v>
       </c>
       <c r="R60" t="n">
-        <v>6818350</v>
+        <v>6818365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
         <v>125728170</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>125728144</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728153</v>
+        <v>125728115</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489420</v>
+        <v>489204</v>
       </c>
       <c r="R63" t="n">
-        <v>6818126</v>
+        <v>6818104</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R64" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,11 +6822,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6853,10 +6848,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728078</v>
+        <v>125728153</v>
       </c>
       <c r="B65" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6864,21 +6859,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6888,10 +6883,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489352</v>
+        <v>489420</v>
       </c>
       <c r="R65" t="n">
-        <v>6818362</v>
+        <v>6818126</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6950,10 +6945,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728115</v>
+        <v>125728136</v>
       </c>
       <c r="B66" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6956,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6980,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489204</v>
+        <v>489467</v>
       </c>
       <c r="R66" t="n">
-        <v>6818104</v>
+        <v>6818200</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7021,6 +7016,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B67" t="n">
-        <v>78999</v>
+        <v>91242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R67" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728130</v>
+        <v>125728151</v>
       </c>
       <c r="B68" t="n">
-        <v>91241</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489444</v>
+        <v>489396</v>
       </c>
       <c r="R68" t="n">
-        <v>6818412</v>
+        <v>6818028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728151</v>
+        <v>125728084</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489396</v>
+        <v>489414</v>
       </c>
       <c r="R69" t="n">
-        <v>6818028</v>
+        <v>6818350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728114</v>
+        <v>125728162</v>
       </c>
       <c r="B70" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489364</v>
+        <v>489460</v>
       </c>
       <c r="R70" t="n">
-        <v>6818169</v>
+        <v>6818444</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7438,7 +7438,7 @@
         <v>125728160</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>125728133</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>125728142</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728162</v>
+        <v>125728114</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489460</v>
+        <v>489364</v>
       </c>
       <c r="R74" t="n">
-        <v>6818444</v>
+        <v>6818169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,32 +7828,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728140</v>
+        <v>125728179</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>95186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>2383</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489337</v>
+        <v>489412</v>
       </c>
       <c r="R75" t="n">
-        <v>6818236</v>
+        <v>6818351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,45 +7925,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728098</v>
+        <v>125728100</v>
       </c>
       <c r="B76" t="n">
-        <v>80099</v>
+        <v>57648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489262</v>
+        <v>489327</v>
       </c>
       <c r="R76" t="n">
-        <v>6818039</v>
+        <v>6818047</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,32 +8027,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728145</v>
+        <v>125728098</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>80100</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8062,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489365</v>
+        <v>489262</v>
       </c>
       <c r="R77" t="n">
-        <v>6818143</v>
+        <v>6818039</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,7 +8127,7 @@
         <v>125728097</v>
       </c>
       <c r="B78" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8216,10 +8221,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728100</v>
+        <v>125728140</v>
       </c>
       <c r="B79" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8227,39 +8232,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489327</v>
+        <v>489337</v>
       </c>
       <c r="R79" t="n">
-        <v>6818047</v>
+        <v>6818236</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8318,32 +8318,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728179</v>
+        <v>125728145</v>
       </c>
       <c r="B80" t="n">
-        <v>95183</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2383</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489412</v>
+        <v>489365</v>
       </c>
       <c r="R80" t="n">
-        <v>6818351</v>
+        <v>6818143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
         <v>125728123</v>
       </c>
       <c r="B81" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125728148</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>125728099</v>
       </c>
       <c r="B83" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728077</v>
+        <v>125728102</v>
       </c>
       <c r="B84" t="n">
-        <v>75066</v>
+        <v>80072</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489458</v>
+        <v>489338</v>
       </c>
       <c r="R84" t="n">
-        <v>6818455</v>
+        <v>6818240</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728077</v>
       </c>
       <c r="B85" t="n">
-        <v>80070</v>
+        <v>75067</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489458</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818455</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728102</v>
+        <v>125728125</v>
       </c>
       <c r="B86" t="n">
         <v>80071</v>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489338</v>
+        <v>489320</v>
       </c>
       <c r="R86" t="n">
-        <v>6818240</v>
+        <v>6818042</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9000,7 +9000,7 @@
         <v>125728117</v>
       </c>
       <c r="B87" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728094</v>
+        <v>125728087</v>
       </c>
       <c r="B88" t="n">
-        <v>91192</v>
+        <v>79000</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489357</v>
+        <v>489343</v>
       </c>
       <c r="R88" t="n">
-        <v>6818380</v>
+        <v>6818374</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728152</v>
+        <v>125728105</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>79975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489415</v>
+        <v>489306</v>
       </c>
       <c r="R89" t="n">
-        <v>6818087</v>
+        <v>6818062</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728105</v>
+        <v>125728094</v>
       </c>
       <c r="B90" t="n">
-        <v>79974</v>
+        <v>91193</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R90" t="n">
-        <v>6818062</v>
+        <v>6818380</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728087</v>
+        <v>125728152</v>
       </c>
       <c r="B91" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489343</v>
+        <v>489415</v>
       </c>
       <c r="R91" t="n">
-        <v>6818374</v>
+        <v>6818087</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B93" t="n">
-        <v>78634</v>
+        <v>91594</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R93" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728070</v>
+        <v>125728177</v>
       </c>
       <c r="B94" t="n">
-        <v>79585</v>
+        <v>78635</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489185</v>
+        <v>489452</v>
       </c>
       <c r="R94" t="n">
-        <v>6818091</v>
+        <v>6818167</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B95" t="n">
-        <v>91590</v>
+        <v>79586</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R95" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
         <v>125728090</v>
       </c>
       <c r="B96" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728143</v>
+        <v>125728116</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9988,21 +9988,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489366</v>
+        <v>489187</v>
       </c>
       <c r="R97" t="n">
-        <v>6818215</v>
+        <v>6818091</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728116</v>
+        <v>125728143</v>
       </c>
       <c r="B98" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10085,21 +10085,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489187</v>
+        <v>489366</v>
       </c>
       <c r="R98" t="n">
-        <v>6818091</v>
+        <v>6818215</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728139</v>
+        <v>125728172</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489360</v>
+        <v>489366</v>
       </c>
       <c r="R99" t="n">
-        <v>6818301</v>
+        <v>6818389</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728173</v>
+        <v>125728127</v>
       </c>
       <c r="B100" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489340</v>
+        <v>489267</v>
       </c>
       <c r="R100" t="n">
-        <v>6818386</v>
+        <v>6818149</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728172</v>
+        <v>125728173</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489366</v>
+        <v>489340</v>
       </c>
       <c r="R101" t="n">
-        <v>6818389</v>
+        <v>6818386</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728127</v>
+        <v>125728139</v>
       </c>
       <c r="B102" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10473,21 +10473,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489267</v>
+        <v>489360</v>
       </c>
       <c r="R102" t="n">
-        <v>6818149</v>
+        <v>6818301</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10562,7 +10562,7 @@
         <v>125728129</v>
       </c>
       <c r="B103" t="n">
-        <v>91845</v>
+        <v>91849</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,39 +10773,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R105" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,11 +10833,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10869,10 +10859,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10880,34 +10870,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R106" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10940,6 +10935,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125869106</v>
+        <v>125869105</v>
       </c>
       <c r="B129" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13219,10 +13219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>489469</v>
+        <v>489416</v>
       </c>
       <c r="R129" t="n">
-        <v>6818353</v>
+        <v>6818376</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13281,10 +13281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125869105</v>
+        <v>125869106</v>
       </c>
       <c r="B130" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>489416</v>
+        <v>489469</v>
       </c>
       <c r="R130" t="n">
-        <v>6818376</v>
+        <v>6818353</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125869112</v>
+        <v>125869115</v>
       </c>
       <c r="B131" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489429</v>
+        <v>489123</v>
       </c>
       <c r="R131" t="n">
-        <v>6818389</v>
+        <v>6817993</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125869115</v>
+        <v>125869112</v>
       </c>
       <c r="B132" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13537,10 +13537,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>489123</v>
+        <v>489429</v>
       </c>
       <c r="R132" t="n">
-        <v>6817993</v>
+        <v>6818389</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125996346</v>
+        <v>125995142</v>
       </c>
       <c r="B138" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,37 +14113,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>489439</v>
+        <v>489041</v>
       </c>
       <c r="R138" t="n">
-        <v>6818061</v>
+        <v>6817951</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14187,22 +14187,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125996407</v>
+        <v>125994090</v>
       </c>
       <c r="B139" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,34 +14210,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489391</v>
+        <v>488989</v>
       </c>
       <c r="R139" t="n">
-        <v>6818133</v>
+        <v>6817941</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125995990</v>
+        <v>125996346</v>
       </c>
       <c r="B140" t="n">
         <v>79000</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489201</v>
+        <v>489439</v>
       </c>
       <c r="R140" t="n">
-        <v>6818003</v>
+        <v>6818061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125994090</v>
+        <v>125996407</v>
       </c>
       <c r="B141" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,34 +14404,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>488989</v>
+        <v>489391</v>
       </c>
       <c r="R141" t="n">
-        <v>6817941</v>
+        <v>6818133</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995142</v>
+        <v>125995990</v>
       </c>
       <c r="B142" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489041</v>
+        <v>489201</v>
       </c>
       <c r="R142" t="n">
-        <v>6817951</v>
+        <v>6818003</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,22 +14575,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125993983</v>
+        <v>125993642</v>
       </c>
       <c r="B143" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14598,21 +14598,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>488964</v>
+        <v>488965</v>
       </c>
       <c r="R143" t="n">
-        <v>6817921</v>
+        <v>6817938</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14658,11 +14658,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14786,10 +14781,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125993642</v>
+        <v>125993983</v>
       </c>
       <c r="B145" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14797,21 +14792,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14821,10 +14816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>488965</v>
+        <v>488964</v>
       </c>
       <c r="R145" t="n">
-        <v>6817938</v>
+        <v>6817921</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -14857,6 +14852,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14883,7 +14883,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125996446</v>
+        <v>125996662</v>
       </c>
       <c r="B146" t="n">
         <v>78968</v>
@@ -14918,13 +14918,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>489329</v>
+        <v>489260</v>
       </c>
       <c r="R146" t="n">
-        <v>6818061</v>
+        <v>6818067</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14968,19 +14968,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125996662</v>
+        <v>125996446</v>
       </c>
       <c r="B147" t="n">
         <v>78968</v>
@@ -15015,13 +15015,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>489260</v>
+        <v>489329</v>
       </c>
       <c r="R147" t="n">
-        <v>6818067</v>
+        <v>6818061</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15065,12 +15065,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125995957</v>
+        <v>125993318</v>
       </c>
       <c r="B149" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489236</v>
+        <v>488825</v>
       </c>
       <c r="R149" t="n">
-        <v>6817991</v>
+        <v>6817957</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15247,11 +15247,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Fyra individer.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15264,22 +15259,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125993318</v>
+        <v>125995957</v>
       </c>
       <c r="B150" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15287,34 +15282,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>488825</v>
+        <v>489236</v>
       </c>
       <c r="R150" t="n">
-        <v>6817957</v>
+        <v>6817991</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15349,6 +15344,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15361,12 +15361,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996438</v>
+        <v>125996286</v>
       </c>
       <c r="B155" t="n">
         <v>78968</v>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489309</v>
+        <v>489446</v>
       </c>
       <c r="R155" t="n">
-        <v>6818107</v>
+        <v>6818036</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B156" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,13 +15893,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R156" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B157" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,21 +15966,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15990,10 +15990,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R157" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16249,7 +16249,7 @@
         <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125991267</v>
+        <v>125992967</v>
       </c>
       <c r="B162" t="n">
         <v>78968</v>
@@ -16475,13 +16475,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>488729</v>
+        <v>488808</v>
       </c>
       <c r="R162" t="n">
-        <v>6817882</v>
+        <v>6817936</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16525,19 +16525,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996410</v>
+        <v>125991267</v>
       </c>
       <c r="B163" t="n">
         <v>78968</v>
@@ -16568,17 +16568,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489371</v>
+        <v>488729</v>
       </c>
       <c r="R163" t="n">
-        <v>6818137</v>
+        <v>6817882</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125992967</v>
+        <v>125996410</v>
       </c>
       <c r="B164" t="n">
         <v>78968</v>
@@ -16665,14 +16665,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488808</v>
+        <v>489371</v>
       </c>
       <c r="R164" t="n">
-        <v>6817936</v>
+        <v>6818137</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125995059</v>
+        <v>125990421</v>
       </c>
       <c r="B170" t="n">
-        <v>78727</v>
+        <v>91682</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,10 +17251,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>489030</v>
+        <v>488613</v>
       </c>
       <c r="R170" t="n">
-        <v>6818049</v>
+        <v>6818174</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17313,32 +17313,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125990421</v>
+        <v>125995059</v>
       </c>
       <c r="B171" t="n">
-        <v>91679</v>
+        <v>78727</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1209</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,10 +17348,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>488613</v>
+        <v>489030</v>
       </c>
       <c r="R171" t="n">
-        <v>6818174</v>
+        <v>6818049</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125994504</v>
+        <v>125996703</v>
       </c>
       <c r="B172" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,34 +17421,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>488931</v>
+        <v>489239</v>
       </c>
       <c r="R172" t="n">
-        <v>6818012</v>
+        <v>6818065</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -17604,10 +17604,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125996703</v>
+        <v>125994504</v>
       </c>
       <c r="B174" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17615,34 +17615,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>489239</v>
+        <v>488931</v>
       </c>
       <c r="R174" t="n">
-        <v>6818065</v>
+        <v>6818012</v>
       </c>
       <c r="S174" t="n">
         <v>15</v>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125996386</v>
+        <v>125995962</v>
       </c>
       <c r="B175" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17712,21 +17712,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>489383</v>
+        <v>489204</v>
       </c>
       <c r="R175" t="n">
-        <v>6818097</v>
+        <v>6818012</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125993566</v>
+        <v>125994342</v>
       </c>
       <c r="B176" t="n">
         <v>78968</v>
@@ -17833,13 +17833,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>488920</v>
+        <v>488947</v>
       </c>
       <c r="R176" t="n">
-        <v>6817948</v>
+        <v>6818000</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,19 +17883,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125996288</v>
+        <v>125996386</v>
       </c>
       <c r="B177" t="n">
         <v>78968</v>
@@ -17930,13 +17930,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>489443</v>
+        <v>489383</v>
       </c>
       <c r="R177" t="n">
-        <v>6818073</v>
+        <v>6818097</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -17980,19 +17980,19 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125993417</v>
+        <v>125993829</v>
       </c>
       <c r="B178" t="n">
         <v>78968</v>
@@ -18027,13 +18027,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>488839</v>
+        <v>488971</v>
       </c>
       <c r="R178" t="n">
-        <v>6817946</v>
+        <v>6817935</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18077,19 +18077,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125993829</v>
+        <v>125996288</v>
       </c>
       <c r="B179" t="n">
         <v>78968</v>
@@ -18120,17 +18120,17 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>488971</v>
+        <v>489443</v>
       </c>
       <c r="R179" t="n">
-        <v>6817935</v>
+        <v>6818073</v>
       </c>
       <c r="S179" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125994342</v>
+        <v>125993417</v>
       </c>
       <c r="B180" t="n">
         <v>78968</v>
@@ -18221,10 +18221,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>488947</v>
+        <v>488839</v>
       </c>
       <c r="R180" t="n">
-        <v>6818000</v>
+        <v>6817946</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18283,10 +18283,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125995962</v>
+        <v>125993566</v>
       </c>
       <c r="B181" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,37 +18294,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>489204</v>
+        <v>488920</v>
       </c>
       <c r="R181" t="n">
-        <v>6818012</v>
+        <v>6817948</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -18368,12 +18368,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -18574,45 +18574,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125993495</v>
+        <v>125996069</v>
       </c>
       <c r="B184" t="n">
-        <v>78968</v>
+        <v>80107</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>488864</v>
+        <v>489255</v>
       </c>
       <c r="R184" t="n">
-        <v>6817945</v>
+        <v>6818046</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18659,57 +18659,57 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125996069</v>
+        <v>125993495</v>
       </c>
       <c r="B185" t="n">
-        <v>80107</v>
+        <v>78968</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>489255</v>
+        <v>488864</v>
       </c>
       <c r="R185" t="n">
-        <v>6818046</v>
+        <v>6817945</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18756,19 +18756,19 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B186" t="n">
         <v>78968</v>
@@ -18799,14 +18799,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,44 +18853,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125991445</v>
       </c>
       <c r="B187" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18900,10 +18900,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>488712</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6817879</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19156,45 +19156,45 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125996514</v>
       </c>
       <c r="B190" t="n">
-        <v>98353</v>
+        <v>78968</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>489277</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6818090</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19241,19 +19241,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125996400</v>
+        <v>125995939</v>
       </c>
       <c r="B191" t="n">
         <v>78968</v>
@@ -19288,13 +19288,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>489414</v>
+        <v>489210</v>
       </c>
       <c r="R191" t="n">
-        <v>6818155</v>
+        <v>6818012</v>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19338,12 +19338,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125995939</v>
+        <v>125996400</v>
       </c>
       <c r="B193" t="n">
         <v>78968</v>
@@ -19482,13 +19482,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>489210</v>
+        <v>489414</v>
       </c>
       <c r="R193" t="n">
-        <v>6818012</v>
+        <v>6818155</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -19532,22 +19532,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125995626</v>
+        <v>125994510</v>
       </c>
       <c r="B194" t="n">
-        <v>78968</v>
+        <v>96587</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,21 +19555,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19579,13 +19579,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>489111</v>
+        <v>488947</v>
       </c>
       <c r="R194" t="n">
-        <v>6817988</v>
+        <v>6818000</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19629,22 +19629,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125994469</v>
+        <v>125995904</v>
       </c>
       <c r="B195" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>488925</v>
+        <v>489185</v>
       </c>
       <c r="R195" t="n">
-        <v>6817999</v>
+        <v>6818003</v>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,19 +19726,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995410</v>
+        <v>125995626</v>
       </c>
       <c r="B196" t="n">
         <v>78968</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489050</v>
+        <v>489111</v>
       </c>
       <c r="R196" t="n">
-        <v>6817957</v>
+        <v>6817988</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125994510</v>
+        <v>125994469</v>
       </c>
       <c r="B197" t="n">
-        <v>96585</v>
+        <v>78968</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,21 +19846,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19870,13 +19870,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>488947</v>
+        <v>488925</v>
       </c>
       <c r="R197" t="n">
-        <v>6818000</v>
+        <v>6817999</v>
       </c>
       <c r="S197" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995904</v>
+        <v>125995410</v>
       </c>
       <c r="B198" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489185</v>
+        <v>489050</v>
       </c>
       <c r="R198" t="n">
-        <v>6818003</v>
+        <v>6817957</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,22 +20017,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125996064</v>
+        <v>125996494</v>
       </c>
       <c r="B199" t="n">
-        <v>80072</v>
+        <v>78727</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20040,21 +20040,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20064,13 +20064,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489258</v>
+        <v>489277</v>
       </c>
       <c r="R199" t="n">
-        <v>6818035</v>
+        <v>6818089</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -20114,12 +20114,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996970</v>
+        <v>125996064</v>
       </c>
       <c r="B202" t="n">
-        <v>78968</v>
+        <v>80072</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,13 +20355,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489179</v>
+        <v>489258</v>
       </c>
       <c r="R202" t="n">
-        <v>6818027</v>
+        <v>6818035</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20405,19 +20405,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996240</v>
+        <v>125996970</v>
       </c>
       <c r="B203" t="n">
         <v>78968</v>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489466</v>
+        <v>489179</v>
       </c>
       <c r="R203" t="n">
-        <v>6818007</v>
+        <v>6818027</v>
       </c>
       <c r="S203" t="n">
         <v>15</v>
@@ -20514,10 +20514,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125996494</v>
+        <v>125996240</v>
       </c>
       <c r="B204" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20525,21 +20525,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20549,10 +20549,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>489277</v>
+        <v>489466</v>
       </c>
       <c r="R204" t="n">
-        <v>6818089</v>
+        <v>6818007</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728069</v>
+        <v>125728157</v>
       </c>
       <c r="B15" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489204</v>
+        <v>489452</v>
       </c>
       <c r="R15" t="n">
-        <v>6818104</v>
+        <v>6818179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728146</v>
+        <v>125728169</v>
       </c>
       <c r="B16" t="n">
         <v>78968</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489261</v>
+        <v>489407</v>
       </c>
       <c r="R16" t="n">
-        <v>6818155</v>
+        <v>6818356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728155</v>
+        <v>125728135</v>
       </c>
       <c r="B17" t="n">
         <v>78968</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489417</v>
+        <v>489219</v>
       </c>
       <c r="R17" t="n">
-        <v>6818154</v>
+        <v>6818132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2237,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728068</v>
+        <v>125728161</v>
       </c>
       <c r="B18" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489219</v>
+        <v>489439</v>
       </c>
       <c r="R18" t="n">
-        <v>6818134</v>
+        <v>6818361</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,45 +2339,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728157</v>
+        <v>125728111</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489452</v>
+        <v>489223</v>
       </c>
       <c r="R19" t="n">
-        <v>6818179</v>
+        <v>6818133</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728169</v>
+        <v>125728069</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489407</v>
+        <v>489204</v>
       </c>
       <c r="R20" t="n">
-        <v>6818356</v>
+        <v>6818104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,7 +2538,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728135</v>
+        <v>125728146</v>
       </c>
       <c r="B21" t="n">
         <v>78968</v>
@@ -2563,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489219</v>
+        <v>489261</v>
       </c>
       <c r="R21" t="n">
-        <v>6818132</v>
+        <v>6818155</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2599,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2630,7 +2635,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728161</v>
+        <v>125728155</v>
       </c>
       <c r="B22" t="n">
         <v>78968</v>
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489439</v>
+        <v>489417</v>
       </c>
       <c r="R22" t="n">
-        <v>6818361</v>
+        <v>6818154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,50 +2732,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728111</v>
+        <v>125728068</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489223</v>
+        <v>489219</v>
       </c>
       <c r="R23" t="n">
-        <v>6818133</v>
+        <v>6818134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728095</v>
+        <v>125728147</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,42 +2840,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489341</v>
+        <v>489255</v>
       </c>
       <c r="R24" t="n">
-        <v>6818044</v>
+        <v>6818162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2908,11 +2900,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,50 +2926,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728108</v>
+        <v>125728124</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>80107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489429</v>
+        <v>489468</v>
       </c>
       <c r="R25" t="n">
-        <v>6818150</v>
+        <v>6818461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3015,11 +2997,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3046,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728124</v>
+        <v>125728079</v>
       </c>
       <c r="B26" t="n">
-        <v>80107</v>
+        <v>79000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3081,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489468</v>
+        <v>489130</v>
       </c>
       <c r="R26" t="n">
-        <v>6818461</v>
+        <v>6817993</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3143,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728147</v>
+        <v>125728176</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3154,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3178,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489255</v>
+        <v>489383</v>
       </c>
       <c r="R27" t="n">
-        <v>6818162</v>
+        <v>6818074</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3240,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728167</v>
+        <v>125728081</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489417</v>
+        <v>489450</v>
       </c>
       <c r="R28" t="n">
-        <v>6818347</v>
+        <v>6818184</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,7 +3314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728141</v>
+        <v>125728167</v>
       </c>
       <c r="B29" t="n">
         <v>78968</v>
@@ -3372,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489363</v>
+        <v>489417</v>
       </c>
       <c r="R29" t="n">
-        <v>6818242</v>
+        <v>6818347</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3411,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728166</v>
+        <v>125728141</v>
       </c>
       <c r="B30" t="n">
         <v>78968</v>
@@ -3469,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489433</v>
+        <v>489363</v>
       </c>
       <c r="R30" t="n">
-        <v>6818362</v>
+        <v>6818242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3531,7 +3508,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728164</v>
+        <v>125728166</v>
       </c>
       <c r="B31" t="n">
         <v>78968</v>
@@ -3566,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489432</v>
+        <v>489433</v>
       </c>
       <c r="R31" t="n">
-        <v>6818370</v>
+        <v>6818362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728079</v>
+        <v>125728164</v>
       </c>
       <c r="B32" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489130</v>
+        <v>489432</v>
       </c>
       <c r="R32" t="n">
-        <v>6817993</v>
+        <v>6818370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728176</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>78635</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,34 +3713,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489383</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818074</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,6 +3781,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3822,10 +3812,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728081</v>
+        <v>125728108</v>
       </c>
       <c r="B34" t="n">
-        <v>79000</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,34 +3823,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489450</v>
+        <v>489429</v>
       </c>
       <c r="R34" t="n">
-        <v>6818184</v>
+        <v>6818150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,6 +3888,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -8609,32 +8609,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728099</v>
+        <v>125728102</v>
       </c>
       <c r="B83" t="n">
-        <v>80100</v>
+        <v>80072</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489306</v>
+        <v>489338</v>
       </c>
       <c r="R83" t="n">
-        <v>6818056</v>
+        <v>6818240</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728102</v>
+        <v>125728077</v>
       </c>
       <c r="B84" t="n">
-        <v>80072</v>
+        <v>75067</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489338</v>
+        <v>489458</v>
       </c>
       <c r="R84" t="n">
-        <v>6818240</v>
+        <v>6818455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728077</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>75067</v>
+        <v>80071</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489458</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818455</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728125</v>
+        <v>125728099</v>
       </c>
       <c r="B86" t="n">
-        <v>80071</v>
+        <v>80100</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489320</v>
+        <v>489306</v>
       </c>
       <c r="R86" t="n">
-        <v>6818042</v>
+        <v>6818056</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B93" t="n">
-        <v>91594</v>
+        <v>79586</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R93" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728070</v>
+        <v>125728126</v>
       </c>
       <c r="B95" t="n">
-        <v>79586</v>
+        <v>91594</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>2064</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489185</v>
+        <v>489439</v>
       </c>
       <c r="R95" t="n">
-        <v>6818091</v>
+        <v>6818162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125995142</v>
+        <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,37 +14113,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>489041</v>
+        <v>489439</v>
       </c>
       <c r="R138" t="n">
-        <v>6817951</v>
+        <v>6818061</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14187,22 +14187,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125994090</v>
+        <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,34 +14210,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>488989</v>
+        <v>489391</v>
       </c>
       <c r="R139" t="n">
-        <v>6817941</v>
+        <v>6818133</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125996346</v>
+        <v>125995990</v>
       </c>
       <c r="B140" t="n">
         <v>79000</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489439</v>
+        <v>489201</v>
       </c>
       <c r="R140" t="n">
-        <v>6818061</v>
+        <v>6818003</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125996407</v>
+        <v>125995142</v>
       </c>
       <c r="B141" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,37 +14404,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489391</v>
+        <v>489041</v>
       </c>
       <c r="R141" t="n">
-        <v>6818133</v>
+        <v>6817951</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,22 +14478,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995990</v>
+        <v>125994090</v>
       </c>
       <c r="B142" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,34 +14501,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489201</v>
+        <v>488989</v>
       </c>
       <c r="R142" t="n">
-        <v>6818003</v>
+        <v>6817941</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996703</v>
+        <v>125996284</v>
       </c>
       <c r="B172" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,21 +17421,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17445,13 +17445,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489239</v>
+        <v>489434</v>
       </c>
       <c r="R172" t="n">
-        <v>6818065</v>
+        <v>6818042</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996284</v>
+        <v>125996703</v>
       </c>
       <c r="B173" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,21 +17518,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489434</v>
+        <v>489239</v>
       </c>
       <c r="R173" t="n">
-        <v>6818042</v>
+        <v>6818065</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18865,32 +18865,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125991445</v>
+        <v>125992179</v>
       </c>
       <c r="B187" t="n">
-        <v>98355</v>
+        <v>78968</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488712</v>
+        <v>488791</v>
       </c>
       <c r="R187" t="n">
-        <v>6817879</v>
+        <v>6817820</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125995420</v>
       </c>
       <c r="B188" t="n">
         <v>78968</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>489064</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6817976</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19047,19 +19047,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125996514</v>
       </c>
       <c r="B189" t="n">
         <v>78968</v>
@@ -19090,17 +19090,17 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>489277</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6818090</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19156,45 +19156,45 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125728080</v>
       </c>
       <c r="B2" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125728083</v>
       </c>
       <c r="B3" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728120</v>
+        <v>125728101</v>
       </c>
       <c r="B4" t="n">
-        <v>80107</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489345</v>
+        <v>489357</v>
       </c>
       <c r="R4" t="n">
-        <v>6818246</v>
+        <v>6818163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728121</v>
+        <v>125728120</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489306</v>
+        <v>489345</v>
       </c>
       <c r="R5" t="n">
-        <v>6818055</v>
+        <v>6818246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728110</v>
+        <v>125728121</v>
       </c>
       <c r="B6" t="n">
-        <v>92710</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489380</v>
+        <v>489306</v>
       </c>
       <c r="R6" t="n">
-        <v>6818374</v>
+        <v>6818055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728137</v>
+        <v>125728110</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>92714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489352</v>
+        <v>489380</v>
       </c>
       <c r="R7" t="n">
-        <v>6818366</v>
+        <v>6818374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,50 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728112</v>
+        <v>125728150</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489161</v>
+        <v>489356</v>
       </c>
       <c r="R8" t="n">
-        <v>6817982</v>
+        <v>6818016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728150</v>
+        <v>125728137</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489356</v>
+        <v>489352</v>
       </c>
       <c r="R9" t="n">
-        <v>6818016</v>
+        <v>6818366</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>125728174</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,38 +1553,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728101</v>
+        <v>125728112</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489357</v>
+        <v>489161</v>
       </c>
       <c r="R11" t="n">
-        <v>6818163</v>
+        <v>6817982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R14" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,45 +1946,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728157</v>
+        <v>125728111</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489452</v>
+        <v>489223</v>
       </c>
       <c r="R15" t="n">
-        <v>6818179</v>
+        <v>6818133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728169</v>
+        <v>125728069</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489407</v>
+        <v>489204</v>
       </c>
       <c r="R16" t="n">
-        <v>6818356</v>
+        <v>6818104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728135</v>
+        <v>125728068</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,7 +2183,7 @@
         <v>489219</v>
       </c>
       <c r="R17" t="n">
-        <v>6818132</v>
+        <v>6818134</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728161</v>
+        <v>125728157</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489439</v>
+        <v>489452</v>
       </c>
       <c r="R18" t="n">
-        <v>6818361</v>
+        <v>6818179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,50 +2339,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728111</v>
+        <v>125728146</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489223</v>
+        <v>489261</v>
       </c>
       <c r="R19" t="n">
-        <v>6818133</v>
+        <v>6818155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728069</v>
+        <v>125728169</v>
       </c>
       <c r="B20" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489204</v>
+        <v>489407</v>
       </c>
       <c r="R20" t="n">
-        <v>6818104</v>
+        <v>6818356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728146</v>
+        <v>125728155</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489261</v>
+        <v>489417</v>
       </c>
       <c r="R21" t="n">
-        <v>6818155</v>
+        <v>6818154</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728155</v>
+        <v>125728135</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489417</v>
+        <v>489219</v>
       </c>
       <c r="R22" t="n">
-        <v>6818154</v>
+        <v>6818132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,6 +2701,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728068</v>
+        <v>125728161</v>
       </c>
       <c r="B23" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489219</v>
+        <v>489439</v>
       </c>
       <c r="R23" t="n">
-        <v>6818134</v>
+        <v>6818361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728147</v>
+        <v>125728124</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489255</v>
+        <v>489468</v>
       </c>
       <c r="R24" t="n">
-        <v>6818162</v>
+        <v>6818461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,32 +2926,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728124</v>
+        <v>125728079</v>
       </c>
       <c r="B25" t="n">
-        <v>80107</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489468</v>
+        <v>489130</v>
       </c>
       <c r="R25" t="n">
-        <v>6818461</v>
+        <v>6817993</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728079</v>
+        <v>125728176</v>
       </c>
       <c r="B26" t="n">
-        <v>79000</v>
+        <v>78639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489130</v>
+        <v>489383</v>
       </c>
       <c r="R26" t="n">
-        <v>6817993</v>
+        <v>6818074</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728176</v>
+        <v>125728081</v>
       </c>
       <c r="B27" t="n">
-        <v>78635</v>
+        <v>79004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489383</v>
+        <v>489450</v>
       </c>
       <c r="R27" t="n">
-        <v>6818074</v>
+        <v>6818184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728081</v>
+        <v>125728147</v>
       </c>
       <c r="B28" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489450</v>
+        <v>489255</v>
       </c>
       <c r="R28" t="n">
-        <v>6818184</v>
+        <v>6818162</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3317,7 +3317,7 @@
         <v>125728167</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>125728141</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125728166</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>125728164</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728082</v>
+        <v>125728103</v>
       </c>
       <c r="B35" t="n">
-        <v>79000</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489448</v>
+        <v>489344</v>
       </c>
       <c r="R35" t="n">
-        <v>6818191</v>
+        <v>6818246</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,50 +4016,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728181</v>
+        <v>125728104</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489399</v>
+        <v>489262</v>
       </c>
       <c r="R36" t="n">
-        <v>6818343</v>
+        <v>6818043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,45 +4113,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728103</v>
+        <v>125728181</v>
       </c>
       <c r="B37" t="n">
-        <v>80072</v>
+        <v>5176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489344</v>
+        <v>489399</v>
       </c>
       <c r="R37" t="n">
-        <v>6818246</v>
+        <v>6818343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728104</v>
+        <v>125728082</v>
       </c>
       <c r="B38" t="n">
-        <v>80072</v>
+        <v>79004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4226,21 +4226,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489262</v>
+        <v>489448</v>
       </c>
       <c r="R38" t="n">
-        <v>6818043</v>
+        <v>6818191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4315,7 +4315,7 @@
         <v>125728119</v>
       </c>
       <c r="B39" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>125728089</v>
       </c>
       <c r="B40" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>125728178</v>
       </c>
       <c r="B41" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>125728134</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>125728071</v>
       </c>
       <c r="B43" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>125728072</v>
       </c>
       <c r="B44" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728154</v>
+        <v>125728156</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489424</v>
+        <v>489450</v>
       </c>
       <c r="R45" t="n">
-        <v>6818132</v>
+        <v>6818159</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728156</v>
+        <v>125728159</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489450</v>
+        <v>489463</v>
       </c>
       <c r="R46" t="n">
-        <v>6818159</v>
+        <v>6818200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728159</v>
+        <v>125728154</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489463</v>
+        <v>489424</v>
       </c>
       <c r="R47" t="n">
-        <v>6818200</v>
+        <v>6818132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
         <v>125728085</v>
       </c>
       <c r="B49" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728075</v>
+        <v>125728073</v>
       </c>
       <c r="B50" t="n">
-        <v>91150</v>
+        <v>79590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489292</v>
+        <v>489392</v>
       </c>
       <c r="R50" t="n">
-        <v>6818151</v>
+        <v>6818361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728168</v>
+        <v>125728075</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>91154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489413</v>
+        <v>489292</v>
       </c>
       <c r="R51" t="n">
-        <v>6818350</v>
+        <v>6818151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728073</v>
+        <v>125728158</v>
       </c>
       <c r="B52" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489392</v>
+        <v>489449</v>
       </c>
       <c r="R52" t="n">
-        <v>6818361</v>
+        <v>6818184</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728171</v>
+        <v>125728168</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489374</v>
+        <v>489413</v>
       </c>
       <c r="R53" t="n">
-        <v>6818387</v>
+        <v>6818350</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728158</v>
+        <v>125728171</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489449</v>
+        <v>489374</v>
       </c>
       <c r="R54" t="n">
-        <v>6818184</v>
+        <v>6818387</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728109</v>
+        <v>125728086</v>
       </c>
       <c r="B55" t="n">
-        <v>97212</v>
+        <v>79004</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489452</v>
+        <v>489365</v>
       </c>
       <c r="R55" t="n">
-        <v>6818415</v>
+        <v>6818390</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728118</v>
+        <v>125728088</v>
       </c>
       <c r="B56" t="n">
-        <v>78727</v>
+        <v>96591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489422</v>
+        <v>489442</v>
       </c>
       <c r="R56" t="n">
-        <v>6818130</v>
+        <v>6818350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728086</v>
+        <v>125728163</v>
       </c>
       <c r="B57" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489365</v>
+        <v>489456</v>
       </c>
       <c r="R57" t="n">
-        <v>6818390</v>
+        <v>6818471</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728088</v>
+        <v>125728165</v>
       </c>
       <c r="B58" t="n">
-        <v>96587</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489442</v>
+        <v>489432</v>
       </c>
       <c r="R58" t="n">
-        <v>6818350</v>
+        <v>6818365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728163</v>
+        <v>125728109</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>97216</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489456</v>
+        <v>489452</v>
       </c>
       <c r="R59" t="n">
-        <v>6818471</v>
+        <v>6818415</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728165</v>
+        <v>125728118</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489432</v>
+        <v>489422</v>
       </c>
       <c r="R60" t="n">
-        <v>6818365</v>
+        <v>6818130</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
         <v>125728170</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>125728144</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>125728115</v>
       </c>
       <c r="B63" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>125728078</v>
       </c>
       <c r="B64" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>125728153</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>125728136</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B67" t="n">
-        <v>91242</v>
+        <v>79004</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R67" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728151</v>
+        <v>125728130</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>91246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489396</v>
+        <v>489444</v>
       </c>
       <c r="R68" t="n">
-        <v>6818028</v>
+        <v>6818412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728084</v>
+        <v>125728151</v>
       </c>
       <c r="B69" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489414</v>
+        <v>489396</v>
       </c>
       <c r="R69" t="n">
-        <v>6818350</v>
+        <v>6818028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728162</v>
+        <v>125728160</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489460</v>
+        <v>489463</v>
       </c>
       <c r="R70" t="n">
-        <v>6818444</v>
+        <v>6818278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728160</v>
+        <v>125728114</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7446,21 +7446,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489463</v>
+        <v>489364</v>
       </c>
       <c r="R71" t="n">
-        <v>6818278</v>
+        <v>6818169</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7535,7 +7535,7 @@
         <v>125728133</v>
       </c>
       <c r="B72" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>125728142</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728114</v>
+        <v>125728162</v>
       </c>
       <c r="B74" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489364</v>
+        <v>489460</v>
       </c>
       <c r="R74" t="n">
-        <v>6818169</v>
+        <v>6818444</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728179</v>
+        <v>125728098</v>
       </c>
       <c r="B75" t="n">
-        <v>95186</v>
+        <v>80104</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2383</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489412</v>
+        <v>489262</v>
       </c>
       <c r="R75" t="n">
-        <v>6818351</v>
+        <v>6818039</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,50 +7925,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728100</v>
+        <v>125728097</v>
       </c>
       <c r="B76" t="n">
-        <v>57648</v>
+        <v>80104</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489327</v>
+        <v>489345</v>
       </c>
       <c r="R76" t="n">
-        <v>6818047</v>
+        <v>6818245</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8027,10 +8022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728098</v>
+        <v>125728179</v>
       </c>
       <c r="B77" t="n">
-        <v>80100</v>
+        <v>95190</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8038,21 +8033,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>2383</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489262</v>
+        <v>489412</v>
       </c>
       <c r="R77" t="n">
-        <v>6818039</v>
+        <v>6818351</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8124,32 +8119,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728097</v>
+        <v>125728140</v>
       </c>
       <c r="B78" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8159,10 +8154,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489345</v>
+        <v>489337</v>
       </c>
       <c r="R78" t="n">
-        <v>6818245</v>
+        <v>6818236</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8221,10 +8216,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728140</v>
+        <v>125728145</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489337</v>
+        <v>489365</v>
       </c>
       <c r="R79" t="n">
-        <v>6818236</v>
+        <v>6818143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8318,10 +8313,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728145</v>
+        <v>125728100</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8329,34 +8324,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489365</v>
+        <v>489327</v>
       </c>
       <c r="R80" t="n">
-        <v>6818143</v>
+        <v>6818047</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
         <v>125728123</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125728148</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8609,10 +8609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728102</v>
+        <v>125728117</v>
       </c>
       <c r="B83" t="n">
-        <v>80072</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8620,21 +8620,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489338</v>
+        <v>489409</v>
       </c>
       <c r="R83" t="n">
-        <v>6818240</v>
+        <v>6818054</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728077</v>
+        <v>125728099</v>
       </c>
       <c r="B84" t="n">
-        <v>75067</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489458</v>
+        <v>489306</v>
       </c>
       <c r="R84" t="n">
-        <v>6818455</v>
+        <v>6818056</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728077</v>
       </c>
       <c r="B85" t="n">
-        <v>80071</v>
+        <v>75067</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489458</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818455</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728099</v>
+        <v>125728125</v>
       </c>
       <c r="B86" t="n">
-        <v>80100</v>
+        <v>80075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489306</v>
+        <v>489320</v>
       </c>
       <c r="R86" t="n">
-        <v>6818056</v>
+        <v>6818042</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728117</v>
+        <v>125728102</v>
       </c>
       <c r="B87" t="n">
-        <v>78727</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489409</v>
+        <v>489338</v>
       </c>
       <c r="R87" t="n">
-        <v>6818054</v>
+        <v>6818240</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
         <v>125728087</v>
       </c>
       <c r="B88" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>125728105</v>
       </c>
       <c r="B89" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>125728094</v>
       </c>
       <c r="B90" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>125728152</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>125728070</v>
       </c>
       <c r="B93" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B94" t="n">
-        <v>78635</v>
+        <v>91598</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R94" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728126</v>
+        <v>125728177</v>
       </c>
       <c r="B95" t="n">
-        <v>91594</v>
+        <v>78639</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2064</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489439</v>
+        <v>489452</v>
       </c>
       <c r="R95" t="n">
-        <v>6818162</v>
+        <v>6818167</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9880,32 +9880,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728090</v>
+        <v>125728116</v>
       </c>
       <c r="B96" t="n">
-        <v>91193</v>
+        <v>78731</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489418</v>
+        <v>489187</v>
       </c>
       <c r="R96" t="n">
-        <v>6818094</v>
+        <v>6818091</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728116</v>
+        <v>125728090</v>
       </c>
       <c r="B97" t="n">
-        <v>78727</v>
+        <v>91197</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489187</v>
+        <v>489418</v>
       </c>
       <c r="R97" t="n">
-        <v>6818091</v>
+        <v>6818094</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10077,7 +10077,7 @@
         <v>125728143</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728172</v>
+        <v>125728173</v>
       </c>
       <c r="B99" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489366</v>
+        <v>489340</v>
       </c>
       <c r="R99" t="n">
-        <v>6818389</v>
+        <v>6818386</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728127</v>
+        <v>125728172</v>
       </c>
       <c r="B100" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489267</v>
+        <v>489366</v>
       </c>
       <c r="R100" t="n">
-        <v>6818149</v>
+        <v>6818389</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728173</v>
+        <v>125728129</v>
       </c>
       <c r="B101" t="n">
-        <v>78968</v>
+        <v>91853</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10376,21 +10376,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489340</v>
+        <v>489370</v>
       </c>
       <c r="R101" t="n">
-        <v>6818386</v>
+        <v>6818176</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10465,7 +10465,7 @@
         <v>125728139</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728129</v>
+        <v>125728127</v>
       </c>
       <c r="B103" t="n">
-        <v>91849</v>
+        <v>78730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5454</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489370</v>
+        <v>489267</v>
       </c>
       <c r="R103" t="n">
-        <v>6818176</v>
+        <v>6818149</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B105" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,34 +10773,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R105" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10833,6 +10838,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10859,10 +10869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10870,39 +10880,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R106" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10935,11 +10940,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10969,7 +10969,7 @@
         <v>125724254</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11063,10 +11063,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125723347</v>
+        <v>125723877</v>
       </c>
       <c r="B108" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>125724786</v>
       </c>
       <c r="B110" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>125722589</v>
       </c>
       <c r="B111" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>125723050</v>
       </c>
       <c r="B112" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>125725272</v>
       </c>
       <c r="B117" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>125724536</v>
       </c>
       <c r="B118" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>125725082</v>
       </c>
       <c r="B119" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>125724111</v>
       </c>
       <c r="B120" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125869096</v>
       </c>
       <c r="B124" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>125869097</v>
       </c>
       <c r="B125" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869105</v>
       </c>
       <c r="B129" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869106</v>
       </c>
       <c r="B130" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125869115</v>
+        <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489123</v>
+        <v>489429</v>
       </c>
       <c r="R131" t="n">
-        <v>6817993</v>
+        <v>6818389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125869112</v>
+        <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13537,10 +13537,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>489429</v>
+        <v>489123</v>
       </c>
       <c r="R132" t="n">
-        <v>6818389</v>
+        <v>6817993</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13908,45 +13908,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B136" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R136" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14005,45 +14005,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B137" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R137" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14105,7 +14105,7 @@
         <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>125995990</v>
       </c>
       <c r="B140" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125995142</v>
+        <v>125994090</v>
       </c>
       <c r="B141" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489041</v>
+        <v>488989</v>
       </c>
       <c r="R141" t="n">
-        <v>6817951</v>
+        <v>6817941</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,22 +14478,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125994090</v>
+        <v>125995142</v>
       </c>
       <c r="B142" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>488989</v>
+        <v>489041</v>
       </c>
       <c r="R142" t="n">
-        <v>6817941</v>
+        <v>6817951</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,22 +14575,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125993642</v>
+        <v>125994790</v>
       </c>
       <c r="B143" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>488965</v>
+        <v>488932</v>
       </c>
       <c r="R143" t="n">
-        <v>6817938</v>
+        <v>6818043</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14684,10 +14684,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125994790</v>
+        <v>125993642</v>
       </c>
       <c r="B144" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14719,10 +14719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>488932</v>
+        <v>488965</v>
       </c>
       <c r="R144" t="n">
-        <v>6818043</v>
+        <v>6817938</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14883,10 +14883,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125996662</v>
+        <v>125996446</v>
       </c>
       <c r="B146" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14918,13 +14918,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>489260</v>
+        <v>489329</v>
       </c>
       <c r="R146" t="n">
-        <v>6818067</v>
+        <v>6818061</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14968,22 +14968,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125996446</v>
+        <v>125996662</v>
       </c>
       <c r="B147" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15015,13 +15015,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>489329</v>
+        <v>489260</v>
       </c>
       <c r="R147" t="n">
-        <v>6818061</v>
+        <v>6818067</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15065,22 +15065,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B148" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R148" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B149" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R149" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15376,7 +15376,7 @@
         <v>125996385</v>
       </c>
       <c r="B151" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B152" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R152" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B153" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R153" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125995381</v>
+        <v>125996438</v>
       </c>
       <c r="B154" t="n">
-        <v>91242</v>
+        <v>78972</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,37 +15675,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489035</v>
+        <v>489309</v>
       </c>
       <c r="R154" t="n">
-        <v>6817949</v>
+        <v>6818107</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B155" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,10 +15796,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R155" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996438</v>
+        <v>125996286</v>
       </c>
       <c r="B156" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15893,13 +15893,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489309</v>
+        <v>489446</v>
       </c>
       <c r="R156" t="n">
-        <v>6818107</v>
+        <v>6818036</v>
       </c>
       <c r="S156" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125996247</v>
+        <v>125995381</v>
       </c>
       <c r="B157" t="n">
-        <v>80071</v>
+        <v>91246</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489487</v>
+        <v>489035</v>
       </c>
       <c r="R157" t="n">
-        <v>6818014</v>
+        <v>6817949</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>125996113</v>
       </c>
       <c r="B158" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>125996114</v>
       </c>
       <c r="B159" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>125996381</v>
       </c>
       <c r="B161" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125992967</v>
+        <v>125995149</v>
       </c>
       <c r="B162" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,21 +16451,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16475,13 +16475,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>488808</v>
+        <v>489055</v>
       </c>
       <c r="R162" t="n">
-        <v>6817936</v>
+        <v>6818041</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16525,12 +16525,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -16540,7 +16540,7 @@
         <v>125991267</v>
       </c>
       <c r="B163" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>125996410</v>
       </c>
       <c r="B164" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16731,10 +16731,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125991520</v>
+        <v>125992967</v>
       </c>
       <c r="B165" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488720</v>
+        <v>488808</v>
       </c>
       <c r="R165" t="n">
-        <v>6817985</v>
+        <v>6817936</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125996631</v>
+        <v>125991520</v>
       </c>
       <c r="B166" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,34 +16839,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>489259</v>
+        <v>488720</v>
       </c>
       <c r="R166" t="n">
-        <v>6818066</v>
+        <v>6817985</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125995149</v>
+        <v>125996631</v>
       </c>
       <c r="B167" t="n">
-        <v>78727</v>
+        <v>57811</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,37 +16936,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489055</v>
+        <v>489259</v>
       </c>
       <c r="R167" t="n">
-        <v>6818041</v>
+        <v>6818066</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17010,22 +17010,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995740</v>
+        <v>125995059</v>
       </c>
       <c r="B168" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17033,37 +17033,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489141</v>
+        <v>489030</v>
       </c>
       <c r="R168" t="n">
-        <v>6818047</v>
+        <v>6818049</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,22 +17107,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125994323</v>
+        <v>125995740</v>
       </c>
       <c r="B169" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17150,14 +17150,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>488963</v>
+        <v>489141</v>
       </c>
       <c r="R169" t="n">
-        <v>6817966</v>
+        <v>6818047</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125990421</v>
+        <v>125994323</v>
       </c>
       <c r="B170" t="n">
-        <v>91682</v>
+        <v>78972</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488613</v>
+        <v>488963</v>
       </c>
       <c r="R170" t="n">
-        <v>6818174</v>
+        <v>6817966</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,44 +17301,44 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125995059</v>
+        <v>125990421</v>
       </c>
       <c r="B171" t="n">
-        <v>78727</v>
+        <v>91686</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,10 +17348,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>489030</v>
+        <v>488613</v>
       </c>
       <c r="R171" t="n">
-        <v>6818049</v>
+        <v>6818174</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996284</v>
+        <v>125996703</v>
       </c>
       <c r="B172" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,21 +17421,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17445,13 +17445,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489434</v>
+        <v>489239</v>
       </c>
       <c r="R172" t="n">
-        <v>6818042</v>
+        <v>6818065</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996703</v>
+        <v>125996284</v>
       </c>
       <c r="B173" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,21 +17518,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489239</v>
+        <v>489434</v>
       </c>
       <c r="R173" t="n">
-        <v>6818065</v>
+        <v>6818042</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -17607,7 +17607,7 @@
         <v>125994504</v>
       </c>
       <c r="B174" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125995962</v>
+        <v>125996386</v>
       </c>
       <c r="B175" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17712,21 +17712,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>489204</v>
+        <v>489383</v>
       </c>
       <c r="R175" t="n">
-        <v>6818012</v>
+        <v>6818097</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,10 +17798,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125994342</v>
+        <v>125993566</v>
       </c>
       <c r="B176" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17833,13 +17833,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>488947</v>
+        <v>488920</v>
       </c>
       <c r="R176" t="n">
-        <v>6818000</v>
+        <v>6817948</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,22 +17883,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125996386</v>
+        <v>125996288</v>
       </c>
       <c r="B177" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17930,13 +17930,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>489383</v>
+        <v>489443</v>
       </c>
       <c r="R177" t="n">
-        <v>6818097</v>
+        <v>6818073</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -17980,22 +17980,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125993829</v>
+        <v>125993417</v>
       </c>
       <c r="B178" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18027,13 +18027,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>488971</v>
+        <v>488839</v>
       </c>
       <c r="R178" t="n">
-        <v>6817935</v>
+        <v>6817946</v>
       </c>
       <c r="S178" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18077,22 +18077,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125996288</v>
+        <v>125993829</v>
       </c>
       <c r="B179" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18120,17 +18120,17 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>489443</v>
+        <v>488971</v>
       </c>
       <c r="R179" t="n">
-        <v>6818073</v>
+        <v>6817935</v>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18186,10 +18186,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125993417</v>
+        <v>125994342</v>
       </c>
       <c r="B180" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18221,10 +18221,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>488839</v>
+        <v>488947</v>
       </c>
       <c r="R180" t="n">
-        <v>6817946</v>
+        <v>6818000</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18283,10 +18283,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125993566</v>
+        <v>125995962</v>
       </c>
       <c r="B181" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,37 +18294,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>488920</v>
+        <v>489204</v>
       </c>
       <c r="R181" t="n">
-        <v>6817948</v>
+        <v>6818012</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -18368,22 +18368,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125996119</v>
+        <v>125993495</v>
       </c>
       <c r="B182" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18391,37 +18391,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>489362</v>
+        <v>488864</v>
       </c>
       <c r="R182" t="n">
-        <v>6818010</v>
+        <v>6817945</v>
       </c>
       <c r="S182" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18465,44 +18465,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125996051</v>
+        <v>125996069</v>
       </c>
       <c r="B183" t="n">
-        <v>79000</v>
+        <v>80111</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18512,10 +18512,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>489241</v>
+        <v>489255</v>
       </c>
       <c r="R183" t="n">
-        <v>6818009</v>
+        <v>6818046</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18574,32 +18574,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125996069</v>
+        <v>125996119</v>
       </c>
       <c r="B184" t="n">
-        <v>80107</v>
+        <v>79004</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18609,13 +18609,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>489255</v>
+        <v>489362</v>
       </c>
       <c r="R184" t="n">
-        <v>6818046</v>
+        <v>6818010</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -18671,10 +18671,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125993495</v>
+        <v>125996051</v>
       </c>
       <c r="B185" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18682,34 +18682,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>488864</v>
+        <v>489241</v>
       </c>
       <c r="R185" t="n">
-        <v>6817945</v>
+        <v>6818009</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18756,22 +18756,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18799,14 +18799,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,22 +18853,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125992179</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488791</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6817820</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18962,10 +18962,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125995420</v>
+        <v>125992179</v>
       </c>
       <c r="B188" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>489064</v>
+        <v>488791</v>
       </c>
       <c r="R188" t="n">
-        <v>6817976</v>
+        <v>6817820</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19047,22 +19047,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125996514</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19090,17 +19090,17 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489277</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6818090</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19253,10 +19253,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125995939</v>
+        <v>125996400</v>
       </c>
       <c r="B191" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19288,13 +19288,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>489210</v>
+        <v>489414</v>
       </c>
       <c r="R191" t="n">
-        <v>6818012</v>
+        <v>6818155</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19338,12 +19338,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -19353,7 +19353,7 @@
         <v>125996428</v>
       </c>
       <c r="B192" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19447,10 +19447,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125996400</v>
+        <v>125995939</v>
       </c>
       <c r="B193" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19482,13 +19482,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>489414</v>
+        <v>489210</v>
       </c>
       <c r="R193" t="n">
-        <v>6818155</v>
+        <v>6818012</v>
       </c>
       <c r="S193" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -19532,12 +19532,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -19547,7 +19547,7 @@
         <v>125994510</v>
       </c>
       <c r="B194" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>125995904</v>
       </c>
       <c r="B195" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>125995626</v>
       </c>
       <c r="B196" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>125994469</v>
       </c>
       <c r="B197" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>125995410</v>
       </c>
       <c r="B198" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20029,10 +20029,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125996494</v>
+        <v>125996865</v>
       </c>
       <c r="B199" t="n">
-        <v>78727</v>
+        <v>79004</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20040,21 +20040,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20064,13 +20064,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489277</v>
+        <v>489208</v>
       </c>
       <c r="R199" t="n">
-        <v>6818089</v>
+        <v>6818043</v>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -20114,22 +20114,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125996865</v>
+        <v>125996064</v>
       </c>
       <c r="B200" t="n">
-        <v>79000</v>
+        <v>80076</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20137,21 +20137,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489208</v>
+        <v>489258</v>
       </c>
       <c r="R200" t="n">
-        <v>6818043</v>
+        <v>6818035</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20226,7 +20226,7 @@
         <v>125995830</v>
       </c>
       <c r="B201" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996064</v>
+        <v>125996494</v>
       </c>
       <c r="B202" t="n">
-        <v>80072</v>
+        <v>78731</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,13 +20355,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489258</v>
+        <v>489277</v>
       </c>
       <c r="R202" t="n">
-        <v>6818035</v>
+        <v>6818089</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20405,12 +20405,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
@@ -20420,7 +20420,7 @@
         <v>125996970</v>
       </c>
       <c r="B203" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>125996240</v>
       </c>
       <c r="B204" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728101</v>
+        <v>125728120</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>80111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489357</v>
+        <v>489345</v>
       </c>
       <c r="R4" t="n">
-        <v>6818163</v>
+        <v>6818246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728120</v>
+        <v>125728121</v>
       </c>
       <c r="B5" t="n">
         <v>80111</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489345</v>
+        <v>489306</v>
       </c>
       <c r="R5" t="n">
-        <v>6818246</v>
+        <v>6818055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728121</v>
+        <v>125728110</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>92714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489306</v>
+        <v>489380</v>
       </c>
       <c r="R6" t="n">
-        <v>6818055</v>
+        <v>6818374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728110</v>
+        <v>125728101</v>
       </c>
       <c r="B7" t="n">
-        <v>92714</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1171,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489380</v>
+        <v>489357</v>
       </c>
       <c r="R7" t="n">
-        <v>6818374</v>
+        <v>6818163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B13" t="n">
-        <v>91197</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728091</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>91197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489452</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728160</v>
+        <v>125728114</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489463</v>
+        <v>489364</v>
       </c>
       <c r="R70" t="n">
-        <v>6818278</v>
+        <v>6818169</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B71" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7446,21 +7446,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R71" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -12252,45 +12252,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B120" t="n">
-        <v>78972</v>
+        <v>57473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R120" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12349,50 +12354,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B121" t="n">
-        <v>57473</v>
+        <v>78972</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R121" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996241</v>
+        <v>125996409</v>
       </c>
       <c r="B135" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13846,13 +13846,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489437</v>
+        <v>489377</v>
       </c>
       <c r="R135" t="n">
-        <v>6818032</v>
+        <v>6818145</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,60 +13896,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125995667</v>
+        <v>125996241</v>
       </c>
       <c r="B136" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489117</v>
+        <v>489437</v>
       </c>
       <c r="R136" t="n">
-        <v>6818011</v>
+        <v>6818032</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125996346</v>
+        <v>125994090</v>
       </c>
       <c r="B138" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>489439</v>
+        <v>488989</v>
       </c>
       <c r="R138" t="n">
-        <v>6818061</v>
+        <v>6817941</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,10 +14199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125996407</v>
+        <v>125995142</v>
       </c>
       <c r="B139" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,37 +14210,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489391</v>
+        <v>489041</v>
       </c>
       <c r="R139" t="n">
-        <v>6818133</v>
+        <v>6817951</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14284,19 +14284,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125995990</v>
+        <v>125996346</v>
       </c>
       <c r="B140" t="n">
         <v>79004</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489201</v>
+        <v>489439</v>
       </c>
       <c r="R140" t="n">
-        <v>6818003</v>
+        <v>6818061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125994090</v>
+        <v>125996407</v>
       </c>
       <c r="B141" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,34 +14404,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>488989</v>
+        <v>489391</v>
       </c>
       <c r="R141" t="n">
-        <v>6817941</v>
+        <v>6818133</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995142</v>
+        <v>125995990</v>
       </c>
       <c r="B142" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489041</v>
+        <v>489201</v>
       </c>
       <c r="R142" t="n">
-        <v>6817951</v>
+        <v>6818003</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B152" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R152" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B153" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R153" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125996438</v>
+        <v>125995381</v>
       </c>
       <c r="B154" t="n">
-        <v>78972</v>
+        <v>91246</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,37 +15675,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489309</v>
+        <v>489035</v>
       </c>
       <c r="R154" t="n">
-        <v>6818107</v>
+        <v>6817949</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B155" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R155" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B156" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R156" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125995381</v>
+        <v>125996286</v>
       </c>
       <c r="B157" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489035</v>
+        <v>489446</v>
       </c>
       <c r="R157" t="n">
-        <v>6817949</v>
+        <v>6818036</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125995149</v>
+        <v>125991267</v>
       </c>
       <c r="B162" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,21 +16451,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>489055</v>
+        <v>488729</v>
       </c>
       <c r="R162" t="n">
-        <v>6818041</v>
+        <v>6817882</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16537,7 +16537,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125991267</v>
+        <v>125996410</v>
       </c>
       <c r="B163" t="n">
         <v>78972</v>
@@ -16568,17 +16568,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>488729</v>
+        <v>489371</v>
       </c>
       <c r="R163" t="n">
-        <v>6817882</v>
+        <v>6818137</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125996410</v>
+        <v>125992967</v>
       </c>
       <c r="B164" t="n">
         <v>78972</v>
@@ -16665,14 +16665,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>489371</v>
+        <v>488808</v>
       </c>
       <c r="R164" t="n">
-        <v>6818137</v>
+        <v>6817936</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125992967</v>
+        <v>125991520</v>
       </c>
       <c r="B165" t="n">
         <v>78972</v>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488808</v>
+        <v>488720</v>
       </c>
       <c r="R165" t="n">
-        <v>6817936</v>
+        <v>6817985</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125991520</v>
+        <v>125996631</v>
       </c>
       <c r="B166" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,34 +16839,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488720</v>
+        <v>489259</v>
       </c>
       <c r="R166" t="n">
-        <v>6817985</v>
+        <v>6818066</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125996631</v>
+        <v>125995149</v>
       </c>
       <c r="B167" t="n">
-        <v>57811</v>
+        <v>78731</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,37 +16936,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489259</v>
+        <v>489055</v>
       </c>
       <c r="R167" t="n">
-        <v>6818066</v>
+        <v>6818041</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17010,22 +17010,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995059</v>
+        <v>125995740</v>
       </c>
       <c r="B168" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17033,37 +17033,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489030</v>
+        <v>489141</v>
       </c>
       <c r="R168" t="n">
-        <v>6818049</v>
+        <v>6818047</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,19 +17107,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995740</v>
+        <v>125994323</v>
       </c>
       <c r="B169" t="n">
         <v>78972</v>
@@ -17150,14 +17150,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489141</v>
+        <v>488963</v>
       </c>
       <c r="R169" t="n">
-        <v>6818047</v>
+        <v>6817966</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125994323</v>
+        <v>125990421</v>
       </c>
       <c r="B170" t="n">
-        <v>78972</v>
+        <v>91686</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488963</v>
+        <v>488613</v>
       </c>
       <c r="R170" t="n">
-        <v>6817966</v>
+        <v>6818174</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,44 +17301,44 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125990421</v>
+        <v>125995059</v>
       </c>
       <c r="B171" t="n">
-        <v>91686</v>
+        <v>78731</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1209</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,10 +17348,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>488613</v>
+        <v>489030</v>
       </c>
       <c r="R171" t="n">
-        <v>6818174</v>
+        <v>6818049</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B186" t="n">
-        <v>78972</v>
+        <v>98359</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B187" t="n">
         <v>78972</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125993813</v>
       </c>
       <c r="B188" t="n">
         <v>78972</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>488933</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6817911</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125992179</v>
       </c>
       <c r="B189" t="n">
         <v>78972</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>488791</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6817820</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125995420</v>
       </c>
       <c r="B190" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>489064</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6817976</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728120</v>
+        <v>125728150</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489345</v>
+        <v>489356</v>
       </c>
       <c r="R4" t="n">
-        <v>6818246</v>
+        <v>6818016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728121</v>
+        <v>125728101</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R5" t="n">
-        <v>6818055</v>
+        <v>6818163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728110</v>
+        <v>125728137</v>
       </c>
       <c r="B6" t="n">
-        <v>92714</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489380</v>
+        <v>489352</v>
       </c>
       <c r="R6" t="n">
-        <v>6818374</v>
+        <v>6818366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728101</v>
+        <v>125728174</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,39 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489357</v>
+        <v>489338</v>
       </c>
       <c r="R7" t="n">
-        <v>6818163</v>
+        <v>6818397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728150</v>
+        <v>125728120</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489356</v>
+        <v>489345</v>
       </c>
       <c r="R8" t="n">
-        <v>6818016</v>
+        <v>6818246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728137</v>
+        <v>125728121</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489352</v>
+        <v>489306</v>
       </c>
       <c r="R9" t="n">
-        <v>6818366</v>
+        <v>6818055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728174</v>
+        <v>125728110</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489338</v>
+        <v>489380</v>
       </c>
       <c r="R10" t="n">
-        <v>6818397</v>
+        <v>6818374</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728113</v>
+        <v>125728091</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489363</v>
+        <v>489452</v>
       </c>
       <c r="R12" t="n">
-        <v>6818242</v>
+        <v>6818425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728091</v>
+        <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>91197</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489452</v>
+        <v>489363</v>
       </c>
       <c r="R14" t="n">
-        <v>6818425</v>
+        <v>6818242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,50 +1946,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728111</v>
+        <v>125728157</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489223</v>
+        <v>489452</v>
       </c>
       <c r="R15" t="n">
-        <v>6818133</v>
+        <v>6818179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728069</v>
+        <v>125728169</v>
       </c>
       <c r="B16" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489204</v>
+        <v>489407</v>
       </c>
       <c r="R16" t="n">
-        <v>6818104</v>
+        <v>6818356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728068</v>
+        <v>125728135</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2183,7 +2178,7 @@
         <v>489219</v>
       </c>
       <c r="R17" t="n">
-        <v>6818134</v>
+        <v>6818132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728157</v>
+        <v>125728146</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489452</v>
+        <v>489261</v>
       </c>
       <c r="R18" t="n">
-        <v>6818179</v>
+        <v>6818155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728146</v>
+        <v>125728155</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489261</v>
+        <v>489417</v>
       </c>
       <c r="R19" t="n">
-        <v>6818155</v>
+        <v>6818154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728169</v>
+        <v>125728161</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489407</v>
+        <v>489439</v>
       </c>
       <c r="R20" t="n">
-        <v>6818356</v>
+        <v>6818361</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728155</v>
+        <v>125728069</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489417</v>
+        <v>489204</v>
       </c>
       <c r="R21" t="n">
-        <v>6818154</v>
+        <v>6818104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728135</v>
+        <v>125728068</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         <v>489219</v>
       </c>
       <c r="R22" t="n">
-        <v>6818132</v>
+        <v>6818134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,45 +2727,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728161</v>
+        <v>125728111</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489439</v>
+        <v>489223</v>
       </c>
       <c r="R23" t="n">
-        <v>6818361</v>
+        <v>6818133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728103</v>
+        <v>125728082</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>79004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489344</v>
+        <v>489448</v>
       </c>
       <c r="R35" t="n">
-        <v>6818246</v>
+        <v>6818191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728104</v>
+        <v>125728103</v>
       </c>
       <c r="B36" t="n">
         <v>80076</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489262</v>
+        <v>489344</v>
       </c>
       <c r="R36" t="n">
-        <v>6818043</v>
+        <v>6818246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,50 +4113,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728181</v>
+        <v>125728104</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489399</v>
+        <v>489262</v>
       </c>
       <c r="R37" t="n">
-        <v>6818343</v>
+        <v>6818043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,45 +4210,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728082</v>
+        <v>125728181</v>
       </c>
       <c r="B38" t="n">
-        <v>79004</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489448</v>
+        <v>489399</v>
       </c>
       <c r="R38" t="n">
-        <v>6818191</v>
+        <v>6818343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728119</v>
+        <v>125728089</v>
       </c>
       <c r="B39" t="n">
-        <v>78731</v>
+        <v>96592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489446</v>
+        <v>489455</v>
       </c>
       <c r="R39" t="n">
-        <v>6818191</v>
+        <v>6818449</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728089</v>
+        <v>125728178</v>
       </c>
       <c r="B40" t="n">
-        <v>96591</v>
+        <v>78639</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489455</v>
+        <v>489394</v>
       </c>
       <c r="R40" t="n">
-        <v>6818449</v>
+        <v>6818362</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728178</v>
+        <v>125728134</v>
       </c>
       <c r="B41" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489394</v>
+        <v>489318</v>
       </c>
       <c r="R41" t="n">
-        <v>6818362</v>
+        <v>6818135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4577,6 +4577,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4603,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728134</v>
+        <v>125728119</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489318</v>
+        <v>489446</v>
       </c>
       <c r="R42" t="n">
-        <v>6818135</v>
+        <v>6818191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728071</v>
+        <v>125728154</v>
       </c>
       <c r="B43" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489452</v>
+        <v>489424</v>
       </c>
       <c r="R43" t="n">
-        <v>6818185</v>
+        <v>6818132</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728072</v>
+        <v>125728071</v>
       </c>
       <c r="B44" t="n">
         <v>79590</v>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489446</v>
+        <v>489452</v>
       </c>
       <c r="R44" t="n">
-        <v>6818191</v>
+        <v>6818185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728156</v>
+        <v>125728072</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489450</v>
+        <v>489446</v>
       </c>
       <c r="R45" t="n">
-        <v>6818159</v>
+        <v>6818191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728159</v>
+        <v>125728156</v>
       </c>
       <c r="B46" t="n">
         <v>78972</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489463</v>
+        <v>489450</v>
       </c>
       <c r="R46" t="n">
-        <v>6818200</v>
+        <v>6818159</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728154</v>
+        <v>125728159</v>
       </c>
       <c r="B47" t="n">
         <v>78972</v>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489424</v>
+        <v>489463</v>
       </c>
       <c r="R47" t="n">
-        <v>6818132</v>
+        <v>6818200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R49" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728073</v>
+        <v>125728085</v>
       </c>
       <c r="B50" t="n">
-        <v>79590</v>
+        <v>79004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489392</v>
+        <v>489411</v>
       </c>
       <c r="R50" t="n">
-        <v>6818361</v>
+        <v>6818380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728075</v>
+        <v>125728158</v>
       </c>
       <c r="B51" t="n">
-        <v>91154</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489292</v>
+        <v>489449</v>
       </c>
       <c r="R51" t="n">
-        <v>6818151</v>
+        <v>6818184</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728158</v>
+        <v>125728168</v>
       </c>
       <c r="B52" t="n">
         <v>78972</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489449</v>
+        <v>489413</v>
       </c>
       <c r="R52" t="n">
-        <v>6818184</v>
+        <v>6818350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728168</v>
+        <v>125728171</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489413</v>
+        <v>489374</v>
       </c>
       <c r="R53" t="n">
-        <v>6818350</v>
+        <v>6818387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728171</v>
+        <v>125728075</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>91154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489374</v>
+        <v>489292</v>
       </c>
       <c r="R54" t="n">
-        <v>6818387</v>
+        <v>6818151</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5978,7 +5978,7 @@
         <v>125728088</v>
       </c>
       <c r="B56" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>125728109</v>
       </c>
       <c r="B59" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728078</v>
+        <v>125728153</v>
       </c>
       <c r="B64" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489352</v>
+        <v>489420</v>
       </c>
       <c r="R64" t="n">
-        <v>6818362</v>
+        <v>6818126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B65" t="n">
         <v>78972</v>
@@ -6883,10 +6883,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R65" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,6 +6919,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6945,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6956,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6980,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R66" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,11 +7021,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B67" t="n">
-        <v>79004</v>
+        <v>91246</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R67" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B68" t="n">
-        <v>91246</v>
+        <v>79004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R68" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728160</v>
+        <v>125728133</v>
       </c>
       <c r="B71" t="n">
         <v>78972</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489463</v>
+        <v>489386</v>
       </c>
       <c r="R71" t="n">
-        <v>6818278</v>
+        <v>6818081</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,6 +7506,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,7 +7537,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728133</v>
+        <v>125728160</v>
       </c>
       <c r="B72" t="n">
         <v>78972</v>
@@ -7567,10 +7572,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489386</v>
+        <v>489463</v>
       </c>
       <c r="R72" t="n">
-        <v>6818081</v>
+        <v>6818278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,11 +7608,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7828,32 +7828,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728098</v>
+        <v>125728140</v>
       </c>
       <c r="B75" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489262</v>
+        <v>489337</v>
       </c>
       <c r="R75" t="n">
-        <v>6818039</v>
+        <v>6818236</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,32 +7925,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728097</v>
+        <v>125728145</v>
       </c>
       <c r="B76" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489345</v>
+        <v>489365</v>
       </c>
       <c r="R76" t="n">
-        <v>6818245</v>
+        <v>6818143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728179</v>
+        <v>125728098</v>
       </c>
       <c r="B77" t="n">
-        <v>95190</v>
+        <v>80104</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2383</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489412</v>
+        <v>489262</v>
       </c>
       <c r="R77" t="n">
-        <v>6818351</v>
+        <v>6818039</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,32 +8119,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728140</v>
+        <v>125728097</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489337</v>
+        <v>489345</v>
       </c>
       <c r="R78" t="n">
-        <v>6818236</v>
+        <v>6818245</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8216,32 +8216,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728145</v>
+        <v>125728179</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>95191</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2383</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489365</v>
+        <v>489412</v>
       </c>
       <c r="R79" t="n">
-        <v>6818143</v>
+        <v>6818351</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8609,32 +8609,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728117</v>
+        <v>125728099</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489409</v>
+        <v>489306</v>
       </c>
       <c r="R83" t="n">
-        <v>6818054</v>
+        <v>6818056</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728099</v>
+        <v>125728077</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>75067</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489306</v>
+        <v>489458</v>
       </c>
       <c r="R84" t="n">
-        <v>6818056</v>
+        <v>6818455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728077</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>75067</v>
+        <v>80075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489458</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818455</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728125</v>
+        <v>125728102</v>
       </c>
       <c r="B86" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489320</v>
+        <v>489338</v>
       </c>
       <c r="R86" t="n">
-        <v>6818042</v>
+        <v>6818240</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728102</v>
+        <v>125728117</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489338</v>
+        <v>489409</v>
       </c>
       <c r="R87" t="n">
-        <v>6818240</v>
+        <v>6818054</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728087</v>
+        <v>125728105</v>
       </c>
       <c r="B88" t="n">
-        <v>79004</v>
+        <v>79979</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489343</v>
+        <v>489306</v>
       </c>
       <c r="R88" t="n">
-        <v>6818374</v>
+        <v>6818062</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728105</v>
+        <v>125728094</v>
       </c>
       <c r="B89" t="n">
-        <v>79979</v>
+        <v>91197</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9202,21 +9202,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R89" t="n">
-        <v>6818062</v>
+        <v>6818380</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,32 +9288,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728094</v>
+        <v>125728152</v>
       </c>
       <c r="B90" t="n">
-        <v>91197</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489357</v>
+        <v>489415</v>
       </c>
       <c r="R90" t="n">
-        <v>6818380</v>
+        <v>6818087</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728152</v>
+        <v>125728107</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9396,34 +9396,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489415</v>
+        <v>489359</v>
       </c>
       <c r="R91" t="n">
-        <v>6818087</v>
+        <v>6818332</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9456,6 +9461,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9482,10 +9492,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728107</v>
+        <v>125728087</v>
       </c>
       <c r="B92" t="n">
-        <v>57651</v>
+        <v>79004</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9493,39 +9503,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489359</v>
+        <v>489343</v>
       </c>
       <c r="R92" t="n">
-        <v>6818332</v>
+        <v>6818374</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9558,11 +9563,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728070</v>
+        <v>125728177</v>
       </c>
       <c r="B93" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489185</v>
+        <v>489452</v>
       </c>
       <c r="R93" t="n">
-        <v>6818091</v>
+        <v>6818167</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B94" t="n">
-        <v>91598</v>
+        <v>79590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R94" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B95" t="n">
-        <v>78639</v>
+        <v>91598</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R95" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9880,32 +9880,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728116</v>
+        <v>125728090</v>
       </c>
       <c r="B96" t="n">
-        <v>78731</v>
+        <v>91197</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489187</v>
+        <v>489418</v>
       </c>
       <c r="R96" t="n">
-        <v>6818091</v>
+        <v>6818094</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728090</v>
+        <v>125728116</v>
       </c>
       <c r="B97" t="n">
-        <v>91197</v>
+        <v>78731</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489418</v>
+        <v>489187</v>
       </c>
       <c r="R97" t="n">
-        <v>6818094</v>
+        <v>6818091</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10171,7 +10171,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728173</v>
+        <v>125728139</v>
       </c>
       <c r="B99" t="n">
         <v>78972</v>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489340</v>
+        <v>489360</v>
       </c>
       <c r="R99" t="n">
-        <v>6818386</v>
+        <v>6818301</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728172</v>
+        <v>125728127</v>
       </c>
       <c r="B100" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489366</v>
+        <v>489267</v>
       </c>
       <c r="R100" t="n">
-        <v>6818389</v>
+        <v>6818149</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10462,7 +10462,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728139</v>
+        <v>125728173</v>
       </c>
       <c r="B102" t="n">
         <v>78972</v>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489360</v>
+        <v>489340</v>
       </c>
       <c r="R102" t="n">
-        <v>6818301</v>
+        <v>6818386</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728127</v>
+        <v>125728172</v>
       </c>
       <c r="B103" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489267</v>
+        <v>489366</v>
       </c>
       <c r="R103" t="n">
-        <v>6818149</v>
+        <v>6818389</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,39 +10773,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R105" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,11 +10833,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10869,10 +10859,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10880,34 +10870,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R106" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10940,6 +10935,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11650,38 +11650,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125722694</v>
+        <v>125723678</v>
       </c>
       <c r="B114" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R114" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,11 +11726,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11757,38 +11752,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125723678</v>
+        <v>125722694</v>
       </c>
       <c r="B115" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11797,10 +11792,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R115" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11833,6 +11828,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12252,50 +12252,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B120" t="n">
-        <v>57473</v>
+        <v>78972</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R120" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12354,45 +12349,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B121" t="n">
-        <v>78972</v>
+        <v>57473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R121" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125869105</v>
+        <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13219,10 +13219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>489416</v>
+        <v>489469</v>
       </c>
       <c r="R129" t="n">
-        <v>6818376</v>
+        <v>6818353</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13281,10 +13281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125869106</v>
+        <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>489469</v>
+        <v>489416</v>
       </c>
       <c r="R130" t="n">
-        <v>6818353</v>
+        <v>6818376</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13390,7 +13390,7 @@
         <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996409</v>
+        <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13846,13 +13846,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489377</v>
+        <v>489437</v>
       </c>
       <c r="R135" t="n">
-        <v>6818145</v>
+        <v>6818032</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,60 +13896,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996241</v>
+        <v>125995667</v>
       </c>
       <c r="B136" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489437</v>
+        <v>489117</v>
       </c>
       <c r="R136" t="n">
-        <v>6818032</v>
+        <v>6818011</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B137" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R137" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125994090</v>
+        <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>488989</v>
+        <v>489439</v>
       </c>
       <c r="R138" t="n">
-        <v>6817941</v>
+        <v>6818061</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,10 +14199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125995142</v>
+        <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,37 +14210,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489041</v>
+        <v>489391</v>
       </c>
       <c r="R139" t="n">
-        <v>6817951</v>
+        <v>6818133</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14284,22 +14284,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125996346</v>
+        <v>125994090</v>
       </c>
       <c r="B140" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14307,34 +14307,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489439</v>
+        <v>488989</v>
       </c>
       <c r="R140" t="n">
-        <v>6818061</v>
+        <v>6817941</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125996407</v>
+        <v>125995142</v>
       </c>
       <c r="B141" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,37 +14404,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489391</v>
+        <v>489041</v>
       </c>
       <c r="R141" t="n">
-        <v>6818133</v>
+        <v>6817951</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,12 +14478,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125995381</v>
+        <v>125996438</v>
       </c>
       <c r="B154" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,37 +15675,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489035</v>
+        <v>489309</v>
       </c>
       <c r="R154" t="n">
-        <v>6817949</v>
+        <v>6818107</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996438</v>
+        <v>125996247</v>
       </c>
       <c r="B155" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489309</v>
+        <v>489487</v>
       </c>
       <c r="R155" t="n">
-        <v>6818107</v>
+        <v>6818014</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996247</v>
+        <v>125996286</v>
       </c>
       <c r="B156" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489487</v>
+        <v>489446</v>
       </c>
       <c r="R156" t="n">
-        <v>6818014</v>
+        <v>6818036</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125996286</v>
+        <v>125995381</v>
       </c>
       <c r="B157" t="n">
-        <v>78972</v>
+        <v>91246</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489446</v>
+        <v>489035</v>
       </c>
       <c r="R157" t="n">
-        <v>6818036</v>
+        <v>6817949</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16052,48 +16052,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125996113</v>
+        <v>125992923</v>
       </c>
       <c r="B158" t="n">
-        <v>79004</v>
+        <v>98360</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>489312</v>
+        <v>488811</v>
       </c>
       <c r="R158" t="n">
-        <v>6817997</v>
+        <v>6817901</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125996114</v>
+        <v>125996113</v>
       </c>
       <c r="B159" t="n">
         <v>79004</v>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>489329</v>
+        <v>489312</v>
       </c>
       <c r="R159" t="n">
-        <v>6818006</v>
+        <v>6817997</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16246,48 +16246,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125992923</v>
+        <v>125996114</v>
       </c>
       <c r="B160" t="n">
-        <v>98359</v>
+        <v>79004</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>488811</v>
+        <v>489329</v>
       </c>
       <c r="R160" t="n">
-        <v>6817901</v>
+        <v>6818006</v>
       </c>
       <c r="S160" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125991267</v>
+        <v>125996631</v>
       </c>
       <c r="B162" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,37 +16451,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>488729</v>
+        <v>489259</v>
       </c>
       <c r="R162" t="n">
-        <v>6817882</v>
+        <v>6818066</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16525,19 +16525,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996410</v>
+        <v>125991267</v>
       </c>
       <c r="B163" t="n">
         <v>78972</v>
@@ -16568,17 +16568,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489371</v>
+        <v>488729</v>
       </c>
       <c r="R163" t="n">
-        <v>6818137</v>
+        <v>6817882</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125992967</v>
+        <v>125996410</v>
       </c>
       <c r="B164" t="n">
         <v>78972</v>
@@ -16665,14 +16665,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488808</v>
+        <v>489371</v>
       </c>
       <c r="R164" t="n">
-        <v>6817936</v>
+        <v>6818137</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125991520</v>
+        <v>125992967</v>
       </c>
       <c r="B165" t="n">
         <v>78972</v>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488720</v>
+        <v>488808</v>
       </c>
       <c r="R165" t="n">
-        <v>6817985</v>
+        <v>6817936</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125996631</v>
+        <v>125991520</v>
       </c>
       <c r="B166" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,34 +16839,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>489259</v>
+        <v>488720</v>
       </c>
       <c r="R166" t="n">
-        <v>6818066</v>
+        <v>6817985</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17022,48 +17022,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B168" t="n">
-        <v>78972</v>
+        <v>91686</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R168" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,19 +17107,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125994323</v>
+        <v>125995740</v>
       </c>
       <c r="B169" t="n">
         <v>78972</v>
@@ -17150,14 +17150,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>488963</v>
+        <v>489141</v>
       </c>
       <c r="R169" t="n">
-        <v>6817966</v>
+        <v>6818047</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125990421</v>
+        <v>125994323</v>
       </c>
       <c r="B170" t="n">
-        <v>91686</v>
+        <v>78972</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488613</v>
+        <v>488963</v>
       </c>
       <c r="R170" t="n">
-        <v>6818174</v>
+        <v>6817966</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,12 +17301,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996703</v>
+        <v>125994504</v>
       </c>
       <c r="B172" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,34 +17421,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489239</v>
+        <v>488931</v>
       </c>
       <c r="R172" t="n">
-        <v>6818065</v>
+        <v>6818012</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -17507,10 +17507,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996284</v>
+        <v>125996703</v>
       </c>
       <c r="B173" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,21 +17518,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489434</v>
+        <v>489239</v>
       </c>
       <c r="R173" t="n">
-        <v>6818042</v>
+        <v>6818065</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,22 +17592,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125994504</v>
+        <v>125996284</v>
       </c>
       <c r="B174" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17615,37 +17615,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>488931</v>
+        <v>489434</v>
       </c>
       <c r="R174" t="n">
-        <v>6818012</v>
+        <v>6818042</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -17689,12 +17689,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125991445</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488712</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817879</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
         <v>78972</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125993813</v>
+        <v>125992179</v>
       </c>
       <c r="B188" t="n">
         <v>78972</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488933</v>
+        <v>488791</v>
       </c>
       <c r="R188" t="n">
-        <v>6817911</v>
+        <v>6817820</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125992179</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
         <v>78972</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488791</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6817820</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125995420</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489064</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6817976</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,19 +19241,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125996400</v>
+        <v>125995939</v>
       </c>
       <c r="B191" t="n">
         <v>78972</v>
@@ -19288,13 +19288,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>489414</v>
+        <v>489210</v>
       </c>
       <c r="R191" t="n">
-        <v>6818155</v>
+        <v>6818012</v>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19338,19 +19338,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125996428</v>
+        <v>125996400</v>
       </c>
       <c r="B192" t="n">
         <v>78972</v>
@@ -19385,13 +19385,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>489349</v>
+        <v>489414</v>
       </c>
       <c r="R192" t="n">
-        <v>6818082</v>
+        <v>6818155</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -19435,19 +19435,19 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125995939</v>
+        <v>125996428</v>
       </c>
       <c r="B193" t="n">
         <v>78972</v>
@@ -19482,10 +19482,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>489210</v>
+        <v>489349</v>
       </c>
       <c r="R193" t="n">
-        <v>6818012</v>
+        <v>6818082</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125994510</v>
+        <v>125995626</v>
       </c>
       <c r="B194" t="n">
-        <v>96591</v>
+        <v>78972</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,21 +19555,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19579,13 +19579,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>488947</v>
+        <v>489111</v>
       </c>
       <c r="R194" t="n">
-        <v>6818000</v>
+        <v>6817988</v>
       </c>
       <c r="S194" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19629,22 +19629,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125995904</v>
+        <v>125994469</v>
       </c>
       <c r="B195" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>489185</v>
+        <v>488925</v>
       </c>
       <c r="R195" t="n">
-        <v>6818003</v>
+        <v>6817999</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,19 +19726,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995626</v>
+        <v>125995410</v>
       </c>
       <c r="B196" t="n">
         <v>78972</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489111</v>
+        <v>489050</v>
       </c>
       <c r="R196" t="n">
-        <v>6817988</v>
+        <v>6817957</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125994469</v>
+        <v>125994510</v>
       </c>
       <c r="B197" t="n">
-        <v>78972</v>
+        <v>96592</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,21 +19846,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19870,13 +19870,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>488925</v>
+        <v>488947</v>
       </c>
       <c r="R197" t="n">
-        <v>6817999</v>
+        <v>6818000</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995410</v>
+        <v>125995904</v>
       </c>
       <c r="B198" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489050</v>
+        <v>489185</v>
       </c>
       <c r="R198" t="n">
-        <v>6817957</v>
+        <v>6818003</v>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,19 +20017,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125996865</v>
+        <v>125995830</v>
       </c>
       <c r="B199" t="n">
         <v>79004</v>
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489208</v>
+        <v>489169</v>
       </c>
       <c r="R199" t="n">
-        <v>6818043</v>
+        <v>6818007</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125995830</v>
+        <v>125996865</v>
       </c>
       <c r="B201" t="n">
         <v>79004</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489169</v>
+        <v>489208</v>
       </c>
       <c r="R201" t="n">
-        <v>6818007</v>
+        <v>6818043</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996494</v>
+        <v>125996970</v>
       </c>
       <c r="B202" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,10 +20355,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489277</v>
+        <v>489179</v>
       </c>
       <c r="R202" t="n">
-        <v>6818089</v>
+        <v>6818027</v>
       </c>
       <c r="S202" t="n">
         <v>15</v>
@@ -20417,7 +20417,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996970</v>
+        <v>125996240</v>
       </c>
       <c r="B203" t="n">
         <v>78972</v>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489179</v>
+        <v>489466</v>
       </c>
       <c r="R203" t="n">
-        <v>6818027</v>
+        <v>6818007</v>
       </c>
       <c r="S203" t="n">
         <v>15</v>
@@ -20514,10 +20514,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125996240</v>
+        <v>125996494</v>
       </c>
       <c r="B204" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20525,21 +20525,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20549,10 +20549,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>489466</v>
+        <v>489277</v>
       </c>
       <c r="R204" t="n">
-        <v>6818007</v>
+        <v>6818089</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>91197</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728149</v>
+        <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>91197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489154</v>
+        <v>489452</v>
       </c>
       <c r="R13" t="n">
-        <v>6818070</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728124</v>
+        <v>125728164</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489468</v>
+        <v>489432</v>
       </c>
       <c r="R24" t="n">
-        <v>6818461</v>
+        <v>6818370</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728079</v>
+        <v>125728095</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489130</v>
+        <v>489341</v>
       </c>
       <c r="R25" t="n">
-        <v>6817993</v>
+        <v>6818044</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2997,6 +3005,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3023,10 +3036,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728176</v>
+        <v>125728108</v>
       </c>
       <c r="B26" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,34 +3047,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489383</v>
+        <v>489429</v>
       </c>
       <c r="R26" t="n">
-        <v>6818074</v>
+        <v>6818150</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3094,6 +3112,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3120,7 +3143,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728081</v>
+        <v>125728079</v>
       </c>
       <c r="B27" t="n">
         <v>79004</v>
@@ -3155,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489450</v>
+        <v>489130</v>
       </c>
       <c r="R27" t="n">
-        <v>6818184</v>
+        <v>6817993</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728147</v>
+        <v>125728176</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3251,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489255</v>
+        <v>489383</v>
       </c>
       <c r="R28" t="n">
-        <v>6818162</v>
+        <v>6818074</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,10 +3337,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728167</v>
+        <v>125728081</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3325,21 +3348,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3372,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489417</v>
+        <v>489450</v>
       </c>
       <c r="R29" t="n">
-        <v>6818347</v>
+        <v>6818184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3434,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728141</v>
+        <v>125728147</v>
       </c>
       <c r="B30" t="n">
         <v>78972</v>
@@ -3446,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489363</v>
+        <v>489255</v>
       </c>
       <c r="R30" t="n">
-        <v>6818242</v>
+        <v>6818162</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728166</v>
+        <v>125728167</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3543,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489433</v>
+        <v>489417</v>
       </c>
       <c r="R31" t="n">
-        <v>6818362</v>
+        <v>6818347</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,7 +3628,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728164</v>
+        <v>125728141</v>
       </c>
       <c r="B32" t="n">
         <v>78972</v>
@@ -3640,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489432</v>
+        <v>489363</v>
       </c>
       <c r="R32" t="n">
-        <v>6818370</v>
+        <v>6818242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728166</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,42 +3736,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489433</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6818362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3796,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3812,50 +3822,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728108</v>
+        <v>125728124</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489429</v>
+        <v>489468</v>
       </c>
       <c r="R34" t="n">
-        <v>6818150</v>
+        <v>6818461</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3888,11 +3893,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728073</v>
+        <v>125728085</v>
       </c>
       <c r="B49" t="n">
-        <v>79590</v>
+        <v>79004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489392</v>
+        <v>489411</v>
       </c>
       <c r="R49" t="n">
-        <v>6818361</v>
+        <v>6818380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B50" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R50" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728168</v>
+        <v>125728171</v>
       </c>
       <c r="B52" t="n">
         <v>78972</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489413</v>
+        <v>489374</v>
       </c>
       <c r="R52" t="n">
-        <v>6818350</v>
+        <v>6818387</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728171</v>
+        <v>125728168</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489374</v>
+        <v>489413</v>
       </c>
       <c r="R53" t="n">
-        <v>6818387</v>
+        <v>6818350</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728115</v>
+        <v>125728078</v>
       </c>
       <c r="B63" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489204</v>
+        <v>489352</v>
       </c>
       <c r="R63" t="n">
-        <v>6818104</v>
+        <v>6818362</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>79004</v>
+        <v>78731</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -14296,10 +14296,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125994090</v>
+        <v>125995990</v>
       </c>
       <c r="B140" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14307,34 +14307,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>488989</v>
+        <v>489201</v>
       </c>
       <c r="R140" t="n">
-        <v>6817941</v>
+        <v>6818003</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,7 +14393,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125995142</v>
+        <v>125994090</v>
       </c>
       <c r="B141" t="n">
         <v>78972</v>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489041</v>
+        <v>488989</v>
       </c>
       <c r="R141" t="n">
-        <v>6817951</v>
+        <v>6817941</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,22 +14478,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995990</v>
+        <v>125995142</v>
       </c>
       <c r="B142" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489201</v>
+        <v>489041</v>
       </c>
       <c r="R142" t="n">
-        <v>6818003</v>
+        <v>6817951</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B148" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R148" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125996237</v>
+        <v>125995957</v>
       </c>
       <c r="B149" t="n">
-        <v>79004</v>
+        <v>57811</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,21 +15185,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15209,10 +15209,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489427</v>
+        <v>489236</v>
       </c>
       <c r="R149" t="n">
-        <v>6818004</v>
+        <v>6817991</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15247,6 +15247,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15259,22 +15264,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125995957</v>
+        <v>125993318</v>
       </c>
       <c r="B150" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15282,34 +15287,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>489236</v>
+        <v>488825</v>
       </c>
       <c r="R150" t="n">
-        <v>6817991</v>
+        <v>6817957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15344,11 +15349,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Fyra individer.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15361,12 +15361,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125996631</v>
+        <v>125991267</v>
       </c>
       <c r="B162" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,37 +16451,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>489259</v>
+        <v>488729</v>
       </c>
       <c r="R162" t="n">
-        <v>6818066</v>
+        <v>6817882</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16525,19 +16525,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125991267</v>
+        <v>125996410</v>
       </c>
       <c r="B163" t="n">
         <v>78972</v>
@@ -16568,17 +16568,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>488729</v>
+        <v>489371</v>
       </c>
       <c r="R163" t="n">
-        <v>6817882</v>
+        <v>6818137</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125996410</v>
+        <v>125992967</v>
       </c>
       <c r="B164" t="n">
         <v>78972</v>
@@ -16665,14 +16665,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>489371</v>
+        <v>488808</v>
       </c>
       <c r="R164" t="n">
-        <v>6818137</v>
+        <v>6817936</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125992967</v>
+        <v>125991520</v>
       </c>
       <c r="B165" t="n">
         <v>78972</v>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488808</v>
+        <v>488720</v>
       </c>
       <c r="R165" t="n">
-        <v>6817936</v>
+        <v>6817985</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125991520</v>
+        <v>125996631</v>
       </c>
       <c r="B166" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,34 +16839,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488720</v>
+        <v>489259</v>
       </c>
       <c r="R166" t="n">
-        <v>6817985</v>
+        <v>6818066</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125994504</v>
+        <v>125996284</v>
       </c>
       <c r="B172" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,37 +17421,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>488931</v>
+        <v>489434</v>
       </c>
       <c r="R172" t="n">
-        <v>6818012</v>
+        <v>6818042</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,12 +17495,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
@@ -17604,10 +17604,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125996284</v>
+        <v>125994504</v>
       </c>
       <c r="B174" t="n">
-        <v>79004</v>
+        <v>78731</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17615,37 +17615,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>489434</v>
+        <v>488931</v>
       </c>
       <c r="R174" t="n">
-        <v>6818042</v>
+        <v>6818012</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -17689,12 +17689,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B186" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B187" t="n">
         <v>78972</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125993813</v>
       </c>
       <c r="B188" t="n">
         <v>78972</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>488933</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6817911</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125992179</v>
       </c>
       <c r="B189" t="n">
         <v>78972</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>488791</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6817820</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125995420</v>
       </c>
       <c r="B190" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>489064</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6817976</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728150</v>
+        <v>125728137</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489356</v>
+        <v>489352</v>
       </c>
       <c r="R4" t="n">
-        <v>6818016</v>
+        <v>6818366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728101</v>
+        <v>125728174</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489357</v>
+        <v>489338</v>
       </c>
       <c r="R5" t="n">
-        <v>6818163</v>
+        <v>6818397</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728137</v>
+        <v>125728120</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489352</v>
+        <v>489345</v>
       </c>
       <c r="R6" t="n">
-        <v>6818366</v>
+        <v>6818246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728174</v>
+        <v>125728121</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489338</v>
+        <v>489306</v>
       </c>
       <c r="R7" t="n">
-        <v>6818397</v>
+        <v>6818055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728120</v>
+        <v>125728110</v>
       </c>
       <c r="B8" t="n">
-        <v>80111</v>
+        <v>92714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489345</v>
+        <v>489380</v>
       </c>
       <c r="R8" t="n">
-        <v>6818246</v>
+        <v>6818374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728121</v>
+        <v>125728150</v>
       </c>
       <c r="B9" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489306</v>
+        <v>489356</v>
       </c>
       <c r="R9" t="n">
-        <v>6818055</v>
+        <v>6818016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728110</v>
+        <v>125728101</v>
       </c>
       <c r="B10" t="n">
-        <v>92714</v>
+        <v>57648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1462,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489380</v>
+        <v>489357</v>
       </c>
       <c r="R10" t="n">
-        <v>6818374</v>
+        <v>6818163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728091</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489452</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B13" t="n">
-        <v>91197</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728157</v>
+        <v>125728069</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489452</v>
+        <v>489204</v>
       </c>
       <c r="R15" t="n">
-        <v>6818179</v>
+        <v>6818104</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728169</v>
+        <v>125728068</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489407</v>
+        <v>489219</v>
       </c>
       <c r="R16" t="n">
-        <v>6818356</v>
+        <v>6818134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728135</v>
+        <v>125728146</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489219</v>
+        <v>489261</v>
       </c>
       <c r="R17" t="n">
-        <v>6818132</v>
+        <v>6818155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728146</v>
+        <v>125728155</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2277,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489261</v>
+        <v>489417</v>
       </c>
       <c r="R18" t="n">
-        <v>6818155</v>
+        <v>6818154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728155</v>
+        <v>125728161</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489417</v>
+        <v>489439</v>
       </c>
       <c r="R19" t="n">
-        <v>6818154</v>
+        <v>6818361</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,45 +2431,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728161</v>
+        <v>125728111</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489439</v>
+        <v>489223</v>
       </c>
       <c r="R20" t="n">
-        <v>6818361</v>
+        <v>6818133</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728069</v>
+        <v>125728157</v>
       </c>
       <c r="B21" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489204</v>
+        <v>489452</v>
       </c>
       <c r="R21" t="n">
-        <v>6818104</v>
+        <v>6818179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728068</v>
+        <v>125728169</v>
       </c>
       <c r="B22" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489219</v>
+        <v>489407</v>
       </c>
       <c r="R22" t="n">
-        <v>6818134</v>
+        <v>6818356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,50 +2727,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728111</v>
+        <v>125728135</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489223</v>
+        <v>489219</v>
       </c>
       <c r="R23" t="n">
-        <v>6818133</v>
+        <v>6818132</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2803,6 +2798,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728164</v>
+        <v>125728124</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489432</v>
+        <v>489468</v>
       </c>
       <c r="R24" t="n">
-        <v>6818370</v>
+        <v>6818461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728095</v>
+        <v>125728079</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489341</v>
+        <v>489130</v>
       </c>
       <c r="R25" t="n">
-        <v>6818044</v>
+        <v>6817993</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,11 +2997,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3036,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728108</v>
+        <v>125728176</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3047,39 +3034,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489429</v>
+        <v>489383</v>
       </c>
       <c r="R26" t="n">
-        <v>6818150</v>
+        <v>6818074</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3112,11 +3094,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3143,7 +3120,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728079</v>
+        <v>125728081</v>
       </c>
       <c r="B27" t="n">
         <v>79004</v>
@@ -3178,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489130</v>
+        <v>489450</v>
       </c>
       <c r="R27" t="n">
-        <v>6817993</v>
+        <v>6818184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3240,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728176</v>
+        <v>125728147</v>
       </c>
       <c r="B28" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489383</v>
+        <v>489255</v>
       </c>
       <c r="R28" t="n">
-        <v>6818074</v>
+        <v>6818162</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728081</v>
+        <v>125728167</v>
       </c>
       <c r="B29" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3348,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3372,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489450</v>
+        <v>489417</v>
       </c>
       <c r="R29" t="n">
-        <v>6818184</v>
+        <v>6818347</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3411,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728147</v>
+        <v>125728141</v>
       </c>
       <c r="B30" t="n">
         <v>78972</v>
@@ -3469,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489255</v>
+        <v>489363</v>
       </c>
       <c r="R30" t="n">
-        <v>6818162</v>
+        <v>6818242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3531,7 +3508,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728167</v>
+        <v>125728166</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3566,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489417</v>
+        <v>489433</v>
       </c>
       <c r="R31" t="n">
-        <v>6818347</v>
+        <v>6818362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,7 +3605,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728141</v>
+        <v>125728164</v>
       </c>
       <c r="B32" t="n">
         <v>78972</v>
@@ -3663,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489363</v>
+        <v>489432</v>
       </c>
       <c r="R32" t="n">
-        <v>6818242</v>
+        <v>6818370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728166</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,34 +3713,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489433</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818362</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,6 +3781,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3822,45 +3812,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728124</v>
+        <v>125728108</v>
       </c>
       <c r="B34" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489468</v>
+        <v>489429</v>
       </c>
       <c r="R34" t="n">
-        <v>6818461</v>
+        <v>6818150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,6 +3888,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4016,45 +4016,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728103</v>
+        <v>125728181</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>5176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489344</v>
+        <v>489399</v>
       </c>
       <c r="R36" t="n">
-        <v>6818246</v>
+        <v>6818343</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,7 +4118,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728104</v>
+        <v>125728103</v>
       </c>
       <c r="B37" t="n">
         <v>80076</v>
@@ -4148,10 +4153,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489262</v>
+        <v>489344</v>
       </c>
       <c r="R37" t="n">
-        <v>6818043</v>
+        <v>6818246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4210,50 +4215,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728181</v>
+        <v>125728104</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489399</v>
+        <v>489262</v>
       </c>
       <c r="R38" t="n">
-        <v>6818343</v>
+        <v>6818043</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>79590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R49" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728073</v>
+        <v>125728085</v>
       </c>
       <c r="B50" t="n">
-        <v>79590</v>
+        <v>79004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489392</v>
+        <v>489411</v>
       </c>
       <c r="R50" t="n">
-        <v>6818361</v>
+        <v>6818380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728171</v>
+        <v>125728168</v>
       </c>
       <c r="B52" t="n">
         <v>78972</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489374</v>
+        <v>489413</v>
       </c>
       <c r="R52" t="n">
-        <v>6818387</v>
+        <v>6818350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728168</v>
+        <v>125728171</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489413</v>
+        <v>489374</v>
       </c>
       <c r="R53" t="n">
-        <v>6818350</v>
+        <v>6818387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B63" t="n">
-        <v>79004</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R63" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728115</v>
+        <v>125728078</v>
       </c>
       <c r="B66" t="n">
-        <v>78731</v>
+        <v>79004</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489204</v>
+        <v>489352</v>
       </c>
       <c r="R66" t="n">
-        <v>6818104</v>
+        <v>6818362</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B70" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R70" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728133</v>
+        <v>125728142</v>
       </c>
       <c r="B71" t="n">
         <v>78972</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489386</v>
+        <v>489363</v>
       </c>
       <c r="R71" t="n">
-        <v>6818081</v>
+        <v>6818235</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,11 +7506,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7537,7 +7532,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728160</v>
+        <v>125728162</v>
       </c>
       <c r="B72" t="n">
         <v>78972</v>
@@ -7572,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489463</v>
+        <v>489460</v>
       </c>
       <c r="R72" t="n">
-        <v>6818278</v>
+        <v>6818444</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7634,10 +7629,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728142</v>
+        <v>125728114</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7645,21 +7640,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7669,10 +7664,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489363</v>
+        <v>489364</v>
       </c>
       <c r="R73" t="n">
-        <v>6818235</v>
+        <v>6818169</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7731,7 +7726,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728162</v>
+        <v>125728133</v>
       </c>
       <c r="B74" t="n">
         <v>78972</v>
@@ -7766,10 +7761,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489460</v>
+        <v>489386</v>
       </c>
       <c r="R74" t="n">
-        <v>6818444</v>
+        <v>6818081</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7802,6 +7797,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8609,32 +8609,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728099</v>
+        <v>125728117</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489306</v>
+        <v>489409</v>
       </c>
       <c r="R83" t="n">
-        <v>6818056</v>
+        <v>6818054</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728077</v>
+        <v>125728099</v>
       </c>
       <c r="B84" t="n">
-        <v>75067</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489458</v>
+        <v>489306</v>
       </c>
       <c r="R84" t="n">
-        <v>6818455</v>
+        <v>6818056</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728077</v>
       </c>
       <c r="B85" t="n">
-        <v>80075</v>
+        <v>75067</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489458</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818455</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728102</v>
+        <v>125728125</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489338</v>
+        <v>489320</v>
       </c>
       <c r="R86" t="n">
-        <v>6818240</v>
+        <v>6818042</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728117</v>
+        <v>125728102</v>
       </c>
       <c r="B87" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489409</v>
+        <v>489338</v>
       </c>
       <c r="R87" t="n">
-        <v>6818054</v>
+        <v>6818240</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728139</v>
+        <v>125728127</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489360</v>
+        <v>489267</v>
       </c>
       <c r="R99" t="n">
-        <v>6818301</v>
+        <v>6818149</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728127</v>
+        <v>125728129</v>
       </c>
       <c r="B100" t="n">
-        <v>78730</v>
+        <v>91853</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>5454</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489267</v>
+        <v>489370</v>
       </c>
       <c r="R100" t="n">
-        <v>6818149</v>
+        <v>6818176</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728129</v>
+        <v>125728139</v>
       </c>
       <c r="B101" t="n">
-        <v>91853</v>
+        <v>78972</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10376,21 +10376,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489370</v>
+        <v>489360</v>
       </c>
       <c r="R101" t="n">
-        <v>6818176</v>
+        <v>6818301</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11650,38 +11650,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125723678</v>
+        <v>125722694</v>
       </c>
       <c r="B114" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R114" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,6 +11726,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11752,38 +11757,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125722694</v>
+        <v>125723678</v>
       </c>
       <c r="B115" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11792,10 +11797,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R115" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11828,11 +11833,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14296,10 +14296,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125995990</v>
+        <v>125994090</v>
       </c>
       <c r="B140" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14307,34 +14307,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489201</v>
+        <v>488989</v>
       </c>
       <c r="R140" t="n">
-        <v>6818003</v>
+        <v>6817941</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,7 +14393,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125994090</v>
+        <v>125995142</v>
       </c>
       <c r="B141" t="n">
         <v>78972</v>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>488989</v>
+        <v>489041</v>
       </c>
       <c r="R141" t="n">
-        <v>6817941</v>
+        <v>6817951</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,22 +14478,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995142</v>
+        <v>125995990</v>
       </c>
       <c r="B142" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489041</v>
+        <v>489201</v>
       </c>
       <c r="R142" t="n">
-        <v>6817951</v>
+        <v>6818003</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -17022,48 +17022,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125990421</v>
+        <v>125995740</v>
       </c>
       <c r="B168" t="n">
-        <v>91686</v>
+        <v>78972</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>488613</v>
+        <v>489141</v>
       </c>
       <c r="R168" t="n">
-        <v>6818174</v>
+        <v>6818047</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,19 +17107,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995740</v>
+        <v>125994323</v>
       </c>
       <c r="B169" t="n">
         <v>78972</v>
@@ -17150,14 +17150,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489141</v>
+        <v>488963</v>
       </c>
       <c r="R169" t="n">
-        <v>6818047</v>
+        <v>6817966</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125994323</v>
+        <v>125990421</v>
       </c>
       <c r="B170" t="n">
-        <v>78972</v>
+        <v>91686</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488963</v>
+        <v>488613</v>
       </c>
       <c r="R170" t="n">
-        <v>6817966</v>
+        <v>6818174</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,12 +17301,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125991445</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488712</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817879</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
         <v>78972</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125993813</v>
+        <v>125992179</v>
       </c>
       <c r="B188" t="n">
         <v>78972</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488933</v>
+        <v>488791</v>
       </c>
       <c r="R188" t="n">
-        <v>6817911</v>
+        <v>6817820</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125992179</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
         <v>78972</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488791</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6817820</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125995420</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489064</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6817976</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125728080</v>
       </c>
       <c r="B2" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125728083</v>
       </c>
       <c r="B3" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728137</v>
+        <v>125728112</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489352</v>
+        <v>489161</v>
       </c>
       <c r="R4" t="n">
-        <v>6818366</v>
+        <v>6817982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728174</v>
+        <v>125728120</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489338</v>
+        <v>489345</v>
       </c>
       <c r="R5" t="n">
-        <v>6818397</v>
+        <v>6818246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728120</v>
+        <v>125728121</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489345</v>
+        <v>489306</v>
       </c>
       <c r="R6" t="n">
-        <v>6818246</v>
+        <v>6818055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728121</v>
+        <v>125728137</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489306</v>
+        <v>489352</v>
       </c>
       <c r="R7" t="n">
-        <v>6818055</v>
+        <v>6818366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728110</v>
+        <v>125728174</v>
       </c>
       <c r="B8" t="n">
-        <v>92714</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489380</v>
+        <v>489338</v>
       </c>
       <c r="R8" t="n">
-        <v>6818374</v>
+        <v>6818397</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728150</v>
+        <v>125728101</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1370,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489356</v>
+        <v>489357</v>
       </c>
       <c r="R9" t="n">
-        <v>6818016</v>
+        <v>6818163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728101</v>
+        <v>125728110</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
+        <v>92716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,39 +1472,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489357</v>
+        <v>489380</v>
       </c>
       <c r="R10" t="n">
-        <v>6818163</v>
+        <v>6818374</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,50 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728112</v>
+        <v>125728150</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489161</v>
+        <v>489356</v>
       </c>
       <c r="R11" t="n">
-        <v>6817982</v>
+        <v>6818016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>91197</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728149</v>
+        <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>91199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489154</v>
+        <v>489452</v>
       </c>
       <c r="R13" t="n">
-        <v>6818070</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>125728069</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>125728068</v>
       </c>
       <c r="B16" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728146</v>
+        <v>125728169</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489261</v>
+        <v>489407</v>
       </c>
       <c r="R17" t="n">
-        <v>6818155</v>
+        <v>6818356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,7 +2240,7 @@
         <v>125728155</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728161</v>
+        <v>125728146</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489439</v>
+        <v>489261</v>
       </c>
       <c r="R19" t="n">
-        <v>6818361</v>
+        <v>6818155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,50 +2431,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728111</v>
+        <v>125728161</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489223</v>
+        <v>489439</v>
       </c>
       <c r="R20" t="n">
-        <v>6818133</v>
+        <v>6818361</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,45 +2528,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728157</v>
+        <v>125728111</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489452</v>
+        <v>489223</v>
       </c>
       <c r="R21" t="n">
-        <v>6818179</v>
+        <v>6818133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728169</v>
+        <v>125728157</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489407</v>
+        <v>489452</v>
       </c>
       <c r="R22" t="n">
-        <v>6818356</v>
+        <v>6818179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>125728135</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,45 +2829,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728124</v>
+        <v>125728095</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489468</v>
+        <v>489341</v>
       </c>
       <c r="R24" t="n">
-        <v>6818461</v>
+        <v>6818044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2900,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2929,7 +2942,7 @@
         <v>125728079</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3039,7 @@
         <v>125728176</v>
       </c>
       <c r="B26" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,7 +3136,7 @@
         <v>125728081</v>
       </c>
       <c r="B27" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3217,32 +3230,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728147</v>
+        <v>125728124</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489255</v>
+        <v>489468</v>
       </c>
       <c r="R28" t="n">
-        <v>6818162</v>
+        <v>6818461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3317,7 +3330,7 @@
         <v>125728167</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3411,10 +3424,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728141</v>
+        <v>125728164</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3446,10 +3459,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489363</v>
+        <v>489432</v>
       </c>
       <c r="R30" t="n">
-        <v>6818242</v>
+        <v>6818370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3521,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728166</v>
+        <v>125728141</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3543,10 +3556,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489433</v>
+        <v>489363</v>
       </c>
       <c r="R31" t="n">
-        <v>6818362</v>
+        <v>6818242</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3618,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728164</v>
+        <v>125728147</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3640,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489432</v>
+        <v>489255</v>
       </c>
       <c r="R32" t="n">
-        <v>6818370</v>
+        <v>6818162</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,10 +3715,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728166</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,42 +3726,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489433</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6818362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3786,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3815,7 +3815,7 @@
         <v>125728108</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>125728082</v>
       </c>
       <c r="B35" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,50 +4016,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728181</v>
+        <v>125728103</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>80077</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489399</v>
+        <v>489344</v>
       </c>
       <c r="R36" t="n">
-        <v>6818343</v>
+        <v>6818246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728103</v>
+        <v>125728104</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4153,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489344</v>
+        <v>489262</v>
       </c>
       <c r="R37" t="n">
-        <v>6818246</v>
+        <v>6818043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,45 +4210,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728104</v>
+        <v>125728181</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489262</v>
+        <v>489399</v>
       </c>
       <c r="R38" t="n">
-        <v>6818043</v>
+        <v>6818343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728089</v>
+        <v>125728119</v>
       </c>
       <c r="B39" t="n">
-        <v>96592</v>
+        <v>78732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489455</v>
+        <v>489446</v>
       </c>
       <c r="R39" t="n">
-        <v>6818449</v>
+        <v>6818191</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728178</v>
+        <v>125728089</v>
       </c>
       <c r="B40" t="n">
-        <v>78639</v>
+        <v>96594</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489394</v>
+        <v>489455</v>
       </c>
       <c r="R40" t="n">
-        <v>6818362</v>
+        <v>6818449</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728134</v>
+        <v>125728178</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489318</v>
+        <v>489394</v>
       </c>
       <c r="R41" t="n">
-        <v>6818135</v>
+        <v>6818362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4577,11 +4577,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4608,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728119</v>
+        <v>125728134</v>
       </c>
       <c r="B42" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489446</v>
+        <v>489318</v>
       </c>
       <c r="R42" t="n">
-        <v>6818191</v>
+        <v>6818135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4674,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728154</v>
+        <v>125728159</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489424</v>
+        <v>489463</v>
       </c>
       <c r="R43" t="n">
-        <v>6818132</v>
+        <v>6818200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728071</v>
+        <v>125728156</v>
       </c>
       <c r="B44" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489452</v>
+        <v>489450</v>
       </c>
       <c r="R44" t="n">
-        <v>6818185</v>
+        <v>6818159</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728072</v>
+        <v>125728071</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489446</v>
+        <v>489452</v>
       </c>
       <c r="R45" t="n">
-        <v>6818191</v>
+        <v>6818185</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728156</v>
+        <v>125728072</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489450</v>
+        <v>489446</v>
       </c>
       <c r="R46" t="n">
-        <v>6818159</v>
+        <v>6818191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728159</v>
+        <v>125728180</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,34 +5104,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489463</v>
+        <v>489407</v>
       </c>
       <c r="R47" t="n">
-        <v>6818200</v>
+        <v>6818050</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5164,6 +5168,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5190,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728180</v>
+        <v>125728154</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5201,38 +5210,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489407</v>
+        <v>489424</v>
       </c>
       <c r="R48" t="n">
-        <v>6818050</v>
+        <v>6818132</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5265,11 +5270,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728073</v>
+        <v>125728085</v>
       </c>
       <c r="B49" t="n">
-        <v>79590</v>
+        <v>79005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489392</v>
+        <v>489411</v>
       </c>
       <c r="R49" t="n">
-        <v>6818361</v>
+        <v>6818380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B50" t="n">
-        <v>79004</v>
+        <v>79591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R50" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728158</v>
+        <v>125728171</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489449</v>
+        <v>489374</v>
       </c>
       <c r="R51" t="n">
-        <v>6818184</v>
+        <v>6818387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5590,7 +5590,7 @@
         <v>125728168</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728171</v>
+        <v>125728075</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>91156</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489374</v>
+        <v>489292</v>
       </c>
       <c r="R53" t="n">
-        <v>6818387</v>
+        <v>6818151</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728075</v>
+        <v>125728158</v>
       </c>
       <c r="B54" t="n">
-        <v>91154</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489292</v>
+        <v>489449</v>
       </c>
       <c r="R54" t="n">
-        <v>6818151</v>
+        <v>6818184</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728086</v>
+        <v>125728109</v>
       </c>
       <c r="B55" t="n">
-        <v>79004</v>
+        <v>97219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489365</v>
+        <v>489452</v>
       </c>
       <c r="R55" t="n">
-        <v>6818390</v>
+        <v>6818415</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728088</v>
+        <v>125728086</v>
       </c>
       <c r="B56" t="n">
-        <v>96592</v>
+        <v>79005</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489442</v>
+        <v>489365</v>
       </c>
       <c r="R56" t="n">
-        <v>6818350</v>
+        <v>6818390</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728163</v>
+        <v>125728088</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>96594</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489456</v>
+        <v>489442</v>
       </c>
       <c r="R57" t="n">
-        <v>6818471</v>
+        <v>6818350</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
         <v>125728165</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728109</v>
+        <v>125728163</v>
       </c>
       <c r="B59" t="n">
-        <v>97217</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489452</v>
+        <v>489456</v>
       </c>
       <c r="R59" t="n">
-        <v>6818415</v>
+        <v>6818471</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6366,7 +6366,7 @@
         <v>125728118</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125728170</v>
+        <v>125728144</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489395</v>
+        <v>489370</v>
       </c>
       <c r="R61" t="n">
-        <v>6818361</v>
+        <v>6818176</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125728144</v>
+        <v>125728170</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489370</v>
+        <v>489395</v>
       </c>
       <c r="R62" t="n">
-        <v>6818176</v>
+        <v>6818361</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728115</v>
+        <v>125728078</v>
       </c>
       <c r="B63" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489204</v>
+        <v>489352</v>
       </c>
       <c r="R63" t="n">
-        <v>6818104</v>
+        <v>6818362</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R64" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6822,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6848,10 +6853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728136</v>
+        <v>125728153</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489467</v>
+        <v>489420</v>
       </c>
       <c r="R65" t="n">
-        <v>6818200</v>
+        <v>6818126</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,11 +6924,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>79004</v>
+        <v>78732</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B67" t="n">
-        <v>91246</v>
+        <v>79005</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R67" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728084</v>
+        <v>125728151</v>
       </c>
       <c r="B68" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489414</v>
+        <v>489396</v>
       </c>
       <c r="R68" t="n">
-        <v>6818350</v>
+        <v>6818028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728151</v>
+        <v>125728130</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>91248</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489396</v>
+        <v>489444</v>
       </c>
       <c r="R69" t="n">
-        <v>6818028</v>
+        <v>6818412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728160</v>
+        <v>125728142</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489463</v>
+        <v>489363</v>
       </c>
       <c r="R70" t="n">
-        <v>6818278</v>
+        <v>6818235</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728142</v>
+        <v>125728162</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489363</v>
+        <v>489460</v>
       </c>
       <c r="R71" t="n">
-        <v>6818235</v>
+        <v>6818444</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728162</v>
+        <v>125728133</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489460</v>
+        <v>489386</v>
       </c>
       <c r="R72" t="n">
-        <v>6818444</v>
+        <v>6818081</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,6 +7603,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7629,10 +7634,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7640,21 +7645,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7664,10 +7669,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R73" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7726,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728133</v>
+        <v>125728114</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7737,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7761,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489386</v>
+        <v>489364</v>
       </c>
       <c r="R74" t="n">
-        <v>6818081</v>
+        <v>6818169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,11 +7802,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7828,32 +7828,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728140</v>
+        <v>125728098</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>80105</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489337</v>
+        <v>489262</v>
       </c>
       <c r="R75" t="n">
-        <v>6818236</v>
+        <v>6818039</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,32 +7925,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728145</v>
+        <v>125728097</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>80105</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489365</v>
+        <v>489345</v>
       </c>
       <c r="R76" t="n">
-        <v>6818143</v>
+        <v>6818245</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,32 +8022,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728098</v>
+        <v>125728140</v>
       </c>
       <c r="B77" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489262</v>
+        <v>489337</v>
       </c>
       <c r="R77" t="n">
-        <v>6818039</v>
+        <v>6818236</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,45 +8119,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728097</v>
+        <v>125728100</v>
       </c>
       <c r="B78" t="n">
-        <v>80104</v>
+        <v>57649</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489345</v>
+        <v>489327</v>
       </c>
       <c r="R78" t="n">
-        <v>6818245</v>
+        <v>6818047</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8216,32 +8221,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728179</v>
+        <v>125728145</v>
       </c>
       <c r="B79" t="n">
-        <v>95191</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2383</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489412</v>
+        <v>489365</v>
       </c>
       <c r="R79" t="n">
-        <v>6818351</v>
+        <v>6818143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8313,50 +8318,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728100</v>
+        <v>125728179</v>
       </c>
       <c r="B80" t="n">
-        <v>57648</v>
+        <v>95193</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>2383</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489327</v>
+        <v>489412</v>
       </c>
       <c r="R80" t="n">
-        <v>6818047</v>
+        <v>6818351</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
         <v>125728123</v>
       </c>
       <c r="B81" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125728148</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>125728117</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>125728099</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728077</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>75067</v>
+        <v>80076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489458</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818455</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728125</v>
+        <v>125728077</v>
       </c>
       <c r="B86" t="n">
-        <v>80075</v>
+        <v>75068</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489320</v>
+        <v>489458</v>
       </c>
       <c r="R86" t="n">
-        <v>6818042</v>
+        <v>6818455</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9000,7 +9000,7 @@
         <v>125728102</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728105</v>
+        <v>125728152</v>
       </c>
       <c r="B88" t="n">
-        <v>79979</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489306</v>
+        <v>489415</v>
       </c>
       <c r="R88" t="n">
-        <v>6818062</v>
+        <v>6818087</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9194,7 +9194,7 @@
         <v>125728094</v>
       </c>
       <c r="B89" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728152</v>
+        <v>125728087</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489415</v>
+        <v>489343</v>
       </c>
       <c r="R90" t="n">
-        <v>6818087</v>
+        <v>6818374</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9385,50 +9385,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728107</v>
+        <v>125728105</v>
       </c>
       <c r="B91" t="n">
-        <v>57651</v>
+        <v>79980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489359</v>
+        <v>489306</v>
       </c>
       <c r="R91" t="n">
-        <v>6818332</v>
+        <v>6818062</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9461,11 +9456,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9492,10 +9482,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728087</v>
+        <v>125728107</v>
       </c>
       <c r="B92" t="n">
-        <v>79004</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9503,34 +9493,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489343</v>
+        <v>489359</v>
       </c>
       <c r="R92" t="n">
-        <v>6818374</v>
+        <v>6818332</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9563,6 +9558,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728177</v>
+        <v>125728070</v>
       </c>
       <c r="B93" t="n">
-        <v>78639</v>
+        <v>79591</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489452</v>
+        <v>489185</v>
       </c>
       <c r="R93" t="n">
-        <v>6818167</v>
+        <v>6818091</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728070</v>
+        <v>125728177</v>
       </c>
       <c r="B94" t="n">
-        <v>79590</v>
+        <v>78640</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489185</v>
+        <v>489452</v>
       </c>
       <c r="R94" t="n">
-        <v>6818091</v>
+        <v>6818167</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9786,7 +9786,7 @@
         <v>125728126</v>
       </c>
       <c r="B95" t="n">
-        <v>91598</v>
+        <v>91600</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9880,32 +9880,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728090</v>
+        <v>125728116</v>
       </c>
       <c r="B96" t="n">
-        <v>91197</v>
+        <v>78732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489418</v>
+        <v>489187</v>
       </c>
       <c r="R96" t="n">
-        <v>6818094</v>
+        <v>6818091</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,10 +9977,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728116</v>
+        <v>125728143</v>
       </c>
       <c r="B97" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9988,21 +9988,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489187</v>
+        <v>489366</v>
       </c>
       <c r="R97" t="n">
-        <v>6818091</v>
+        <v>6818215</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10074,32 +10074,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728143</v>
+        <v>125728090</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>91199</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489366</v>
+        <v>489418</v>
       </c>
       <c r="R98" t="n">
-        <v>6818215</v>
+        <v>6818094</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728127</v>
+        <v>125728172</v>
       </c>
       <c r="B99" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489267</v>
+        <v>489366</v>
       </c>
       <c r="R99" t="n">
-        <v>6818149</v>
+        <v>6818389</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
         <v>125728129</v>
       </c>
       <c r="B100" t="n">
-        <v>91853</v>
+        <v>91855</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728139</v>
+        <v>125728173</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489360</v>
+        <v>489340</v>
       </c>
       <c r="R101" t="n">
-        <v>6818301</v>
+        <v>6818386</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728173</v>
+        <v>125728127</v>
       </c>
       <c r="B102" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10473,21 +10473,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489340</v>
+        <v>489267</v>
       </c>
       <c r="R102" t="n">
-        <v>6818386</v>
+        <v>6818149</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728172</v>
+        <v>125728139</v>
       </c>
       <c r="B103" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489366</v>
+        <v>489360</v>
       </c>
       <c r="R103" t="n">
-        <v>6818389</v>
+        <v>6818301</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>125724254</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11063,10 +11063,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125723877</v>
+        <v>125723347</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>125724786</v>
       </c>
       <c r="B110" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>125722589</v>
       </c>
       <c r="B111" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>125723050</v>
       </c>
       <c r="B112" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11548,10 +11548,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125723419</v>
+        <v>125722694</v>
       </c>
       <c r="B113" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R113" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11624,6 +11624,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11650,38 +11655,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125722694</v>
+        <v>125723678</v>
       </c>
       <c r="B114" t="n">
-        <v>57651</v>
+        <v>56844</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -11690,10 +11695,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R114" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,11 +11731,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11757,38 +11757,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125723678</v>
+        <v>125723419</v>
       </c>
       <c r="B115" t="n">
-        <v>56843</v>
+        <v>57652</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11862,7 +11862,7 @@
         <v>125723960</v>
       </c>
       <c r="B116" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>125725272</v>
       </c>
       <c r="B117" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>125724536</v>
       </c>
       <c r="B118" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>125725082</v>
       </c>
       <c r="B119" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12252,45 +12252,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B120" t="n">
-        <v>78972</v>
+        <v>57474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R120" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12349,50 +12354,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B121" t="n">
-        <v>57473</v>
+        <v>78973</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R121" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125869096</v>
       </c>
       <c r="B124" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>125869097</v>
       </c>
       <c r="B125" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125869112</v>
+        <v>125869115</v>
       </c>
       <c r="B131" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489429</v>
+        <v>489123</v>
       </c>
       <c r="R131" t="n">
-        <v>6818389</v>
+        <v>6817993</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125869115</v>
+        <v>125869112</v>
       </c>
       <c r="B132" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13537,10 +13537,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>489123</v>
+        <v>489429</v>
       </c>
       <c r="R132" t="n">
-        <v>6817993</v>
+        <v>6818389</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996241</v>
+        <v>125996409</v>
       </c>
       <c r="B135" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13846,13 +13846,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489437</v>
+        <v>489377</v>
       </c>
       <c r="R135" t="n">
-        <v>6818032</v>
+        <v>6818145</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,60 +13896,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125995667</v>
+        <v>125996241</v>
       </c>
       <c r="B136" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489117</v>
+        <v>489437</v>
       </c>
       <c r="R136" t="n">
-        <v>6818011</v>
+        <v>6818032</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125996346</v>
+        <v>125994090</v>
       </c>
       <c r="B138" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>489439</v>
+        <v>488989</v>
       </c>
       <c r="R138" t="n">
-        <v>6818061</v>
+        <v>6817941</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,10 +14199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125996407</v>
+        <v>125995142</v>
       </c>
       <c r="B139" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,37 +14210,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489391</v>
+        <v>489041</v>
       </c>
       <c r="R139" t="n">
-        <v>6818133</v>
+        <v>6817951</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14284,22 +14284,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125994090</v>
+        <v>125996346</v>
       </c>
       <c r="B140" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14307,34 +14307,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>488989</v>
+        <v>489439</v>
       </c>
       <c r="R140" t="n">
-        <v>6817941</v>
+        <v>6818061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125995142</v>
+        <v>125996407</v>
       </c>
       <c r="B141" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,37 +14404,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489041</v>
+        <v>489391</v>
       </c>
       <c r="R141" t="n">
-        <v>6817951</v>
+        <v>6818133</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,12 +14478,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
         <v>125995990</v>
       </c>
       <c r="B142" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14587,10 +14587,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125994790</v>
+        <v>125993983</v>
       </c>
       <c r="B143" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14598,21 +14598,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>488932</v>
+        <v>488964</v>
       </c>
       <c r="R143" t="n">
-        <v>6818043</v>
+        <v>6817921</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14658,6 +14658,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14684,10 +14689,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125993642</v>
+        <v>125994790</v>
       </c>
       <c r="B144" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14719,10 +14724,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>488965</v>
+        <v>488932</v>
       </c>
       <c r="R144" t="n">
-        <v>6817938</v>
+        <v>6818043</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14781,10 +14786,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125993983</v>
+        <v>125993642</v>
       </c>
       <c r="B145" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14792,21 +14797,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14816,10 +14821,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>488964</v>
+        <v>488965</v>
       </c>
       <c r="R145" t="n">
-        <v>6817921</v>
+        <v>6817938</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -14852,11 +14857,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14886,7 +14886,7 @@
         <v>125996446</v>
       </c>
       <c r="B146" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>125996662</v>
       </c>
       <c r="B147" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B148" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R148" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125995957</v>
+        <v>125996237</v>
       </c>
       <c r="B149" t="n">
-        <v>57811</v>
+        <v>79005</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,21 +15185,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15209,10 +15209,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489236</v>
+        <v>489427</v>
       </c>
       <c r="R149" t="n">
-        <v>6817991</v>
+        <v>6818004</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15247,11 +15247,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Fyra individer.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15264,22 +15259,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125993318</v>
+        <v>125995957</v>
       </c>
       <c r="B150" t="n">
-        <v>78972</v>
+        <v>57812</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15287,34 +15282,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>488825</v>
+        <v>489236</v>
       </c>
       <c r="R150" t="n">
-        <v>6817957</v>
+        <v>6817991</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15349,6 +15344,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15361,12 +15361,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -15376,7 +15376,7 @@
         <v>125996385</v>
       </c>
       <c r="B151" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>125996392</v>
       </c>
       <c r="B152" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>125995781</v>
       </c>
       <c r="B153" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125996438</v>
+        <v>125996247</v>
       </c>
       <c r="B154" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,21 +15675,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15699,13 +15699,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489309</v>
+        <v>489487</v>
       </c>
       <c r="R154" t="n">
-        <v>6818107</v>
+        <v>6818014</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B155" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R155" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>125996286</v>
       </c>
       <c r="B156" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>125995381</v>
       </c>
       <c r="B157" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16052,48 +16052,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125992923</v>
+        <v>125996113</v>
       </c>
       <c r="B158" t="n">
-        <v>98360</v>
+        <v>79005</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>488811</v>
+        <v>489312</v>
       </c>
       <c r="R158" t="n">
-        <v>6817901</v>
+        <v>6817997</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16149,10 +16149,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125996113</v>
+        <v>125996114</v>
       </c>
       <c r="B159" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>489312</v>
+        <v>489329</v>
       </c>
       <c r="R159" t="n">
-        <v>6817997</v>
+        <v>6818006</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16246,48 +16246,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125996114</v>
+        <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>79004</v>
+        <v>98362</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>489329</v>
+        <v>488811</v>
       </c>
       <c r="R160" t="n">
-        <v>6818006</v>
+        <v>6817901</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>125996381</v>
       </c>
       <c r="B161" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>125991267</v>
       </c>
       <c r="B162" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>125996410</v>
       </c>
       <c r="B163" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>125992967</v>
       </c>
       <c r="B164" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>125991520</v>
       </c>
       <c r="B165" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>125996631</v>
       </c>
       <c r="B166" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>125995149</v>
       </c>
       <c r="B167" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17022,10 +17022,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995740</v>
+        <v>125995059</v>
       </c>
       <c r="B168" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17033,37 +17033,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489141</v>
+        <v>489030</v>
       </c>
       <c r="R168" t="n">
-        <v>6818047</v>
+        <v>6818049</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,22 +17107,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125994323</v>
+        <v>125995740</v>
       </c>
       <c r="B169" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17150,14 +17150,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>488963</v>
+        <v>489141</v>
       </c>
       <c r="R169" t="n">
-        <v>6817966</v>
+        <v>6818047</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17216,32 +17216,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125990421</v>
+        <v>125994323</v>
       </c>
       <c r="B170" t="n">
-        <v>91686</v>
+        <v>78973</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488613</v>
+        <v>488963</v>
       </c>
       <c r="R170" t="n">
-        <v>6818174</v>
+        <v>6817966</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,44 +17301,44 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125995059</v>
+        <v>125990421</v>
       </c>
       <c r="B171" t="n">
-        <v>78731</v>
+        <v>91688</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,10 +17348,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>489030</v>
+        <v>488613</v>
       </c>
       <c r="R171" t="n">
-        <v>6818049</v>
+        <v>6818174</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996284</v>
+        <v>125996703</v>
       </c>
       <c r="B172" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,21 +17421,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17445,13 +17445,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489434</v>
+        <v>489239</v>
       </c>
       <c r="R172" t="n">
-        <v>6818042</v>
+        <v>6818065</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996703</v>
+        <v>125996284</v>
       </c>
       <c r="B173" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,21 +17518,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489239</v>
+        <v>489434</v>
       </c>
       <c r="R173" t="n">
-        <v>6818065</v>
+        <v>6818042</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -17607,7 +17607,7 @@
         <v>125994504</v>
       </c>
       <c r="B174" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>125996386</v>
       </c>
       <c r="B175" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>125993566</v>
       </c>
       <c r="B176" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>125996288</v>
       </c>
       <c r="B177" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>125993417</v>
       </c>
       <c r="B178" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>125993829</v>
       </c>
       <c r="B179" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>125994342</v>
       </c>
       <c r="B180" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>125995962</v>
       </c>
       <c r="B181" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>125993495</v>
       </c>
       <c r="B182" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>125996069</v>
       </c>
       <c r="B183" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>125996119</v>
       </c>
       <c r="B184" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>125996051</v>
       </c>
       <c r="B185" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>125993813</v>
       </c>
       <c r="B187" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>125992179</v>
       </c>
       <c r="B188" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>125995420</v>
       </c>
       <c r="B189" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19253,10 +19253,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125995939</v>
+        <v>125996400</v>
       </c>
       <c r="B191" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19288,13 +19288,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>489210</v>
+        <v>489414</v>
       </c>
       <c r="R191" t="n">
-        <v>6818012</v>
+        <v>6818155</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19338,22 +19338,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125996400</v>
+        <v>125996428</v>
       </c>
       <c r="B192" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19385,13 +19385,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>489414</v>
+        <v>489349</v>
       </c>
       <c r="R192" t="n">
-        <v>6818155</v>
+        <v>6818082</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -19435,22 +19435,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125996428</v>
+        <v>125995939</v>
       </c>
       <c r="B193" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19482,10 +19482,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>489349</v>
+        <v>489210</v>
       </c>
       <c r="R193" t="n">
-        <v>6818082</v>
+        <v>6818012</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19547,7 +19547,7 @@
         <v>125995626</v>
       </c>
       <c r="B194" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>125994469</v>
       </c>
       <c r="B195" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>125995410</v>
       </c>
       <c r="B196" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125994510</v>
+        <v>125995904</v>
       </c>
       <c r="B197" t="n">
-        <v>96592</v>
+        <v>79005</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,37 +19846,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>488947</v>
+        <v>489185</v>
       </c>
       <c r="R197" t="n">
-        <v>6818000</v>
+        <v>6818003</v>
       </c>
       <c r="S197" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19932,10 +19932,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995904</v>
+        <v>125994510</v>
       </c>
       <c r="B198" t="n">
-        <v>79004</v>
+        <v>96594</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489185</v>
+        <v>488947</v>
       </c>
       <c r="R198" t="n">
-        <v>6818003</v>
+        <v>6818000</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20029,10 +20029,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125995830</v>
+        <v>125996865</v>
       </c>
       <c r="B199" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489169</v>
+        <v>489208</v>
       </c>
       <c r="R199" t="n">
-        <v>6818007</v>
+        <v>6818043</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20129,7 +20129,7 @@
         <v>125996064</v>
       </c>
       <c r="B200" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125996865</v>
+        <v>125995830</v>
       </c>
       <c r="B201" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489208</v>
+        <v>489169</v>
       </c>
       <c r="R201" t="n">
-        <v>6818043</v>
+        <v>6818007</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20323,7 +20323,7 @@
         <v>125996970</v>
       </c>
       <c r="B202" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>125996240</v>
       </c>
       <c r="B203" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>125996494</v>
       </c>
       <c r="B204" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B13" t="n">
-        <v>91199</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728091</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>91199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489452</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R43" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728156</v>
+        <v>125728072</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489450</v>
+        <v>489446</v>
       </c>
       <c r="R44" t="n">
-        <v>6818159</v>
+        <v>6818191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728071</v>
+        <v>125728159</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489452</v>
+        <v>489463</v>
       </c>
       <c r="R45" t="n">
-        <v>6818185</v>
+        <v>6818200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728072</v>
+        <v>125728156</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489446</v>
+        <v>489450</v>
       </c>
       <c r="R46" t="n">
-        <v>6818191</v>
+        <v>6818159</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728085</v>
+        <v>125728171</v>
       </c>
       <c r="B49" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489411</v>
+        <v>489374</v>
       </c>
       <c r="R49" t="n">
-        <v>6818380</v>
+        <v>6818387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728073</v>
+        <v>125728168</v>
       </c>
       <c r="B50" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489392</v>
+        <v>489413</v>
       </c>
       <c r="R50" t="n">
-        <v>6818361</v>
+        <v>6818350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728171</v>
+        <v>125728075</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>91156</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489374</v>
+        <v>489292</v>
       </c>
       <c r="R51" t="n">
-        <v>6818387</v>
+        <v>6818151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728168</v>
+        <v>125728158</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489413</v>
+        <v>489449</v>
       </c>
       <c r="R52" t="n">
-        <v>6818350</v>
+        <v>6818184</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728075</v>
+        <v>125728085</v>
       </c>
       <c r="B53" t="n">
-        <v>91156</v>
+        <v>79005</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489292</v>
+        <v>489411</v>
       </c>
       <c r="R53" t="n">
-        <v>6818151</v>
+        <v>6818380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728158</v>
+        <v>125728073</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489449</v>
+        <v>489392</v>
       </c>
       <c r="R54" t="n">
-        <v>6818184</v>
+        <v>6818361</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728109</v>
+        <v>125728086</v>
       </c>
       <c r="B55" t="n">
-        <v>97219</v>
+        <v>79005</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489452</v>
+        <v>489365</v>
       </c>
       <c r="R55" t="n">
-        <v>6818415</v>
+        <v>6818390</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728086</v>
+        <v>125728088</v>
       </c>
       <c r="B56" t="n">
-        <v>79005</v>
+        <v>96594</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489365</v>
+        <v>489442</v>
       </c>
       <c r="R56" t="n">
-        <v>6818390</v>
+        <v>6818350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728088</v>
+        <v>125728165</v>
       </c>
       <c r="B57" t="n">
-        <v>96594</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489442</v>
+        <v>489432</v>
       </c>
       <c r="R57" t="n">
-        <v>6818350</v>
+        <v>6818365</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728165</v>
+        <v>125728163</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489432</v>
+        <v>489456</v>
       </c>
       <c r="R58" t="n">
-        <v>6818365</v>
+        <v>6818471</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728163</v>
+        <v>125728109</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>97219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489456</v>
+        <v>489452</v>
       </c>
       <c r="R59" t="n">
-        <v>6818471</v>
+        <v>6818415</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B63" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R63" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R64" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,11 +6822,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6950,10 +6945,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728115</v>
+        <v>125728136</v>
       </c>
       <c r="B66" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6956,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6980,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489204</v>
+        <v>489467</v>
       </c>
       <c r="R66" t="n">
-        <v>6818104</v>
+        <v>6818200</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7021,6 +7016,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728142</v>
+        <v>125728114</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489363</v>
+        <v>489364</v>
       </c>
       <c r="R70" t="n">
-        <v>6818235</v>
+        <v>6818169</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728162</v>
+        <v>125728142</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489460</v>
+        <v>489363</v>
       </c>
       <c r="R71" t="n">
-        <v>6818444</v>
+        <v>6818235</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728133</v>
+        <v>125728162</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489386</v>
+        <v>489460</v>
       </c>
       <c r="R72" t="n">
-        <v>6818081</v>
+        <v>6818444</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,11 +7603,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7634,7 +7629,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728160</v>
+        <v>125728133</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7669,10 +7664,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489463</v>
+        <v>489386</v>
       </c>
       <c r="R73" t="n">
-        <v>6818278</v>
+        <v>6818081</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7705,6 +7700,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B74" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R74" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,32 +7828,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728098</v>
+        <v>125728145</v>
       </c>
       <c r="B75" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489262</v>
+        <v>489365</v>
       </c>
       <c r="R75" t="n">
-        <v>6818039</v>
+        <v>6818143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728097</v>
+        <v>125728179</v>
       </c>
       <c r="B76" t="n">
-        <v>80105</v>
+        <v>95193</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>2383</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489345</v>
+        <v>489412</v>
       </c>
       <c r="R76" t="n">
-        <v>6818245</v>
+        <v>6818351</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,32 +8022,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728140</v>
+        <v>125728098</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489337</v>
+        <v>489262</v>
       </c>
       <c r="R77" t="n">
-        <v>6818236</v>
+        <v>6818039</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,50 +8119,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728100</v>
+        <v>125728097</v>
       </c>
       <c r="B78" t="n">
-        <v>57649</v>
+        <v>80105</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489327</v>
+        <v>489345</v>
       </c>
       <c r="R78" t="n">
-        <v>6818047</v>
+        <v>6818245</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8221,7 +8216,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728145</v>
+        <v>125728140</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489365</v>
+        <v>489337</v>
       </c>
       <c r="R79" t="n">
-        <v>6818143</v>
+        <v>6818236</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8318,45 +8313,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728179</v>
+        <v>125728100</v>
       </c>
       <c r="B80" t="n">
-        <v>95193</v>
+        <v>57649</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2383</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489412</v>
+        <v>489327</v>
       </c>
       <c r="R80" t="n">
-        <v>6818351</v>
+        <v>6818047</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B94" t="n">
-        <v>78640</v>
+        <v>91600</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R94" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728126</v>
+        <v>125728177</v>
       </c>
       <c r="B95" t="n">
-        <v>91600</v>
+        <v>78640</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2064</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489439</v>
+        <v>489452</v>
       </c>
       <c r="R95" t="n">
-        <v>6818162</v>
+        <v>6818167</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728116</v>
+        <v>125728143</v>
       </c>
       <c r="B96" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9891,21 +9891,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489187</v>
+        <v>489366</v>
       </c>
       <c r="R96" t="n">
-        <v>6818091</v>
+        <v>6818215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728143</v>
+        <v>125728090</v>
       </c>
       <c r="B97" t="n">
-        <v>78973</v>
+        <v>91199</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489366</v>
+        <v>489418</v>
       </c>
       <c r="R97" t="n">
-        <v>6818215</v>
+        <v>6818094</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10074,32 +10074,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728090</v>
+        <v>125728116</v>
       </c>
       <c r="B98" t="n">
-        <v>91199</v>
+        <v>78732</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489418</v>
+        <v>489187</v>
       </c>
       <c r="R98" t="n">
-        <v>6818094</v>
+        <v>6818091</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,34 +10773,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R105" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10833,6 +10838,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10859,10 +10869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B106" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10870,39 +10880,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R106" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10935,11 +10940,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13811,10 +13811,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996409</v>
+        <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13846,13 +13846,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489377</v>
+        <v>489437</v>
       </c>
       <c r="R135" t="n">
-        <v>6818145</v>
+        <v>6818032</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,60 +13896,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996241</v>
+        <v>125995667</v>
       </c>
       <c r="B136" t="n">
-        <v>79005</v>
+        <v>98341</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489437</v>
+        <v>489117</v>
       </c>
       <c r="R136" t="n">
-        <v>6818032</v>
+        <v>6818011</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B137" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R137" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B152" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R152" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B153" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R153" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B154" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,21 +15675,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15699,13 +15699,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R154" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996438</v>
+        <v>125996286</v>
       </c>
       <c r="B155" t="n">
         <v>78973</v>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489309</v>
+        <v>489446</v>
       </c>
       <c r="R155" t="n">
-        <v>6818107</v>
+        <v>6818036</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B156" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R156" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125991267</v>
+        <v>125995149</v>
       </c>
       <c r="B162" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,21 +16451,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>488729</v>
+        <v>489055</v>
       </c>
       <c r="R162" t="n">
-        <v>6817882</v>
+        <v>6818041</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996410</v>
+        <v>125996631</v>
       </c>
       <c r="B163" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16548,21 +16548,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16572,10 +16572,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489371</v>
+        <v>489259</v>
       </c>
       <c r="R163" t="n">
-        <v>6818137</v>
+        <v>6818066</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -16634,7 +16634,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125992967</v>
+        <v>125991267</v>
       </c>
       <c r="B164" t="n">
         <v>78973</v>
@@ -16669,13 +16669,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488808</v>
+        <v>488729</v>
       </c>
       <c r="R164" t="n">
-        <v>6817936</v>
+        <v>6817882</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16719,19 +16719,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125991520</v>
+        <v>125996410</v>
       </c>
       <c r="B165" t="n">
         <v>78973</v>
@@ -16762,14 +16762,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488720</v>
+        <v>489371</v>
       </c>
       <c r="R165" t="n">
-        <v>6817985</v>
+        <v>6818137</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125996631</v>
+        <v>125992967</v>
       </c>
       <c r="B166" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,34 +16839,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>489259</v>
+        <v>488808</v>
       </c>
       <c r="R166" t="n">
-        <v>6818066</v>
+        <v>6817936</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125995149</v>
+        <v>125991520</v>
       </c>
       <c r="B167" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,21 +16936,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16960,13 +16960,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489055</v>
+        <v>488720</v>
       </c>
       <c r="R167" t="n">
-        <v>6818041</v>
+        <v>6817985</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17010,12 +17010,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -17119,48 +17119,48 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B169" t="n">
-        <v>78973</v>
+        <v>91688</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R169" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17204,19 +17204,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125994323</v>
+        <v>125995740</v>
       </c>
       <c r="B170" t="n">
         <v>78973</v>
@@ -17247,14 +17247,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488963</v>
+        <v>489141</v>
       </c>
       <c r="R170" t="n">
-        <v>6817966</v>
+        <v>6818047</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17313,32 +17313,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125990421</v>
+        <v>125994323</v>
       </c>
       <c r="B171" t="n">
-        <v>91688</v>
+        <v>78973</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>488613</v>
+        <v>488963</v>
       </c>
       <c r="R171" t="n">
-        <v>6818174</v>
+        <v>6817966</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17398,22 +17398,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996703</v>
+        <v>125994504</v>
       </c>
       <c r="B172" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,34 +17421,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489239</v>
+        <v>488931</v>
       </c>
       <c r="R172" t="n">
-        <v>6818065</v>
+        <v>6818012</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -17604,10 +17604,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125994504</v>
+        <v>125996703</v>
       </c>
       <c r="B174" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17615,34 +17615,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>488931</v>
+        <v>489239</v>
       </c>
       <c r="R174" t="n">
-        <v>6818012</v>
+        <v>6818065</v>
       </c>
       <c r="S174" t="n">
         <v>15</v>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125996386</v>
+        <v>125995962</v>
       </c>
       <c r="B175" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17712,21 +17712,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>489383</v>
+        <v>489204</v>
       </c>
       <c r="R175" t="n">
-        <v>6818097</v>
+        <v>6818012</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125993566</v>
+        <v>125996386</v>
       </c>
       <c r="B176" t="n">
         <v>78973</v>
@@ -17829,17 +17829,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>488920</v>
+        <v>489383</v>
       </c>
       <c r="R176" t="n">
-        <v>6817948</v>
+        <v>6818097</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,19 +17883,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125996288</v>
+        <v>125993566</v>
       </c>
       <c r="B177" t="n">
         <v>78973</v>
@@ -17926,14 +17926,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>489443</v>
+        <v>488920</v>
       </c>
       <c r="R177" t="n">
-        <v>6818073</v>
+        <v>6817948</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -17992,7 +17992,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125993417</v>
+        <v>125996288</v>
       </c>
       <c r="B178" t="n">
         <v>78973</v>
@@ -18023,17 +18023,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>488839</v>
+        <v>489443</v>
       </c>
       <c r="R178" t="n">
-        <v>6817946</v>
+        <v>6818073</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18077,19 +18077,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125993829</v>
+        <v>125993417</v>
       </c>
       <c r="B179" t="n">
         <v>78973</v>
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>488971</v>
+        <v>488839</v>
       </c>
       <c r="R179" t="n">
-        <v>6817935</v>
+        <v>6817946</v>
       </c>
       <c r="S179" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18174,19 +18174,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125994342</v>
+        <v>125993829</v>
       </c>
       <c r="B180" t="n">
         <v>78973</v>
@@ -18221,13 +18221,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>488947</v>
+        <v>488971</v>
       </c>
       <c r="R180" t="n">
-        <v>6818000</v>
+        <v>6817935</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -18271,22 +18271,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125995962</v>
+        <v>125994342</v>
       </c>
       <c r="B181" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,34 +18294,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>489204</v>
+        <v>488947</v>
       </c>
       <c r="R181" t="n">
-        <v>6818012</v>
+        <v>6818000</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B186" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B187" t="n">
         <v>78973</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125993813</v>
       </c>
       <c r="B188" t="n">
         <v>78973</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>488933</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6817911</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125992179</v>
       </c>
       <c r="B189" t="n">
         <v>78973</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>488791</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6817820</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125995420</v>
       </c>
       <c r="B190" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>489064</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6817976</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125995626</v>
+        <v>125994510</v>
       </c>
       <c r="B194" t="n">
-        <v>78973</v>
+        <v>96594</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,21 +19555,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19579,13 +19579,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>489111</v>
+        <v>488947</v>
       </c>
       <c r="R194" t="n">
-        <v>6817988</v>
+        <v>6818000</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19629,19 +19629,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125994469</v>
+        <v>125995626</v>
       </c>
       <c r="B195" t="n">
         <v>78973</v>
@@ -19676,10 +19676,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>488925</v>
+        <v>489111</v>
       </c>
       <c r="R195" t="n">
-        <v>6817999</v>
+        <v>6817988</v>
       </c>
       <c r="S195" t="n">
         <v>15</v>
@@ -19738,7 +19738,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995410</v>
+        <v>125994469</v>
       </c>
       <c r="B196" t="n">
         <v>78973</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489050</v>
+        <v>488925</v>
       </c>
       <c r="R196" t="n">
-        <v>6817957</v>
+        <v>6817999</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125995904</v>
+        <v>125995410</v>
       </c>
       <c r="B197" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,37 +19846,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>489185</v>
+        <v>489050</v>
       </c>
       <c r="R197" t="n">
-        <v>6818003</v>
+        <v>6817957</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125994510</v>
+        <v>125995904</v>
       </c>
       <c r="B198" t="n">
-        <v>96594</v>
+        <v>79005</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>488947</v>
+        <v>489185</v>
       </c>
       <c r="R198" t="n">
-        <v>6818000</v>
+        <v>6818003</v>
       </c>
       <c r="S198" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728080</v>
+        <v>125728101</v>
       </c>
       <c r="B2" t="n">
-        <v>79005</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489424</v>
+        <v>489357</v>
       </c>
       <c r="R2" t="n">
-        <v>6818132</v>
+        <v>6818163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125728083</v>
+        <v>125728110</v>
       </c>
       <c r="B3" t="n">
-        <v>79005</v>
+        <v>92718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489470</v>
+        <v>489380</v>
       </c>
       <c r="R3" t="n">
-        <v>6818266</v>
+        <v>6818374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728112</v>
+        <v>125728150</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489161</v>
+        <v>489356</v>
       </c>
       <c r="R4" t="n">
-        <v>6817982</v>
+        <v>6818016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728120</v>
+        <v>125728137</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489345</v>
+        <v>489352</v>
       </c>
       <c r="R5" t="n">
-        <v>6818246</v>
+        <v>6818366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728121</v>
+        <v>125728174</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489306</v>
+        <v>489338</v>
       </c>
       <c r="R6" t="n">
-        <v>6818055</v>
+        <v>6818397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728137</v>
+        <v>125728120</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489352</v>
+        <v>489345</v>
       </c>
       <c r="R7" t="n">
-        <v>6818366</v>
+        <v>6818246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728174</v>
+        <v>125728121</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489338</v>
+        <v>489306</v>
       </c>
       <c r="R8" t="n">
-        <v>6818397</v>
+        <v>6818055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,38 +1359,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728101</v>
+        <v>125728112</v>
       </c>
       <c r="B9" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489357</v>
+        <v>489161</v>
       </c>
       <c r="R9" t="n">
-        <v>6818163</v>
+        <v>6817982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728110</v>
+        <v>125728080</v>
       </c>
       <c r="B10" t="n">
-        <v>92716</v>
+        <v>79005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489380</v>
+        <v>489424</v>
       </c>
       <c r="R10" t="n">
-        <v>6818374</v>
+        <v>6818132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728150</v>
+        <v>125728083</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489356</v>
+        <v>489470</v>
       </c>
       <c r="R11" t="n">
-        <v>6818016</v>
+        <v>6818266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728149</v>
+        <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>91201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489154</v>
+        <v>489452</v>
       </c>
       <c r="R13" t="n">
-        <v>6818070</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728091</v>
+        <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>91199</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489452</v>
+        <v>489363</v>
       </c>
       <c r="R14" t="n">
-        <v>6818425</v>
+        <v>6818242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728069</v>
+        <v>125728157</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489204</v>
+        <v>489452</v>
       </c>
       <c r="R15" t="n">
-        <v>6818104</v>
+        <v>6818179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728068</v>
+        <v>125728146</v>
       </c>
       <c r="B16" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489219</v>
+        <v>489261</v>
       </c>
       <c r="R16" t="n">
-        <v>6818134</v>
+        <v>6818155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728146</v>
+        <v>125728135</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489261</v>
+        <v>489219</v>
       </c>
       <c r="R19" t="n">
-        <v>6818155</v>
+        <v>6818132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2405,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,50 +2533,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728111</v>
+        <v>125728069</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489223</v>
+        <v>489204</v>
       </c>
       <c r="R21" t="n">
-        <v>6818133</v>
+        <v>6818104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728157</v>
+        <v>125728068</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489452</v>
+        <v>489219</v>
       </c>
       <c r="R22" t="n">
-        <v>6818179</v>
+        <v>6818134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,45 +2727,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728135</v>
+        <v>125728111</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489219</v>
+        <v>489223</v>
       </c>
       <c r="R23" t="n">
-        <v>6818132</v>
+        <v>6818133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2798,11 +2803,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728095</v>
+        <v>125728147</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,42 +2840,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489341</v>
+        <v>489255</v>
       </c>
       <c r="R24" t="n">
-        <v>6818044</v>
+        <v>6818162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2908,11 +2900,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728079</v>
+        <v>125728167</v>
       </c>
       <c r="B25" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2950,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2974,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489130</v>
+        <v>489417</v>
       </c>
       <c r="R25" t="n">
-        <v>6817993</v>
+        <v>6818347</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728176</v>
+        <v>125728141</v>
       </c>
       <c r="B26" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3047,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3071,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489383</v>
+        <v>489363</v>
       </c>
       <c r="R26" t="n">
-        <v>6818074</v>
+        <v>6818242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3133,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728081</v>
+        <v>125728166</v>
       </c>
       <c r="B27" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3144,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489450</v>
+        <v>489433</v>
       </c>
       <c r="R27" t="n">
-        <v>6818184</v>
+        <v>6818362</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3230,32 +3217,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728124</v>
+        <v>125728164</v>
       </c>
       <c r="B28" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489468</v>
+        <v>489432</v>
       </c>
       <c r="R28" t="n">
-        <v>6818461</v>
+        <v>6818370</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,32 +3314,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728167</v>
+        <v>125728124</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489417</v>
+        <v>489468</v>
       </c>
       <c r="R29" t="n">
-        <v>6818347</v>
+        <v>6818461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,10 +3411,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728164</v>
+        <v>125728081</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3435,21 +3422,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3459,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489432</v>
+        <v>489450</v>
       </c>
       <c r="R30" t="n">
-        <v>6818370</v>
+        <v>6818184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728141</v>
+        <v>125728079</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3532,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3556,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489363</v>
+        <v>489130</v>
       </c>
       <c r="R31" t="n">
-        <v>6818242</v>
+        <v>6817993</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728147</v>
+        <v>125728176</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3629,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489255</v>
+        <v>489383</v>
       </c>
       <c r="R32" t="n">
-        <v>6818162</v>
+        <v>6818074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3715,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728166</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3726,34 +3713,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489433</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818362</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3786,6 +3781,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125728082</v>
+        <v>125728103</v>
       </c>
       <c r="B35" t="n">
-        <v>79005</v>
+        <v>80077</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489448</v>
+        <v>489344</v>
       </c>
       <c r="R35" t="n">
-        <v>6818191</v>
+        <v>6818246</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125728103</v>
+        <v>125728104</v>
       </c>
       <c r="B36" t="n">
         <v>80077</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489344</v>
+        <v>489262</v>
       </c>
       <c r="R36" t="n">
-        <v>6818246</v>
+        <v>6818043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,45 +4113,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728104</v>
+        <v>125728181</v>
       </c>
       <c r="B37" t="n">
-        <v>80077</v>
+        <v>5176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489262</v>
+        <v>489399</v>
       </c>
       <c r="R37" t="n">
-        <v>6818043</v>
+        <v>6818343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4210,50 +4215,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728181</v>
+        <v>125728082</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>79005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489399</v>
+        <v>489448</v>
       </c>
       <c r="R38" t="n">
-        <v>6818343</v>
+        <v>6818191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728119</v>
+        <v>125728134</v>
       </c>
       <c r="B39" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489446</v>
+        <v>489318</v>
       </c>
       <c r="R39" t="n">
-        <v>6818191</v>
+        <v>6818135</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,6 +4383,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728089</v>
+        <v>125728119</v>
       </c>
       <c r="B40" t="n">
-        <v>96594</v>
+        <v>78732</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4425,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489455</v>
+        <v>489446</v>
       </c>
       <c r="R40" t="n">
-        <v>6818449</v>
+        <v>6818191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728134</v>
+        <v>125728089</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>96596</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489318</v>
+        <v>489455</v>
       </c>
       <c r="R42" t="n">
-        <v>6818135</v>
+        <v>6818449</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728071</v>
+        <v>125728156</v>
       </c>
       <c r="B43" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489452</v>
+        <v>489450</v>
       </c>
       <c r="R43" t="n">
-        <v>6818185</v>
+        <v>6818159</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728072</v>
+        <v>125728159</v>
       </c>
       <c r="B44" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489446</v>
+        <v>489463</v>
       </c>
       <c r="R44" t="n">
-        <v>6818191</v>
+        <v>6818200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728159</v>
+        <v>125728154</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489463</v>
+        <v>489424</v>
       </c>
       <c r="R45" t="n">
-        <v>6818200</v>
+        <v>6818132</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728156</v>
+        <v>125728180</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,34 +5007,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489450</v>
+        <v>489407</v>
       </c>
       <c r="R46" t="n">
-        <v>6818159</v>
+        <v>6818050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5067,6 +5071,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5093,10 +5102,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728180</v>
+        <v>125728071</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>79591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,38 +5113,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489407</v>
+        <v>489452</v>
       </c>
       <c r="R47" t="n">
-        <v>6818050</v>
+        <v>6818185</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5168,11 +5173,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728154</v>
+        <v>125728072</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5210,21 +5210,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489424</v>
+        <v>489446</v>
       </c>
       <c r="R48" t="n">
-        <v>6818132</v>
+        <v>6818191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728171</v>
+        <v>125728075</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>91158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489374</v>
+        <v>489292</v>
       </c>
       <c r="R49" t="n">
-        <v>6818387</v>
+        <v>6818151</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728168</v>
+        <v>125728158</v>
       </c>
       <c r="B50" t="n">
         <v>78973</v>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489413</v>
+        <v>489449</v>
       </c>
       <c r="R50" t="n">
-        <v>6818350</v>
+        <v>6818184</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728075</v>
+        <v>125728168</v>
       </c>
       <c r="B51" t="n">
-        <v>91156</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489292</v>
+        <v>489413</v>
       </c>
       <c r="R51" t="n">
-        <v>6818151</v>
+        <v>6818350</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728158</v>
+        <v>125728171</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489449</v>
+        <v>489374</v>
       </c>
       <c r="R52" t="n">
-        <v>6818184</v>
+        <v>6818387</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B53" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R53" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728073</v>
+        <v>125728085</v>
       </c>
       <c r="B54" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489392</v>
+        <v>489411</v>
       </c>
       <c r="R54" t="n">
-        <v>6818361</v>
+        <v>6818380</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,10 +5878,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728086</v>
+        <v>125728163</v>
       </c>
       <c r="B55" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489365</v>
+        <v>489456</v>
       </c>
       <c r="R55" t="n">
-        <v>6818390</v>
+        <v>6818471</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728088</v>
+        <v>125728165</v>
       </c>
       <c r="B56" t="n">
-        <v>96594</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489442</v>
+        <v>489432</v>
       </c>
       <c r="R56" t="n">
-        <v>6818350</v>
+        <v>6818365</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728165</v>
+        <v>125728086</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489432</v>
+        <v>489365</v>
       </c>
       <c r="R57" t="n">
-        <v>6818365</v>
+        <v>6818390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728163</v>
+        <v>125728088</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>96596</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489456</v>
+        <v>489442</v>
       </c>
       <c r="R58" t="n">
-        <v>6818471</v>
+        <v>6818350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6269,7 +6269,7 @@
         <v>125728109</v>
       </c>
       <c r="B59" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125728144</v>
+        <v>125728170</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489370</v>
+        <v>489395</v>
       </c>
       <c r="R61" t="n">
-        <v>6818176</v>
+        <v>6818361</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125728170</v>
+        <v>125728144</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489395</v>
+        <v>489370</v>
       </c>
       <c r="R62" t="n">
-        <v>6818361</v>
+        <v>6818176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728115</v>
+        <v>125728078</v>
       </c>
       <c r="B63" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489204</v>
+        <v>489352</v>
       </c>
       <c r="R63" t="n">
-        <v>6818104</v>
+        <v>6818362</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728078</v>
+        <v>125728153</v>
       </c>
       <c r="B64" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489352</v>
+        <v>489420</v>
       </c>
       <c r="R64" t="n">
-        <v>6818362</v>
+        <v>6818126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6883,10 +6883,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R65" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,6 +6919,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6945,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728136</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6956,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6980,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489467</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818200</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,11 +7021,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B67" t="n">
-        <v>79005</v>
+        <v>91250</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R67" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B69" t="n">
-        <v>91248</v>
+        <v>79005</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R69" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728142</v>
+        <v>125728160</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489363</v>
+        <v>489463</v>
       </c>
       <c r="R71" t="n">
-        <v>6818235</v>
+        <v>6818278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728162</v>
+        <v>125728133</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489460</v>
+        <v>489386</v>
       </c>
       <c r="R72" t="n">
-        <v>6818444</v>
+        <v>6818081</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,6 +7603,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7629,7 +7634,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728133</v>
+        <v>125728142</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7664,10 +7669,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489386</v>
+        <v>489363</v>
       </c>
       <c r="R73" t="n">
-        <v>6818081</v>
+        <v>6818235</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,11 +7705,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7731,7 +7731,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728160</v>
+        <v>125728162</v>
       </c>
       <c r="B74" t="n">
         <v>78973</v>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489463</v>
+        <v>489460</v>
       </c>
       <c r="R74" t="n">
-        <v>6818278</v>
+        <v>6818444</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728145</v>
+        <v>125728100</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7839,34 +7839,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489365</v>
+        <v>489327</v>
       </c>
       <c r="R75" t="n">
-        <v>6818143</v>
+        <v>6818047</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,10 +7930,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728179</v>
+        <v>125728098</v>
       </c>
       <c r="B76" t="n">
-        <v>95193</v>
+        <v>80105</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7936,21 +7941,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2383</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7965,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489412</v>
+        <v>489262</v>
       </c>
       <c r="R76" t="n">
-        <v>6818351</v>
+        <v>6818039</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,7 +8027,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728098</v>
+        <v>125728097</v>
       </c>
       <c r="B77" t="n">
         <v>80105</v>
@@ -8057,10 +8062,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489262</v>
+        <v>489345</v>
       </c>
       <c r="R77" t="n">
-        <v>6818039</v>
+        <v>6818245</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,32 +8124,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728097</v>
+        <v>125728140</v>
       </c>
       <c r="B78" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8154,10 +8159,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489345</v>
+        <v>489337</v>
       </c>
       <c r="R78" t="n">
-        <v>6818245</v>
+        <v>6818236</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8216,7 +8221,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728140</v>
+        <v>125728145</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489337</v>
+        <v>489365</v>
       </c>
       <c r="R79" t="n">
-        <v>6818236</v>
+        <v>6818143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8313,50 +8318,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728100</v>
+        <v>125728179</v>
       </c>
       <c r="B80" t="n">
-        <v>57649</v>
+        <v>95195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>2383</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489327</v>
+        <v>489412</v>
       </c>
       <c r="R80" t="n">
-        <v>6818047</v>
+        <v>6818351</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8415,32 +8415,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125728123</v>
+        <v>125728148</v>
       </c>
       <c r="B81" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489494</v>
+        <v>489222</v>
       </c>
       <c r="R81" t="n">
-        <v>6818221</v>
+        <v>6818125</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8512,32 +8512,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125728148</v>
+        <v>125728123</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489222</v>
+        <v>489494</v>
       </c>
       <c r="R82" t="n">
-        <v>6818125</v>
+        <v>6818221</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728099</v>
+        <v>125728102</v>
       </c>
       <c r="B84" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489306</v>
+        <v>489338</v>
       </c>
       <c r="R84" t="n">
-        <v>6818056</v>
+        <v>6818240</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728099</v>
       </c>
       <c r="B85" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489306</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818056</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728102</v>
+        <v>125728125</v>
       </c>
       <c r="B87" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489338</v>
+        <v>489320</v>
       </c>
       <c r="R87" t="n">
-        <v>6818240</v>
+        <v>6818042</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728152</v>
+        <v>125728105</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>79980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489415</v>
+        <v>489306</v>
       </c>
       <c r="R88" t="n">
-        <v>6818087</v>
+        <v>6818062</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728094</v>
+        <v>125728087</v>
       </c>
       <c r="B89" t="n">
-        <v>91199</v>
+        <v>79005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489357</v>
+        <v>489343</v>
       </c>
       <c r="R89" t="n">
-        <v>6818380</v>
+        <v>6818374</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728087</v>
+        <v>125728107</v>
       </c>
       <c r="B90" t="n">
-        <v>79005</v>
+        <v>57652</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,34 +9299,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489343</v>
+        <v>489359</v>
       </c>
       <c r="R90" t="n">
-        <v>6818374</v>
+        <v>6818332</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9359,6 +9364,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9385,10 +9395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728105</v>
+        <v>125728094</v>
       </c>
       <c r="B91" t="n">
-        <v>79980</v>
+        <v>91201</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9396,21 +9406,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9420,10 +9430,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R91" t="n">
-        <v>6818062</v>
+        <v>6818380</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9482,10 +9492,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728107</v>
+        <v>125728152</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9493,39 +9503,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489359</v>
+        <v>489415</v>
       </c>
       <c r="R92" t="n">
-        <v>6818332</v>
+        <v>6818087</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9558,11 +9563,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728070</v>
+        <v>125728126</v>
       </c>
       <c r="B93" t="n">
-        <v>79591</v>
+        <v>91602</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>2064</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489185</v>
+        <v>489439</v>
       </c>
       <c r="R93" t="n">
-        <v>6818091</v>
+        <v>6818162</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B94" t="n">
-        <v>91600</v>
+        <v>79591</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R94" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728143</v>
+        <v>125728116</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9891,21 +9891,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489366</v>
+        <v>489187</v>
       </c>
       <c r="R96" t="n">
-        <v>6818215</v>
+        <v>6818091</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9980,7 +9980,7 @@
         <v>125728090</v>
       </c>
       <c r="B97" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728116</v>
+        <v>125728143</v>
       </c>
       <c r="B98" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10085,21 +10085,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489187</v>
+        <v>489366</v>
       </c>
       <c r="R98" t="n">
-        <v>6818091</v>
+        <v>6818215</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10171,7 +10171,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728172</v>
+        <v>125728173</v>
       </c>
       <c r="B99" t="n">
         <v>78973</v>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489366</v>
+        <v>489340</v>
       </c>
       <c r="R99" t="n">
-        <v>6818389</v>
+        <v>6818386</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728129</v>
+        <v>125728172</v>
       </c>
       <c r="B100" t="n">
-        <v>91855</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489370</v>
+        <v>489366</v>
       </c>
       <c r="R100" t="n">
-        <v>6818176</v>
+        <v>6818389</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728173</v>
+        <v>125728129</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>91857</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10376,21 +10376,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489340</v>
+        <v>489370</v>
       </c>
       <c r="R101" t="n">
-        <v>6818386</v>
+        <v>6818176</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728127</v>
+        <v>125728139</v>
       </c>
       <c r="B102" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10473,21 +10473,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489267</v>
+        <v>489360</v>
       </c>
       <c r="R102" t="n">
-        <v>6818149</v>
+        <v>6818301</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728139</v>
+        <v>125728127</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489360</v>
+        <v>489267</v>
       </c>
       <c r="R103" t="n">
-        <v>6818301</v>
+        <v>6818149</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125722899</v>
+        <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10773,39 +10773,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>489401</v>
+        <v>489467</v>
       </c>
       <c r="R105" t="n">
-        <v>6818344</v>
+        <v>6818063</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,11 +10833,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10869,10 +10859,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724971</v>
+        <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10880,34 +10870,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>489467</v>
+        <v>489401</v>
       </c>
       <c r="R106" t="n">
-        <v>6818063</v>
+        <v>6818344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10940,6 +10935,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125722694</v>
+        <v>125723419</v>
       </c>
       <c r="B113" t="n">
         <v>57652</v>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R113" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11624,11 +11624,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11757,7 +11752,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125723419</v>
+        <v>125722694</v>
       </c>
       <c r="B115" t="n">
         <v>57652</v>
@@ -11797,10 +11792,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R115" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11833,6 +11828,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125869115</v>
+        <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489123</v>
+        <v>489429</v>
       </c>
       <c r="R131" t="n">
-        <v>6817993</v>
+        <v>6818389</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125869112</v>
+        <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13537,10 +13537,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>489429</v>
+        <v>489123</v>
       </c>
       <c r="R132" t="n">
-        <v>6818389</v>
+        <v>6817993</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13908,45 +13908,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B136" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R136" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14005,45 +14005,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125994090</v>
+        <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>488989</v>
+        <v>489439</v>
       </c>
       <c r="R138" t="n">
-        <v>6817941</v>
+        <v>6818061</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,10 +14199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125995142</v>
+        <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14210,37 +14210,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489041</v>
+        <v>489391</v>
       </c>
       <c r="R139" t="n">
-        <v>6817951</v>
+        <v>6818133</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14284,19 +14284,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125996346</v>
+        <v>125995990</v>
       </c>
       <c r="B140" t="n">
         <v>79005</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489439</v>
+        <v>489201</v>
       </c>
       <c r="R140" t="n">
-        <v>6818061</v>
+        <v>6818003</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125996407</v>
+        <v>125994090</v>
       </c>
       <c r="B141" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,34 +14404,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489391</v>
+        <v>488989</v>
       </c>
       <c r="R141" t="n">
-        <v>6818133</v>
+        <v>6817941</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995990</v>
+        <v>125995142</v>
       </c>
       <c r="B142" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14501,37 +14501,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489201</v>
+        <v>489041</v>
       </c>
       <c r="R142" t="n">
-        <v>6818003</v>
+        <v>6817951</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B148" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R148" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B149" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R149" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996286</v>
+        <v>125996247</v>
       </c>
       <c r="B155" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,10 +15796,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R155" t="n">
-        <v>6818036</v>
+        <v>6818014</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996247</v>
+        <v>125995381</v>
       </c>
       <c r="B156" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,34 +15869,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489487</v>
+        <v>489035</v>
       </c>
       <c r="R156" t="n">
-        <v>6818014</v>
+        <v>6817949</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125995381</v>
+        <v>125996286</v>
       </c>
       <c r="B157" t="n">
-        <v>91248</v>
+        <v>78973</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489035</v>
+        <v>489446</v>
       </c>
       <c r="R157" t="n">
-        <v>6817949</v>
+        <v>6818036</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16249,7 +16249,7 @@
         <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996631</v>
+        <v>125991267</v>
       </c>
       <c r="B163" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16548,37 +16548,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489259</v>
+        <v>488729</v>
       </c>
       <c r="R163" t="n">
-        <v>6818066</v>
+        <v>6817882</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125991267</v>
+        <v>125996410</v>
       </c>
       <c r="B164" t="n">
         <v>78973</v>
@@ -16665,17 +16665,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488729</v>
+        <v>489371</v>
       </c>
       <c r="R164" t="n">
-        <v>6817882</v>
+        <v>6818137</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16719,19 +16719,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125996410</v>
+        <v>125992967</v>
       </c>
       <c r="B165" t="n">
         <v>78973</v>
@@ -16762,14 +16762,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>489371</v>
+        <v>488808</v>
       </c>
       <c r="R165" t="n">
-        <v>6818137</v>
+        <v>6817936</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,7 +16828,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125992967</v>
+        <v>125991520</v>
       </c>
       <c r="B166" t="n">
         <v>78973</v>
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488808</v>
+        <v>488720</v>
       </c>
       <c r="R166" t="n">
-        <v>6817936</v>
+        <v>6817985</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125991520</v>
+        <v>125996631</v>
       </c>
       <c r="B167" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,34 +16936,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>488720</v>
+        <v>489259</v>
       </c>
       <c r="R167" t="n">
-        <v>6817985</v>
+        <v>6818066</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17119,48 +17119,48 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125990421</v>
+        <v>125995740</v>
       </c>
       <c r="B169" t="n">
-        <v>91688</v>
+        <v>78973</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>488613</v>
+        <v>489141</v>
       </c>
       <c r="R169" t="n">
-        <v>6818174</v>
+        <v>6818047</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17204,60 +17204,60 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B170" t="n">
-        <v>78973</v>
+        <v>91690</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R170" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,12 +17301,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125994504</v>
+        <v>125996284</v>
       </c>
       <c r="B172" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,37 +17421,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>488931</v>
+        <v>489434</v>
       </c>
       <c r="R172" t="n">
-        <v>6818012</v>
+        <v>6818042</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996284</v>
+        <v>125994504</v>
       </c>
       <c r="B173" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,37 +17518,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489434</v>
+        <v>488931</v>
       </c>
       <c r="R173" t="n">
-        <v>6818042</v>
+        <v>6818012</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18380,10 +18380,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125993495</v>
+        <v>125996119</v>
       </c>
       <c r="B182" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18391,37 +18391,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>488864</v>
+        <v>489362</v>
       </c>
       <c r="R182" t="n">
-        <v>6817945</v>
+        <v>6818010</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18465,44 +18465,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125996069</v>
+        <v>125996051</v>
       </c>
       <c r="B183" t="n">
-        <v>80112</v>
+        <v>79005</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18512,10 +18512,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>489255</v>
+        <v>489241</v>
       </c>
       <c r="R183" t="n">
-        <v>6818046</v>
+        <v>6818009</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18574,10 +18574,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125996119</v>
+        <v>125993495</v>
       </c>
       <c r="B184" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18585,37 +18585,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>489362</v>
+        <v>488864</v>
       </c>
       <c r="R184" t="n">
-        <v>6818010</v>
+        <v>6817945</v>
       </c>
       <c r="S184" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -18659,44 +18659,44 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125996051</v>
+        <v>125996069</v>
       </c>
       <c r="B185" t="n">
-        <v>79005</v>
+        <v>80112</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18706,10 +18706,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>489241</v>
+        <v>489255</v>
       </c>
       <c r="R185" t="n">
-        <v>6818009</v>
+        <v>6818046</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125991445</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488712</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817879</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
         <v>78973</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125993813</v>
+        <v>125992179</v>
       </c>
       <c r="B188" t="n">
         <v>78973</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488933</v>
+        <v>488791</v>
       </c>
       <c r="R188" t="n">
-        <v>6817911</v>
+        <v>6817820</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125992179</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
         <v>78973</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488791</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6817820</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125995420</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489064</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6817976</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -19547,7 +19547,7 @@
         <v>125994510</v>
       </c>
       <c r="B194" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125995626</v>
+        <v>125995904</v>
       </c>
       <c r="B195" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>489111</v>
+        <v>489185</v>
       </c>
       <c r="R195" t="n">
-        <v>6817988</v>
+        <v>6818003</v>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,19 +19726,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125994469</v>
+        <v>125995626</v>
       </c>
       <c r="B196" t="n">
         <v>78973</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>488925</v>
+        <v>489111</v>
       </c>
       <c r="R196" t="n">
-        <v>6817999</v>
+        <v>6817988</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,7 +19835,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125995410</v>
+        <v>125994469</v>
       </c>
       <c r="B197" t="n">
         <v>78973</v>
@@ -19870,10 +19870,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>489050</v>
+        <v>488925</v>
       </c>
       <c r="R197" t="n">
-        <v>6817957</v>
+        <v>6817999</v>
       </c>
       <c r="S197" t="n">
         <v>15</v>
@@ -19932,10 +19932,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995904</v>
+        <v>125995410</v>
       </c>
       <c r="B198" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489185</v>
+        <v>489050</v>
       </c>
       <c r="R198" t="n">
-        <v>6818003</v>
+        <v>6817957</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,12 +20017,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
@@ -20126,10 +20126,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125996064</v>
+        <v>125995830</v>
       </c>
       <c r="B200" t="n">
-        <v>80077</v>
+        <v>79005</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20137,21 +20137,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489258</v>
+        <v>489169</v>
       </c>
       <c r="R200" t="n">
-        <v>6818035</v>
+        <v>6818007</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125995830</v>
+        <v>125996970</v>
       </c>
       <c r="B201" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20234,21 +20234,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489169</v>
+        <v>489179</v>
       </c>
       <c r="R201" t="n">
-        <v>6818007</v>
+        <v>6818027</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20308,22 +20308,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996970</v>
+        <v>125996064</v>
       </c>
       <c r="B202" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,13 +20355,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489179</v>
+        <v>489258</v>
       </c>
       <c r="R202" t="n">
-        <v>6818027</v>
+        <v>6818035</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20405,12 +20405,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728156</v>
+        <v>125728071</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489450</v>
+        <v>489452</v>
       </c>
       <c r="R43" t="n">
-        <v>6818159</v>
+        <v>6818185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728159</v>
+        <v>125728072</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489463</v>
+        <v>489446</v>
       </c>
       <c r="R44" t="n">
-        <v>6818200</v>
+        <v>6818191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728154</v>
+        <v>125728180</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,34 +4910,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489424</v>
+        <v>489407</v>
       </c>
       <c r="R45" t="n">
-        <v>6818132</v>
+        <v>6818050</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4970,6 +4974,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4996,10 +5005,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728180</v>
+        <v>125728156</v>
       </c>
       <c r="B46" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,38 +5016,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489407</v>
+        <v>489450</v>
       </c>
       <c r="R46" t="n">
-        <v>6818050</v>
+        <v>6818159</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5071,11 +5076,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5102,10 +5102,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728071</v>
+        <v>125728159</v>
       </c>
       <c r="B47" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5113,21 +5113,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489452</v>
+        <v>489463</v>
       </c>
       <c r="R47" t="n">
-        <v>6818185</v>
+        <v>6818200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728072</v>
+        <v>125728154</v>
       </c>
       <c r="B48" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5210,21 +5210,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489446</v>
+        <v>489424</v>
       </c>
       <c r="R48" t="n">
-        <v>6818191</v>
+        <v>6818132</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728075</v>
+        <v>125728073</v>
       </c>
       <c r="B49" t="n">
-        <v>91158</v>
+        <v>79591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489292</v>
+        <v>489392</v>
       </c>
       <c r="R49" t="n">
-        <v>6818151</v>
+        <v>6818361</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728158</v>
+        <v>125728075</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>91158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489449</v>
+        <v>489292</v>
       </c>
       <c r="R50" t="n">
-        <v>6818184</v>
+        <v>6818151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728168</v>
+        <v>125728158</v>
       </c>
       <c r="B51" t="n">
         <v>78973</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489413</v>
+        <v>489449</v>
       </c>
       <c r="R51" t="n">
-        <v>6818350</v>
+        <v>6818184</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728171</v>
+        <v>125728168</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489374</v>
+        <v>489413</v>
       </c>
       <c r="R52" t="n">
-        <v>6818387</v>
+        <v>6818350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728073</v>
+        <v>125728171</v>
       </c>
       <c r="B53" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489392</v>
+        <v>489374</v>
       </c>
       <c r="R53" t="n">
-        <v>6818361</v>
+        <v>6818387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728078</v>
+        <v>125728153</v>
       </c>
       <c r="B63" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489352</v>
+        <v>489420</v>
       </c>
       <c r="R63" t="n">
-        <v>6818362</v>
+        <v>6818126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R64" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6822,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6848,10 +6853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6859,21 +6864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R65" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,11 +6924,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7828,10 +7828,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728100</v>
+        <v>125728140</v>
       </c>
       <c r="B75" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7839,39 +7839,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489327</v>
+        <v>489337</v>
       </c>
       <c r="R75" t="n">
-        <v>6818047</v>
+        <v>6818236</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7930,32 +7925,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728098</v>
+        <v>125728145</v>
       </c>
       <c r="B76" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7965,10 +7960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489262</v>
+        <v>489365</v>
       </c>
       <c r="R76" t="n">
-        <v>6818039</v>
+        <v>6818143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8027,10 +8022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728097</v>
+        <v>125728179</v>
       </c>
       <c r="B77" t="n">
-        <v>80105</v>
+        <v>95195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8038,21 +8033,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>2383</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489345</v>
+        <v>489412</v>
       </c>
       <c r="R77" t="n">
-        <v>6818245</v>
+        <v>6818351</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8124,32 +8119,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728140</v>
+        <v>125728098</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8159,10 +8154,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489337</v>
+        <v>489262</v>
       </c>
       <c r="R78" t="n">
-        <v>6818236</v>
+        <v>6818039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8221,32 +8216,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728145</v>
+        <v>125728097</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489365</v>
+        <v>489345</v>
       </c>
       <c r="R79" t="n">
-        <v>6818143</v>
+        <v>6818245</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8318,45 +8313,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728179</v>
+        <v>125728100</v>
       </c>
       <c r="B80" t="n">
-        <v>95195</v>
+        <v>57649</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2383</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489412</v>
+        <v>489327</v>
       </c>
       <c r="R80" t="n">
-        <v>6818351</v>
+        <v>6818047</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -13811,48 +13811,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996241</v>
+        <v>125995667</v>
       </c>
       <c r="B135" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489437</v>
+        <v>489117</v>
       </c>
       <c r="R135" t="n">
-        <v>6818032</v>
+        <v>6818011</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,22 +13896,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996409</v>
+        <v>125996241</v>
       </c>
       <c r="B136" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489377</v>
+        <v>489437</v>
       </c>
       <c r="R136" t="n">
-        <v>6818145</v>
+        <v>6818032</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B137" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R137" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B152" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R152" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B153" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R153" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125991267</v>
+        <v>125996631</v>
       </c>
       <c r="B163" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16548,37 +16548,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>488729</v>
+        <v>489259</v>
       </c>
       <c r="R163" t="n">
-        <v>6817882</v>
+        <v>6818066</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125996410</v>
+        <v>125991267</v>
       </c>
       <c r="B164" t="n">
         <v>78973</v>
@@ -16665,17 +16665,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>489371</v>
+        <v>488729</v>
       </c>
       <c r="R164" t="n">
-        <v>6818137</v>
+        <v>6817882</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16719,19 +16719,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125992967</v>
+        <v>125996410</v>
       </c>
       <c r="B165" t="n">
         <v>78973</v>
@@ -16762,14 +16762,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488808</v>
+        <v>489371</v>
       </c>
       <c r="R165" t="n">
-        <v>6817936</v>
+        <v>6818137</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,7 +16828,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125991520</v>
+        <v>125992967</v>
       </c>
       <c r="B166" t="n">
         <v>78973</v>
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488720</v>
+        <v>488808</v>
       </c>
       <c r="R166" t="n">
-        <v>6817985</v>
+        <v>6817936</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125996631</v>
+        <v>125991520</v>
       </c>
       <c r="B167" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,34 +16936,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489259</v>
+        <v>488720</v>
       </c>
       <c r="R167" t="n">
-        <v>6818066</v>
+        <v>6817985</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17022,10 +17022,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995059</v>
+        <v>125995740</v>
       </c>
       <c r="B168" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17033,37 +17033,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489030</v>
+        <v>489141</v>
       </c>
       <c r="R168" t="n">
-        <v>6818049</v>
+        <v>6818047</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,60 +17107,60 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B169" t="n">
-        <v>78973</v>
+        <v>91690</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R169" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17204,44 +17204,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125990421</v>
+        <v>125994323</v>
       </c>
       <c r="B170" t="n">
-        <v>91690</v>
+        <v>78973</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488613</v>
+        <v>488963</v>
       </c>
       <c r="R170" t="n">
-        <v>6818174</v>
+        <v>6817966</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17301,22 +17301,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125994323</v>
+        <v>125995059</v>
       </c>
       <c r="B171" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17324,21 +17324,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>488963</v>
+        <v>489030</v>
       </c>
       <c r="R171" t="n">
-        <v>6817966</v>
+        <v>6818049</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17398,12 +17398,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125995962</v>
+        <v>125996386</v>
       </c>
       <c r="B175" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17712,21 +17712,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>489204</v>
+        <v>489383</v>
       </c>
       <c r="R175" t="n">
-        <v>6818012</v>
+        <v>6818097</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125996386</v>
+        <v>125993566</v>
       </c>
       <c r="B176" t="n">
         <v>78973</v>
@@ -17829,17 +17829,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>489383</v>
+        <v>488920</v>
       </c>
       <c r="R176" t="n">
-        <v>6818097</v>
+        <v>6817948</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,19 +17883,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125993566</v>
+        <v>125996288</v>
       </c>
       <c r="B177" t="n">
         <v>78973</v>
@@ -17926,14 +17926,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>488920</v>
+        <v>489443</v>
       </c>
       <c r="R177" t="n">
-        <v>6817948</v>
+        <v>6818073</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -17992,7 +17992,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125996288</v>
+        <v>125993417</v>
       </c>
       <c r="B178" t="n">
         <v>78973</v>
@@ -18023,17 +18023,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>489443</v>
+        <v>488839</v>
       </c>
       <c r="R178" t="n">
-        <v>6818073</v>
+        <v>6817946</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18077,19 +18077,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125993417</v>
+        <v>125993829</v>
       </c>
       <c r="B179" t="n">
         <v>78973</v>
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>488839</v>
+        <v>488971</v>
       </c>
       <c r="R179" t="n">
-        <v>6817946</v>
+        <v>6817935</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18174,19 +18174,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125993829</v>
+        <v>125994342</v>
       </c>
       <c r="B180" t="n">
         <v>78973</v>
@@ -18221,13 +18221,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>488971</v>
+        <v>488947</v>
       </c>
       <c r="R180" t="n">
-        <v>6817935</v>
+        <v>6818000</v>
       </c>
       <c r="S180" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -18271,22 +18271,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125994342</v>
+        <v>125995962</v>
       </c>
       <c r="B181" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,34 +18294,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>488947</v>
+        <v>489204</v>
       </c>
       <c r="R181" t="n">
-        <v>6818000</v>
+        <v>6818012</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B186" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125996514</v>
       </c>
       <c r="B187" t="n">
         <v>78973</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>489277</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6818090</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125993813</v>
       </c>
       <c r="B188" t="n">
         <v>78973</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>488933</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6817911</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125992179</v>
       </c>
       <c r="B189" t="n">
         <v>78973</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>488791</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6817820</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125995420</v>
       </c>
       <c r="B190" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>489064</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6817976</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125994510</v>
+        <v>125995626</v>
       </c>
       <c r="B194" t="n">
-        <v>96596</v>
+        <v>78973</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,21 +19555,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19579,13 +19579,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>488947</v>
+        <v>489111</v>
       </c>
       <c r="R194" t="n">
-        <v>6818000</v>
+        <v>6817988</v>
       </c>
       <c r="S194" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19629,22 +19629,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125995904</v>
+        <v>125994469</v>
       </c>
       <c r="B195" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>489185</v>
+        <v>488925</v>
       </c>
       <c r="R195" t="n">
-        <v>6818003</v>
+        <v>6817999</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,19 +19726,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995626</v>
+        <v>125995410</v>
       </c>
       <c r="B196" t="n">
         <v>78973</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489111</v>
+        <v>489050</v>
       </c>
       <c r="R196" t="n">
-        <v>6817988</v>
+        <v>6817957</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125994469</v>
+        <v>125994510</v>
       </c>
       <c r="B197" t="n">
-        <v>78973</v>
+        <v>96596</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,21 +19846,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19870,13 +19870,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>488925</v>
+        <v>488947</v>
       </c>
       <c r="R197" t="n">
-        <v>6817999</v>
+        <v>6818000</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995410</v>
+        <v>125995904</v>
       </c>
       <c r="B198" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489050</v>
+        <v>489185</v>
       </c>
       <c r="R198" t="n">
-        <v>6817957</v>
+        <v>6818003</v>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,22 +20017,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125996865</v>
+        <v>125996970</v>
       </c>
       <c r="B199" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20040,21 +20040,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20064,13 +20064,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489208</v>
+        <v>489179</v>
       </c>
       <c r="R199" t="n">
-        <v>6818043</v>
+        <v>6818027</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -20114,22 +20114,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125995830</v>
+        <v>125996064</v>
       </c>
       <c r="B200" t="n">
-        <v>79005</v>
+        <v>80077</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20137,21 +20137,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489169</v>
+        <v>489258</v>
       </c>
       <c r="R200" t="n">
-        <v>6818007</v>
+        <v>6818035</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125996970</v>
+        <v>125996240</v>
       </c>
       <c r="B201" t="n">
         <v>78973</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489179</v>
+        <v>489466</v>
       </c>
       <c r="R201" t="n">
-        <v>6818027</v>
+        <v>6818007</v>
       </c>
       <c r="S201" t="n">
         <v>15</v>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996064</v>
+        <v>125996494</v>
       </c>
       <c r="B202" t="n">
-        <v>80077</v>
+        <v>78732</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,13 +20355,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489258</v>
+        <v>489277</v>
       </c>
       <c r="R202" t="n">
-        <v>6818035</v>
+        <v>6818089</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20405,22 +20405,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996240</v>
+        <v>125996865</v>
       </c>
       <c r="B203" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20428,21 +20428,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20452,13 +20452,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489466</v>
+        <v>489208</v>
       </c>
       <c r="R203" t="n">
-        <v>6818007</v>
+        <v>6818043</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20502,22 +20502,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125996494</v>
+        <v>125995830</v>
       </c>
       <c r="B204" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20525,21 +20525,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20549,13 +20549,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>489277</v>
+        <v>489169</v>
       </c>
       <c r="R204" t="n">
-        <v>6818089</v>
+        <v>6818007</v>
       </c>
       <c r="S204" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -20599,12 +20599,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728101</v>
+        <v>125728080</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>79005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489357</v>
+        <v>489424</v>
       </c>
       <c r="R2" t="n">
-        <v>6818163</v>
+        <v>6818132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +775,7 @@
         <v>125728110</v>
       </c>
       <c r="B3" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728150</v>
+        <v>125728174</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489356</v>
+        <v>489338</v>
       </c>
       <c r="R4" t="n">
-        <v>6818016</v>
+        <v>6818397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728137</v>
+        <v>125728150</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489352</v>
+        <v>489356</v>
       </c>
       <c r="R5" t="n">
-        <v>6818366</v>
+        <v>6818016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728174</v>
+        <v>125728120</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489338</v>
+        <v>489345</v>
       </c>
       <c r="R6" t="n">
-        <v>6818397</v>
+        <v>6818246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728120</v>
+        <v>125728121</v>
       </c>
       <c r="B7" t="n">
         <v>80112</v>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489345</v>
+        <v>489306</v>
       </c>
       <c r="R7" t="n">
-        <v>6818246</v>
+        <v>6818055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728121</v>
+        <v>125728101</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R8" t="n">
-        <v>6818055</v>
+        <v>6818163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,50 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728112</v>
+        <v>125728083</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>79005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489161</v>
+        <v>489470</v>
       </c>
       <c r="R9" t="n">
-        <v>6817982</v>
+        <v>6818266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728080</v>
+        <v>125728137</v>
       </c>
       <c r="B10" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489424</v>
+        <v>489352</v>
       </c>
       <c r="R10" t="n">
-        <v>6818132</v>
+        <v>6818366</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,45 +1553,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125728083</v>
+        <v>125728112</v>
       </c>
       <c r="B11" t="n">
-        <v>79005</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489470</v>
+        <v>489161</v>
       </c>
       <c r="R11" t="n">
-        <v>6818266</v>
+        <v>6817982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728157</v>
+        <v>125728155</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489452</v>
+        <v>489417</v>
       </c>
       <c r="R15" t="n">
-        <v>6818179</v>
+        <v>6818154</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728146</v>
+        <v>125728135</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489261</v>
+        <v>489219</v>
       </c>
       <c r="R16" t="n">
-        <v>6818155</v>
+        <v>6818132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,7 +2145,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728169</v>
+        <v>125728157</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489407</v>
+        <v>489452</v>
       </c>
       <c r="R17" t="n">
-        <v>6818356</v>
+        <v>6818179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728155</v>
+        <v>125728161</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2272,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489417</v>
+        <v>489439</v>
       </c>
       <c r="R18" t="n">
-        <v>6818154</v>
+        <v>6818361</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728135</v>
+        <v>125728069</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489219</v>
+        <v>489204</v>
       </c>
       <c r="R19" t="n">
-        <v>6818132</v>
+        <v>6818104</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728161</v>
+        <v>125728068</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489439</v>
+        <v>489219</v>
       </c>
       <c r="R20" t="n">
-        <v>6818361</v>
+        <v>6818134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,45 +2533,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728069</v>
+        <v>125728111</v>
       </c>
       <c r="B21" t="n">
-        <v>79591</v>
+        <v>8447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489204</v>
+        <v>489223</v>
       </c>
       <c r="R21" t="n">
-        <v>6818104</v>
+        <v>6818133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728068</v>
+        <v>125728146</v>
       </c>
       <c r="B22" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489219</v>
+        <v>489261</v>
       </c>
       <c r="R22" t="n">
-        <v>6818134</v>
+        <v>6818155</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,50 +2732,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728111</v>
+        <v>125728169</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489223</v>
+        <v>489407</v>
       </c>
       <c r="R23" t="n">
-        <v>6818133</v>
+        <v>6818356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728147</v>
+        <v>125728124</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489255</v>
+        <v>489468</v>
       </c>
       <c r="R24" t="n">
-        <v>6818162</v>
+        <v>6818461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728167</v>
+        <v>125728147</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489417</v>
+        <v>489255</v>
       </c>
       <c r="R25" t="n">
-        <v>6818347</v>
+        <v>6818162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728141</v>
+        <v>125728095</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,34 +3034,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489363</v>
+        <v>489341</v>
       </c>
       <c r="R26" t="n">
-        <v>6818242</v>
+        <v>6818044</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3094,6 +3102,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3120,7 +3133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728166</v>
+        <v>125728141</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3155,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489433</v>
+        <v>489363</v>
       </c>
       <c r="R27" t="n">
-        <v>6818362</v>
+        <v>6818242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3230,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728164</v>
+        <v>125728167</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3252,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489432</v>
+        <v>489417</v>
       </c>
       <c r="R28" t="n">
-        <v>6818370</v>
+        <v>6818347</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,32 +3327,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728124</v>
+        <v>125728176</v>
       </c>
       <c r="B29" t="n">
-        <v>80112</v>
+        <v>78640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489468</v>
+        <v>489383</v>
       </c>
       <c r="R29" t="n">
-        <v>6818461</v>
+        <v>6818074</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3521,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728079</v>
+        <v>125728166</v>
       </c>
       <c r="B31" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3532,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3556,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489130</v>
+        <v>489433</v>
       </c>
       <c r="R31" t="n">
-        <v>6817993</v>
+        <v>6818362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3618,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728176</v>
+        <v>125728164</v>
       </c>
       <c r="B32" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,21 +3629,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3640,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489383</v>
+        <v>489432</v>
       </c>
       <c r="R32" t="n">
-        <v>6818074</v>
+        <v>6818370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,10 +3715,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728079</v>
       </c>
       <c r="B33" t="n">
-        <v>57652</v>
+        <v>79005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,42 +3726,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489130</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6817993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3786,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,50 +4113,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125728181</v>
+        <v>125728082</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>79005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489399</v>
+        <v>489448</v>
       </c>
       <c r="R37" t="n">
-        <v>6818343</v>
+        <v>6818191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4215,45 +4210,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125728082</v>
+        <v>125728181</v>
       </c>
       <c r="B38" t="n">
-        <v>79005</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489448</v>
+        <v>489399</v>
       </c>
       <c r="R38" t="n">
-        <v>6818191</v>
+        <v>6818343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125728134</v>
+        <v>125728089</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>96598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489318</v>
+        <v>489455</v>
       </c>
       <c r="R39" t="n">
-        <v>6818135</v>
+        <v>6818449</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,11 +4383,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728119</v>
+        <v>125728134</v>
       </c>
       <c r="B40" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4425,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489446</v>
+        <v>489318</v>
       </c>
       <c r="R40" t="n">
-        <v>6818191</v>
+        <v>6818135</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4485,6 +4480,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125728089</v>
+        <v>125728119</v>
       </c>
       <c r="B42" t="n">
-        <v>96596</v>
+        <v>78732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489455</v>
+        <v>489446</v>
       </c>
       <c r="R42" t="n">
-        <v>6818449</v>
+        <v>6818191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728071</v>
+        <v>125728180</v>
       </c>
       <c r="B43" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,34 +4716,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489452</v>
+        <v>489407</v>
       </c>
       <c r="R43" t="n">
-        <v>6818185</v>
+        <v>6818050</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4776,6 +4780,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4802,10 +4811,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728072</v>
+        <v>125728159</v>
       </c>
       <c r="B44" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4822,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4846,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489446</v>
+        <v>489463</v>
       </c>
       <c r="R44" t="n">
-        <v>6818191</v>
+        <v>6818200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4908,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728180</v>
+        <v>125728156</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,38 +4919,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489407</v>
+        <v>489450</v>
       </c>
       <c r="R45" t="n">
-        <v>6818050</v>
+        <v>6818159</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4974,11 +4979,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5005,7 +5005,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728156</v>
+        <v>125728154</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489450</v>
+        <v>489424</v>
       </c>
       <c r="R46" t="n">
-        <v>6818159</v>
+        <v>6818132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5113,21 +5113,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R47" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728154</v>
+        <v>125728072</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5210,21 +5210,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489424</v>
+        <v>489446</v>
       </c>
       <c r="R48" t="n">
-        <v>6818132</v>
+        <v>6818191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728073</v>
+        <v>125728158</v>
       </c>
       <c r="B49" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489392</v>
+        <v>489449</v>
       </c>
       <c r="R49" t="n">
-        <v>6818361</v>
+        <v>6818184</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728075</v>
+        <v>125728085</v>
       </c>
       <c r="B50" t="n">
-        <v>91158</v>
+        <v>79005</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489292</v>
+        <v>489411</v>
       </c>
       <c r="R50" t="n">
-        <v>6818151</v>
+        <v>6818380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728158</v>
+        <v>125728168</v>
       </c>
       <c r="B51" t="n">
         <v>78973</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489449</v>
+        <v>489413</v>
       </c>
       <c r="R51" t="n">
-        <v>6818184</v>
+        <v>6818350</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728168</v>
+        <v>125728075</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>91160</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489413</v>
+        <v>489292</v>
       </c>
       <c r="R52" t="n">
-        <v>6818350</v>
+        <v>6818151</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728085</v>
+        <v>125728073</v>
       </c>
       <c r="B54" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489411</v>
+        <v>489392</v>
       </c>
       <c r="R54" t="n">
-        <v>6818380</v>
+        <v>6818361</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,7 +5878,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728163</v>
+        <v>125728165</v>
       </c>
       <c r="B55" t="n">
         <v>78973</v>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489456</v>
+        <v>489432</v>
       </c>
       <c r="R55" t="n">
-        <v>6818471</v>
+        <v>6818365</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728165</v>
+        <v>125728163</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489432</v>
+        <v>489456</v>
       </c>
       <c r="R56" t="n">
-        <v>6818365</v>
+        <v>6818471</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
         <v>125728088</v>
       </c>
       <c r="B58" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>125728109</v>
       </c>
       <c r="B59" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125728170</v>
+        <v>125728144</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489395</v>
+        <v>489370</v>
       </c>
       <c r="R61" t="n">
-        <v>6818361</v>
+        <v>6818176</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125728144</v>
+        <v>125728170</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489370</v>
+        <v>489395</v>
       </c>
       <c r="R62" t="n">
-        <v>6818176</v>
+        <v>6818361</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6654,7 +6654,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728153</v>
+        <v>125728136</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489420</v>
+        <v>489467</v>
       </c>
       <c r="R63" t="n">
-        <v>6818126</v>
+        <v>6818200</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6725,6 +6725,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6751,7 +6756,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728136</v>
+        <v>125728153</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -6786,10 +6791,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489467</v>
+        <v>489420</v>
       </c>
       <c r="R64" t="n">
-        <v>6818200</v>
+        <v>6818126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,11 +6827,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6853,10 +6853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B65" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6864,21 +6864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R65" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728115</v>
+        <v>125728078</v>
       </c>
       <c r="B66" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489204</v>
+        <v>489352</v>
       </c>
       <c r="R66" t="n">
-        <v>6818104</v>
+        <v>6818362</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728130</v>
+        <v>125728084</v>
       </c>
       <c r="B67" t="n">
-        <v>91250</v>
+        <v>79005</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489444</v>
+        <v>489414</v>
       </c>
       <c r="R67" t="n">
-        <v>6818412</v>
+        <v>6818350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B69" t="n">
-        <v>79005</v>
+        <v>91252</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R69" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728160</v>
+        <v>125728133</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489463</v>
+        <v>489386</v>
       </c>
       <c r="R71" t="n">
-        <v>6818278</v>
+        <v>6818081</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,6 +7506,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,7 +7537,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728133</v>
+        <v>125728160</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7567,10 +7572,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489386</v>
+        <v>489463</v>
       </c>
       <c r="R72" t="n">
-        <v>6818081</v>
+        <v>6818278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,11 +7608,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7828,10 +7828,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728140</v>
+        <v>125728100</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7839,34 +7839,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489337</v>
+        <v>489327</v>
       </c>
       <c r="R75" t="n">
-        <v>6818236</v>
+        <v>6818047</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7925,32 +7930,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728145</v>
+        <v>125728179</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>95197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>2383</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7960,10 +7965,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489365</v>
+        <v>489412</v>
       </c>
       <c r="R76" t="n">
-        <v>6818143</v>
+        <v>6818351</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8022,32 +8027,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728179</v>
+        <v>125728140</v>
       </c>
       <c r="B77" t="n">
-        <v>95195</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2383</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8057,10 +8062,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489412</v>
+        <v>489337</v>
       </c>
       <c r="R77" t="n">
-        <v>6818351</v>
+        <v>6818236</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8119,32 +8124,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728098</v>
+        <v>125728145</v>
       </c>
       <c r="B78" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8154,10 +8159,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489262</v>
+        <v>489365</v>
       </c>
       <c r="R78" t="n">
-        <v>6818039</v>
+        <v>6818143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8216,7 +8221,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728097</v>
+        <v>125728098</v>
       </c>
       <c r="B79" t="n">
         <v>80105</v>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489345</v>
+        <v>489262</v>
       </c>
       <c r="R79" t="n">
-        <v>6818245</v>
+        <v>6818039</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8313,50 +8318,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728100</v>
+        <v>125728097</v>
       </c>
       <c r="B80" t="n">
-        <v>57649</v>
+        <v>80105</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489327</v>
+        <v>489345</v>
       </c>
       <c r="R80" t="n">
-        <v>6818047</v>
+        <v>6818245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8415,32 +8415,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125728148</v>
+        <v>125728123</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489222</v>
+        <v>489494</v>
       </c>
       <c r="R81" t="n">
-        <v>6818125</v>
+        <v>6818221</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8512,32 +8512,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125728123</v>
+        <v>125728148</v>
       </c>
       <c r="B82" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489494</v>
+        <v>489222</v>
       </c>
       <c r="R82" t="n">
-        <v>6818221</v>
+        <v>6818125</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8609,10 +8609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728117</v>
+        <v>125728077</v>
       </c>
       <c r="B83" t="n">
-        <v>78732</v>
+        <v>75068</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8620,21 +8620,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489409</v>
+        <v>489458</v>
       </c>
       <c r="R83" t="n">
-        <v>6818054</v>
+        <v>6818455</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728102</v>
+        <v>125728099</v>
       </c>
       <c r="B84" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489338</v>
+        <v>489306</v>
       </c>
       <c r="R84" t="n">
-        <v>6818240</v>
+        <v>6818056</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728099</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489306</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818056</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728077</v>
+        <v>125728102</v>
       </c>
       <c r="B86" t="n">
-        <v>75068</v>
+        <v>80077</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489458</v>
+        <v>489338</v>
       </c>
       <c r="R86" t="n">
-        <v>6818455</v>
+        <v>6818240</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728125</v>
+        <v>125728117</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489320</v>
+        <v>489409</v>
       </c>
       <c r="R87" t="n">
-        <v>6818042</v>
+        <v>6818054</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728105</v>
+        <v>125728087</v>
       </c>
       <c r="B88" t="n">
-        <v>79980</v>
+        <v>79005</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489306</v>
+        <v>489343</v>
       </c>
       <c r="R88" t="n">
-        <v>6818062</v>
+        <v>6818374</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728087</v>
+        <v>125728094</v>
       </c>
       <c r="B89" t="n">
-        <v>79005</v>
+        <v>91203</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489343</v>
+        <v>489357</v>
       </c>
       <c r="R89" t="n">
-        <v>6818374</v>
+        <v>6818380</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,50 +9288,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728107</v>
+        <v>125728105</v>
       </c>
       <c r="B90" t="n">
-        <v>57652</v>
+        <v>79980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489359</v>
+        <v>489306</v>
       </c>
       <c r="R90" t="n">
-        <v>6818332</v>
+        <v>6818062</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9364,11 +9359,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9395,45 +9385,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728094</v>
+        <v>125728107</v>
       </c>
       <c r="B91" t="n">
-        <v>91201</v>
+        <v>57652</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489357</v>
+        <v>489359</v>
       </c>
       <c r="R91" t="n">
-        <v>6818380</v>
+        <v>6818332</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9466,6 +9461,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B93" t="n">
-        <v>91602</v>
+        <v>79591</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R93" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728070</v>
+        <v>125728126</v>
       </c>
       <c r="B94" t="n">
-        <v>79591</v>
+        <v>91604</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>2064</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489185</v>
+        <v>489439</v>
       </c>
       <c r="R94" t="n">
-        <v>6818091</v>
+        <v>6818162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728116</v>
+        <v>125728143</v>
       </c>
       <c r="B96" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9891,21 +9891,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489187</v>
+        <v>489366</v>
       </c>
       <c r="R96" t="n">
-        <v>6818091</v>
+        <v>6818215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728090</v>
+        <v>125728116</v>
       </c>
       <c r="B97" t="n">
-        <v>91201</v>
+        <v>78732</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489418</v>
+        <v>489187</v>
       </c>
       <c r="R97" t="n">
-        <v>6818094</v>
+        <v>6818091</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10074,32 +10074,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728143</v>
+        <v>125728090</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>91203</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489366</v>
+        <v>489418</v>
       </c>
       <c r="R98" t="n">
-        <v>6818215</v>
+        <v>6818094</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728173</v>
+        <v>125728129</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>91859</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489340</v>
+        <v>489370</v>
       </c>
       <c r="R99" t="n">
-        <v>6818386</v>
+        <v>6818176</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,7 +10268,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728172</v>
+        <v>125728173</v>
       </c>
       <c r="B100" t="n">
         <v>78973</v>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489366</v>
+        <v>489340</v>
       </c>
       <c r="R100" t="n">
-        <v>6818389</v>
+        <v>6818386</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728129</v>
+        <v>125728172</v>
       </c>
       <c r="B101" t="n">
-        <v>91857</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10376,21 +10376,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489370</v>
+        <v>489366</v>
       </c>
       <c r="R101" t="n">
-        <v>6818176</v>
+        <v>6818389</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11650,38 +11650,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125723678</v>
+        <v>125722694</v>
       </c>
       <c r="B114" t="n">
-        <v>56844</v>
+        <v>57652</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R114" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,6 +11726,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11752,38 +11757,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125722694</v>
+        <v>125723678</v>
       </c>
       <c r="B115" t="n">
-        <v>57652</v>
+        <v>56844</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11792,10 +11797,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R115" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11828,11 +11833,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12252,50 +12252,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B120" t="n">
-        <v>57474</v>
+        <v>78973</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R120" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12354,45 +12349,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B121" t="n">
-        <v>78973</v>
+        <v>57474</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R121" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,48 +13811,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125995667</v>
+        <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489117</v>
+        <v>489437</v>
       </c>
       <c r="R135" t="n">
-        <v>6818011</v>
+        <v>6818032</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,22 +13896,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996241</v>
+        <v>125996409</v>
       </c>
       <c r="B136" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489437</v>
+        <v>489377</v>
       </c>
       <c r="R136" t="n">
-        <v>6818032</v>
+        <v>6818145</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14587,10 +14587,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125993983</v>
+        <v>125994790</v>
       </c>
       <c r="B143" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14598,21 +14598,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>488964</v>
+        <v>488932</v>
       </c>
       <c r="R143" t="n">
-        <v>6817921</v>
+        <v>6818043</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14658,11 +14658,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14689,7 +14684,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125994790</v>
+        <v>125993642</v>
       </c>
       <c r="B144" t="n">
         <v>78973</v>
@@ -14724,10 +14719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>488932</v>
+        <v>488965</v>
       </c>
       <c r="R144" t="n">
-        <v>6818043</v>
+        <v>6817938</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14786,10 +14781,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125993642</v>
+        <v>125993983</v>
       </c>
       <c r="B145" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14797,21 +14792,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14821,10 +14816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>488965</v>
+        <v>488964</v>
       </c>
       <c r="R145" t="n">
-        <v>6817938</v>
+        <v>6817921</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -14857,6 +14852,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B148" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R148" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B149" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R149" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125996438</v>
+        <v>125996247</v>
       </c>
       <c r="B154" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,21 +15675,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15699,13 +15699,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489309</v>
+        <v>489487</v>
       </c>
       <c r="R154" t="n">
-        <v>6818107</v>
+        <v>6818014</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B155" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R155" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125995381</v>
+        <v>125996286</v>
       </c>
       <c r="B156" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,34 +15869,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489035</v>
+        <v>489446</v>
       </c>
       <c r="R156" t="n">
-        <v>6817949</v>
+        <v>6818036</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125996286</v>
+        <v>125995381</v>
       </c>
       <c r="B157" t="n">
-        <v>78973</v>
+        <v>91252</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489446</v>
+        <v>489035</v>
       </c>
       <c r="R157" t="n">
-        <v>6818036</v>
+        <v>6817949</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16052,48 +16052,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125996113</v>
+        <v>125992923</v>
       </c>
       <c r="B158" t="n">
-        <v>79005</v>
+        <v>98366</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>489312</v>
+        <v>488811</v>
       </c>
       <c r="R158" t="n">
-        <v>6817997</v>
+        <v>6817901</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125996114</v>
+        <v>125996113</v>
       </c>
       <c r="B159" t="n">
         <v>79005</v>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>489329</v>
+        <v>489312</v>
       </c>
       <c r="R159" t="n">
-        <v>6818006</v>
+        <v>6817997</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16246,48 +16246,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125992923</v>
+        <v>125996114</v>
       </c>
       <c r="B160" t="n">
-        <v>98364</v>
+        <v>79005</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>488811</v>
+        <v>489329</v>
       </c>
       <c r="R160" t="n">
-        <v>6817901</v>
+        <v>6818006</v>
       </c>
       <c r="S160" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996631</v>
+        <v>125991267</v>
       </c>
       <c r="B163" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16548,37 +16548,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489259</v>
+        <v>488729</v>
       </c>
       <c r="R163" t="n">
-        <v>6818066</v>
+        <v>6817882</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125991267</v>
+        <v>125996410</v>
       </c>
       <c r="B164" t="n">
         <v>78973</v>
@@ -16665,17 +16665,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488729</v>
+        <v>489371</v>
       </c>
       <c r="R164" t="n">
-        <v>6817882</v>
+        <v>6818137</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16719,19 +16719,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125996410</v>
+        <v>125992967</v>
       </c>
       <c r="B165" t="n">
         <v>78973</v>
@@ -16762,14 +16762,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>489371</v>
+        <v>488808</v>
       </c>
       <c r="R165" t="n">
-        <v>6818137</v>
+        <v>6817936</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,7 +16828,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125992967</v>
+        <v>125991520</v>
       </c>
       <c r="B166" t="n">
         <v>78973</v>
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488808</v>
+        <v>488720</v>
       </c>
       <c r="R166" t="n">
-        <v>6817936</v>
+        <v>6817985</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125991520</v>
+        <v>125996631</v>
       </c>
       <c r="B167" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,34 +16936,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>488720</v>
+        <v>489259</v>
       </c>
       <c r="R167" t="n">
-        <v>6817985</v>
+        <v>6818066</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17022,48 +17022,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125995740</v>
+        <v>125990421</v>
       </c>
       <c r="B168" t="n">
-        <v>78973</v>
+        <v>91692</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>489141</v>
+        <v>488613</v>
       </c>
       <c r="R168" t="n">
-        <v>6818047</v>
+        <v>6818174</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17107,44 +17107,44 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125990421</v>
+        <v>125995059</v>
       </c>
       <c r="B169" t="n">
-        <v>91690</v>
+        <v>78732</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1209</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17154,10 +17154,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>488613</v>
+        <v>489030</v>
       </c>
       <c r="R169" t="n">
-        <v>6818174</v>
+        <v>6818049</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17216,7 +17216,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125994323</v>
+        <v>125995740</v>
       </c>
       <c r="B170" t="n">
         <v>78973</v>
@@ -17247,14 +17247,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>488963</v>
+        <v>489141</v>
       </c>
       <c r="R170" t="n">
-        <v>6817966</v>
+        <v>6818047</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17313,10 +17313,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125995059</v>
+        <v>125994323</v>
       </c>
       <c r="B171" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17324,21 +17324,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>489030</v>
+        <v>488963</v>
       </c>
       <c r="R171" t="n">
-        <v>6818049</v>
+        <v>6817966</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17398,22 +17398,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125996284</v>
+        <v>125994504</v>
       </c>
       <c r="B172" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,37 +17421,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>489434</v>
+        <v>488931</v>
       </c>
       <c r="R172" t="n">
-        <v>6818042</v>
+        <v>6818012</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125994504</v>
+        <v>125996284</v>
       </c>
       <c r="B173" t="n">
-        <v>78732</v>
+        <v>79005</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,37 +17518,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>488931</v>
+        <v>489434</v>
       </c>
       <c r="R173" t="n">
-        <v>6818012</v>
+        <v>6818042</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -17701,10 +17701,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125996386</v>
+        <v>125995962</v>
       </c>
       <c r="B175" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17712,21 +17712,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>489383</v>
+        <v>489204</v>
       </c>
       <c r="R175" t="n">
-        <v>6818097</v>
+        <v>6818012</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125993566</v>
+        <v>125996386</v>
       </c>
       <c r="B176" t="n">
         <v>78973</v>
@@ -17829,17 +17829,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>488920</v>
+        <v>489383</v>
       </c>
       <c r="R176" t="n">
-        <v>6817948</v>
+        <v>6818097</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,19 +17883,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125996288</v>
+        <v>125993566</v>
       </c>
       <c r="B177" t="n">
         <v>78973</v>
@@ -17926,14 +17926,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>489443</v>
+        <v>488920</v>
       </c>
       <c r="R177" t="n">
-        <v>6818073</v>
+        <v>6817948</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -17992,7 +17992,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125993417</v>
+        <v>125996288</v>
       </c>
       <c r="B178" t="n">
         <v>78973</v>
@@ -18023,17 +18023,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>488839</v>
+        <v>489443</v>
       </c>
       <c r="R178" t="n">
-        <v>6817946</v>
+        <v>6818073</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18077,19 +18077,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125993829</v>
+        <v>125993417</v>
       </c>
       <c r="B179" t="n">
         <v>78973</v>
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>488971</v>
+        <v>488839</v>
       </c>
       <c r="R179" t="n">
-        <v>6817935</v>
+        <v>6817946</v>
       </c>
       <c r="S179" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18174,19 +18174,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125994342</v>
+        <v>125993829</v>
       </c>
       <c r="B180" t="n">
         <v>78973</v>
@@ -18221,13 +18221,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>488947</v>
+        <v>488971</v>
       </c>
       <c r="R180" t="n">
-        <v>6818000</v>
+        <v>6817935</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -18271,22 +18271,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125995962</v>
+        <v>125994342</v>
       </c>
       <c r="B181" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18294,34 +18294,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>489204</v>
+        <v>488947</v>
       </c>
       <c r="R181" t="n">
-        <v>6818012</v>
+        <v>6818000</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125991445</v>
+        <v>125996514</v>
       </c>
       <c r="B186" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>488712</v>
+        <v>489277</v>
       </c>
       <c r="R186" t="n">
-        <v>6817879</v>
+        <v>6818090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,19 +18853,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B187" t="n">
         <v>78973</v>
@@ -18896,14 +18896,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R187" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18950,19 +18950,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125993813</v>
+        <v>125992179</v>
       </c>
       <c r="B188" t="n">
         <v>78973</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488933</v>
+        <v>488791</v>
       </c>
       <c r="R188" t="n">
-        <v>6817911</v>
+        <v>6817820</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125992179</v>
+        <v>125995420</v>
       </c>
       <c r="B189" t="n">
         <v>78973</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488791</v>
+        <v>489064</v>
       </c>
       <c r="R189" t="n">
-        <v>6817820</v>
+        <v>6817976</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125995420</v>
+        <v>125991445</v>
       </c>
       <c r="B190" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>489064</v>
+        <v>488712</v>
       </c>
       <c r="R190" t="n">
-        <v>6817976</v>
+        <v>6817879</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125995626</v>
+        <v>125994510</v>
       </c>
       <c r="B194" t="n">
-        <v>78973</v>
+        <v>96598</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,21 +19555,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19579,13 +19579,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>489111</v>
+        <v>488947</v>
       </c>
       <c r="R194" t="n">
-        <v>6817988</v>
+        <v>6818000</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19629,22 +19629,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125994469</v>
+        <v>125995904</v>
       </c>
       <c r="B195" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>488925</v>
+        <v>489185</v>
       </c>
       <c r="R195" t="n">
-        <v>6817999</v>
+        <v>6818003</v>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19726,19 +19726,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125995410</v>
+        <v>125995626</v>
       </c>
       <c r="B196" t="n">
         <v>78973</v>
@@ -19773,10 +19773,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>489050</v>
+        <v>489111</v>
       </c>
       <c r="R196" t="n">
-        <v>6817957</v>
+        <v>6817988</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -19835,10 +19835,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125994510</v>
+        <v>125994469</v>
       </c>
       <c r="B197" t="n">
-        <v>96596</v>
+        <v>78973</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19846,21 +19846,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19870,13 +19870,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>488947</v>
+        <v>488925</v>
       </c>
       <c r="R197" t="n">
-        <v>6818000</v>
+        <v>6817999</v>
       </c>
       <c r="S197" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -19920,22 +19920,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125995904</v>
+        <v>125995410</v>
       </c>
       <c r="B198" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19943,37 +19943,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>489185</v>
+        <v>489050</v>
       </c>
       <c r="R198" t="n">
-        <v>6818003</v>
+        <v>6817957</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20017,22 +20017,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125996970</v>
+        <v>125996064</v>
       </c>
       <c r="B199" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20040,21 +20040,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20064,13 +20064,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>489179</v>
+        <v>489258</v>
       </c>
       <c r="R199" t="n">
-        <v>6818027</v>
+        <v>6818035</v>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -20114,22 +20114,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125996064</v>
+        <v>125995830</v>
       </c>
       <c r="B200" t="n">
-        <v>80077</v>
+        <v>79005</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20137,21 +20137,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489258</v>
+        <v>489169</v>
       </c>
       <c r="R200" t="n">
-        <v>6818035</v>
+        <v>6818007</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125996240</v>
+        <v>125996865</v>
       </c>
       <c r="B201" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20234,21 +20234,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489466</v>
+        <v>489208</v>
       </c>
       <c r="R201" t="n">
-        <v>6818007</v>
+        <v>6818043</v>
       </c>
       <c r="S201" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20308,22 +20308,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996494</v>
+        <v>125996970</v>
       </c>
       <c r="B202" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20331,21 +20331,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20355,10 +20355,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489277</v>
+        <v>489179</v>
       </c>
       <c r="R202" t="n">
-        <v>6818089</v>
+        <v>6818027</v>
       </c>
       <c r="S202" t="n">
         <v>15</v>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996865</v>
+        <v>125996240</v>
       </c>
       <c r="B203" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20428,21 +20428,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20452,13 +20452,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489208</v>
+        <v>489466</v>
       </c>
       <c r="R203" t="n">
-        <v>6818043</v>
+        <v>6818007</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20502,22 +20502,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125995830</v>
+        <v>125996494</v>
       </c>
       <c r="B204" t="n">
-        <v>79005</v>
+        <v>78732</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20525,21 +20525,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20549,13 +20549,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>489169</v>
+        <v>489277</v>
       </c>
       <c r="R204" t="n">
-        <v>6818007</v>
+        <v>6818089</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -20599,12 +20599,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728124</v>
+        <v>125728141</v>
       </c>
       <c r="B24" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489468</v>
+        <v>489363</v>
       </c>
       <c r="R24" t="n">
-        <v>6818461</v>
+        <v>6818242</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728147</v>
+        <v>125728167</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489255</v>
+        <v>489417</v>
       </c>
       <c r="R25" t="n">
-        <v>6818162</v>
+        <v>6818347</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728141</v>
+        <v>125728079</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489363</v>
+        <v>489130</v>
       </c>
       <c r="R27" t="n">
-        <v>6818242</v>
+        <v>6817993</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728167</v>
+        <v>125728176</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489417</v>
+        <v>489383</v>
       </c>
       <c r="R28" t="n">
-        <v>6818347</v>
+        <v>6818074</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728176</v>
+        <v>125728081</v>
       </c>
       <c r="B29" t="n">
-        <v>78640</v>
+        <v>79005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489383</v>
+        <v>489450</v>
       </c>
       <c r="R29" t="n">
-        <v>6818074</v>
+        <v>6818184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728081</v>
+        <v>125728166</v>
       </c>
       <c r="B30" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489450</v>
+        <v>489433</v>
       </c>
       <c r="R30" t="n">
-        <v>6818184</v>
+        <v>6818362</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728166</v>
+        <v>125728147</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489433</v>
+        <v>489255</v>
       </c>
       <c r="R31" t="n">
-        <v>6818362</v>
+        <v>6818162</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,32 +3618,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728164</v>
+        <v>125728124</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489432</v>
+        <v>489468</v>
       </c>
       <c r="R32" t="n">
-        <v>6818370</v>
+        <v>6818461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728079</v>
+        <v>125728108</v>
       </c>
       <c r="B33" t="n">
-        <v>79005</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3726,34 +3726,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489130</v>
+        <v>489429</v>
       </c>
       <c r="R33" t="n">
-        <v>6817993</v>
+        <v>6818150</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3786,6 +3791,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3812,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728108</v>
+        <v>125728164</v>
       </c>
       <c r="B34" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3823,39 +3833,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489429</v>
+        <v>489432</v>
       </c>
       <c r="R34" t="n">
-        <v>6818150</v>
+        <v>6818370</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3888,11 +3893,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728180</v>
+        <v>125728159</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,38 +4716,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489407</v>
+        <v>489463</v>
       </c>
       <c r="R43" t="n">
-        <v>6818050</v>
+        <v>6818200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4780,11 +4776,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4811,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4822,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4846,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R44" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4908,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728156</v>
+        <v>125728072</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4919,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4943,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489450</v>
+        <v>489446</v>
       </c>
       <c r="R45" t="n">
-        <v>6818159</v>
+        <v>6818191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728154</v>
+        <v>125728156</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -5040,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489424</v>
+        <v>489450</v>
       </c>
       <c r="R46" t="n">
-        <v>6818132</v>
+        <v>6818159</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728071</v>
+        <v>125728154</v>
       </c>
       <c r="B47" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5113,21 +5104,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489452</v>
+        <v>489424</v>
       </c>
       <c r="R47" t="n">
-        <v>6818185</v>
+        <v>6818132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5199,10 +5190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125728072</v>
+        <v>125728180</v>
       </c>
       <c r="B48" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5210,34 +5201,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489446</v>
+        <v>489407</v>
       </c>
       <c r="R48" t="n">
-        <v>6818191</v>
+        <v>6818050</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5270,6 +5265,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Eventuellt nyuthackade bohål i björk, Form och storlek stämmer för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7338,10 +7338,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125728114</v>
+        <v>125728160</v>
       </c>
       <c r="B70" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489364</v>
+        <v>489463</v>
       </c>
       <c r="R70" t="n">
-        <v>6818169</v>
+        <v>6818278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728133</v>
+        <v>125728142</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489386</v>
+        <v>489363</v>
       </c>
       <c r="R71" t="n">
-        <v>6818081</v>
+        <v>6818235</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,11 +7506,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7537,10 +7532,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728160</v>
+        <v>125728114</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7548,21 +7543,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7572,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489463</v>
+        <v>489364</v>
       </c>
       <c r="R72" t="n">
-        <v>6818278</v>
+        <v>6818169</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7634,7 +7629,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728142</v>
+        <v>125728133</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7669,10 +7664,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489363</v>
+        <v>489386</v>
       </c>
       <c r="R73" t="n">
-        <v>6818235</v>
+        <v>6818081</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7705,6 +7700,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9094,10 +9094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728087</v>
+        <v>125728152</v>
       </c>
       <c r="B88" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489343</v>
+        <v>489415</v>
       </c>
       <c r="R88" t="n">
-        <v>6818374</v>
+        <v>6818087</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728094</v>
+        <v>125728087</v>
       </c>
       <c r="B89" t="n">
-        <v>91203</v>
+        <v>79005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489357</v>
+        <v>489343</v>
       </c>
       <c r="R89" t="n">
-        <v>6818380</v>
+        <v>6818374</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728105</v>
+        <v>125728094</v>
       </c>
       <c r="B90" t="n">
-        <v>79980</v>
+        <v>91203</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R90" t="n">
-        <v>6818062</v>
+        <v>6818380</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9385,50 +9385,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728107</v>
+        <v>125728105</v>
       </c>
       <c r="B91" t="n">
-        <v>57652</v>
+        <v>79980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489359</v>
+        <v>489306</v>
       </c>
       <c r="R91" t="n">
-        <v>6818332</v>
+        <v>6818062</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9461,11 +9456,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9492,10 +9482,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728152</v>
+        <v>125728107</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9503,34 +9493,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489415</v>
+        <v>489359</v>
       </c>
       <c r="R92" t="n">
-        <v>6818087</v>
+        <v>6818332</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9563,6 +9558,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11063,7 +11063,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125723347</v>
+        <v>125723877</v>
       </c>
       <c r="B108" t="n">
         <v>78973</v>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B148" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,34 +15088,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R148" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B149" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R149" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15664,10 +15664,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125996247</v>
+        <v>125995381</v>
       </c>
       <c r="B154" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,34 +15675,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>489487</v>
+        <v>489035</v>
       </c>
       <c r="R154" t="n">
-        <v>6818014</v>
+        <v>6817949</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996438</v>
+        <v>125996247</v>
       </c>
       <c r="B155" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489309</v>
+        <v>489487</v>
       </c>
       <c r="R155" t="n">
-        <v>6818107</v>
+        <v>6818014</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996286</v>
+        <v>125996438</v>
       </c>
       <c r="B156" t="n">
         <v>78973</v>
@@ -15893,13 +15893,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489446</v>
+        <v>489309</v>
       </c>
       <c r="R156" t="n">
-        <v>6818036</v>
+        <v>6818107</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -15955,10 +15955,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125995381</v>
+        <v>125996286</v>
       </c>
       <c r="B157" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15966,34 +15966,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>489035</v>
+        <v>489446</v>
       </c>
       <c r="R157" t="n">
-        <v>6817949</v>
+        <v>6818036</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17119,10 +17119,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125995059</v>
+        <v>125995740</v>
       </c>
       <c r="B169" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17130,37 +17130,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>489030</v>
+        <v>489141</v>
       </c>
       <c r="R169" t="n">
-        <v>6818049</v>
+        <v>6818047</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17204,19 +17204,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125995740</v>
+        <v>125994323</v>
       </c>
       <c r="B170" t="n">
         <v>78973</v>
@@ -17247,14 +17247,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>489141</v>
+        <v>488963</v>
       </c>
       <c r="R170" t="n">
-        <v>6818047</v>
+        <v>6817966</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17313,10 +17313,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125994323</v>
+        <v>125995059</v>
       </c>
       <c r="B171" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17324,21 +17324,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>488963</v>
+        <v>489030</v>
       </c>
       <c r="R171" t="n">
-        <v>6817966</v>
+        <v>6818049</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17398,12 +17398,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728080</v>
+        <v>125728101</v>
       </c>
       <c r="B2" t="n">
-        <v>79005</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489424</v>
+        <v>489357</v>
       </c>
       <c r="R2" t="n">
-        <v>6818132</v>
+        <v>6818163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +780,7 @@
         <v>125728110</v>
       </c>
       <c r="B3" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728174</v>
+        <v>125728080</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489338</v>
+        <v>489424</v>
       </c>
       <c r="R4" t="n">
-        <v>6818397</v>
+        <v>6818132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728150</v>
+        <v>125728083</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489356</v>
+        <v>489470</v>
       </c>
       <c r="R5" t="n">
-        <v>6818016</v>
+        <v>6818266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728120</v>
+        <v>125728150</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489345</v>
+        <v>489356</v>
       </c>
       <c r="R6" t="n">
-        <v>6818246</v>
+        <v>6818016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728121</v>
+        <v>125728137</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489306</v>
+        <v>489352</v>
       </c>
       <c r="R7" t="n">
-        <v>6818055</v>
+        <v>6818366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728101</v>
+        <v>125728174</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,39 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489357</v>
+        <v>489338</v>
       </c>
       <c r="R8" t="n">
-        <v>6818163</v>
+        <v>6818397</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728083</v>
+        <v>125728120</v>
       </c>
       <c r="B9" t="n">
-        <v>79005</v>
+        <v>80116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489470</v>
+        <v>489345</v>
       </c>
       <c r="R9" t="n">
-        <v>6818266</v>
+        <v>6818246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728137</v>
+        <v>125728121</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>80116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489352</v>
+        <v>489306</v>
       </c>
       <c r="R10" t="n">
-        <v>6818366</v>
+        <v>6818055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728113</v>
+        <v>125728149</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489363</v>
+        <v>489154</v>
       </c>
       <c r="R12" t="n">
-        <v>6818242</v>
+        <v>6818070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125728091</v>
       </c>
       <c r="B13" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R14" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728155</v>
+        <v>125728157</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489417</v>
+        <v>489452</v>
       </c>
       <c r="R15" t="n">
-        <v>6818154</v>
+        <v>6818179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728135</v>
+        <v>125728146</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489219</v>
+        <v>489261</v>
       </c>
       <c r="R16" t="n">
-        <v>6818132</v>
+        <v>6818155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728157</v>
+        <v>125728169</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489452</v>
+        <v>489407</v>
       </c>
       <c r="R17" t="n">
-        <v>6818179</v>
+        <v>6818356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728161</v>
+        <v>125728155</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489439</v>
+        <v>489417</v>
       </c>
       <c r="R18" t="n">
-        <v>6818361</v>
+        <v>6818154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728069</v>
+        <v>125728135</v>
       </c>
       <c r="B19" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489204</v>
+        <v>489219</v>
       </c>
       <c r="R19" t="n">
-        <v>6818104</v>
+        <v>6818132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728068</v>
+        <v>125728161</v>
       </c>
       <c r="B20" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489219</v>
+        <v>489439</v>
       </c>
       <c r="R20" t="n">
-        <v>6818134</v>
+        <v>6818361</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,50 +2533,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728111</v>
+        <v>125728069</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489223</v>
+        <v>489204</v>
       </c>
       <c r="R21" t="n">
-        <v>6818133</v>
+        <v>6818104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728146</v>
+        <v>125728068</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489261</v>
+        <v>489219</v>
       </c>
       <c r="R22" t="n">
-        <v>6818155</v>
+        <v>6818134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,45 +2727,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728169</v>
+        <v>125728111</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489407</v>
+        <v>489223</v>
       </c>
       <c r="R23" t="n">
-        <v>6818356</v>
+        <v>6818133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728141</v>
+        <v>125728079</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489363</v>
+        <v>489130</v>
       </c>
       <c r="R24" t="n">
-        <v>6818242</v>
+        <v>6817993</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728167</v>
+        <v>125728176</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489417</v>
+        <v>489383</v>
       </c>
       <c r="R25" t="n">
-        <v>6818347</v>
+        <v>6818074</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728095</v>
+        <v>125728081</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>79009</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,42 +3034,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489341</v>
+        <v>489450</v>
       </c>
       <c r="R26" t="n">
-        <v>6818044</v>
+        <v>6818184</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,11 +3094,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3133,32 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728079</v>
+        <v>125728124</v>
       </c>
       <c r="B27" t="n">
-        <v>79005</v>
+        <v>80116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489130</v>
+        <v>489468</v>
       </c>
       <c r="R27" t="n">
-        <v>6817993</v>
+        <v>6818461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3230,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125728176</v>
+        <v>125728147</v>
       </c>
       <c r="B28" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3241,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489383</v>
+        <v>489255</v>
       </c>
       <c r="R28" t="n">
-        <v>6818074</v>
+        <v>6818162</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125728081</v>
+        <v>125728167</v>
       </c>
       <c r="B29" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489450</v>
+        <v>489417</v>
       </c>
       <c r="R29" t="n">
-        <v>6818184</v>
+        <v>6818347</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,10 +3411,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125728166</v>
+        <v>125728141</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489433</v>
+        <v>489363</v>
       </c>
       <c r="R30" t="n">
-        <v>6818362</v>
+        <v>6818242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125728147</v>
+        <v>125728166</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3556,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489255</v>
+        <v>489433</v>
       </c>
       <c r="R31" t="n">
-        <v>6818162</v>
+        <v>6818362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,32 +3605,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125728124</v>
+        <v>125728164</v>
       </c>
       <c r="B32" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489468</v>
+        <v>489432</v>
       </c>
       <c r="R32" t="n">
-        <v>6818461</v>
+        <v>6818370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3715,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728108</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3744,21 +3731,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489429</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818150</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3795,7 +3785,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3822,10 +3812,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125728164</v>
+        <v>125728108</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,34 +3823,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489432</v>
+        <v>489429</v>
       </c>
       <c r="R34" t="n">
-        <v>6818370</v>
+        <v>6818150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,6 +3888,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3922,7 +3922,7 @@
         <v>125728103</v>
       </c>
       <c r="B35" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>125728104</v>
       </c>
       <c r="B36" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>125728082</v>
       </c>
       <c r="B37" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>125728089</v>
       </c>
       <c r="B39" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125728134</v>
+        <v>125728178</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489318</v>
+        <v>489394</v>
       </c>
       <c r="R40" t="n">
-        <v>6818135</v>
+        <v>6818362</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4480,11 +4480,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4511,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125728178</v>
+        <v>125728134</v>
       </c>
       <c r="B41" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489394</v>
+        <v>489318</v>
       </c>
       <c r="R41" t="n">
-        <v>6818362</v>
+        <v>6818135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4582,6 +4577,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4611,7 +4611,7 @@
         <v>125728119</v>
       </c>
       <c r="B42" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R43" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728071</v>
+        <v>125728072</v>
       </c>
       <c r="B44" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489452</v>
+        <v>489446</v>
       </c>
       <c r="R44" t="n">
-        <v>6818185</v>
+        <v>6818191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728072</v>
+        <v>125728156</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489446</v>
+        <v>489450</v>
       </c>
       <c r="R45" t="n">
-        <v>6818191</v>
+        <v>6818159</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728156</v>
+        <v>125728159</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489450</v>
+        <v>489463</v>
       </c>
       <c r="R46" t="n">
-        <v>6818159</v>
+        <v>6818200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>125728154</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>125728180</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>125728158</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728085</v>
+        <v>125728168</v>
       </c>
       <c r="B50" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489411</v>
+        <v>489413</v>
       </c>
       <c r="R50" t="n">
-        <v>6818380</v>
+        <v>6818350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728168</v>
+        <v>125728171</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489413</v>
+        <v>489374</v>
       </c>
       <c r="R51" t="n">
-        <v>6818350</v>
+        <v>6818387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5590,7 +5590,7 @@
         <v>125728075</v>
       </c>
       <c r="B52" t="n">
-        <v>91160</v>
+        <v>91164</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728171</v>
+        <v>125728085</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489374</v>
+        <v>489411</v>
       </c>
       <c r="R53" t="n">
-        <v>6818387</v>
+        <v>6818380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5784,7 +5784,7 @@
         <v>125728073</v>
       </c>
       <c r="B54" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5878,10 +5878,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728165</v>
+        <v>125728118</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489432</v>
+        <v>489422</v>
       </c>
       <c r="R55" t="n">
-        <v>6818365</v>
+        <v>6818130</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728163</v>
+        <v>125728086</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489456</v>
+        <v>489365</v>
       </c>
       <c r="R56" t="n">
-        <v>6818471</v>
+        <v>6818390</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728086</v>
+        <v>125728088</v>
       </c>
       <c r="B57" t="n">
-        <v>79005</v>
+        <v>96602</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,21 +6083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489365</v>
+        <v>489442</v>
       </c>
       <c r="R57" t="n">
-        <v>6818390</v>
+        <v>6818350</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728088</v>
+        <v>125728163</v>
       </c>
       <c r="B58" t="n">
-        <v>96598</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489442</v>
+        <v>489456</v>
       </c>
       <c r="R58" t="n">
-        <v>6818350</v>
+        <v>6818471</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728109</v>
+        <v>125728165</v>
       </c>
       <c r="B59" t="n">
-        <v>97223</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489452</v>
+        <v>489432</v>
       </c>
       <c r="R59" t="n">
-        <v>6818415</v>
+        <v>6818365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,32 +6363,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728118</v>
+        <v>125728109</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>97227</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489422</v>
+        <v>489452</v>
       </c>
       <c r="R60" t="n">
-        <v>6818130</v>
+        <v>6818415</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125728144</v>
+        <v>125728170</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489370</v>
+        <v>489395</v>
       </c>
       <c r="R61" t="n">
-        <v>6818176</v>
+        <v>6818361</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125728170</v>
+        <v>125728144</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489395</v>
+        <v>489370</v>
       </c>
       <c r="R62" t="n">
-        <v>6818361</v>
+        <v>6818176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728136</v>
+        <v>125728078</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489467</v>
+        <v>489352</v>
       </c>
       <c r="R63" t="n">
-        <v>6818200</v>
+        <v>6818362</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6725,11 +6725,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6759,7 +6754,7 @@
         <v>125728153</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6853,10 +6848,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728115</v>
+        <v>125728136</v>
       </c>
       <c r="B65" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6864,21 +6859,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6888,10 +6883,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489204</v>
+        <v>489467</v>
       </c>
       <c r="R65" t="n">
-        <v>6818104</v>
+        <v>6818200</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6924,6 +6919,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6950,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>79005</v>
+        <v>78736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125728084</v>
+        <v>125728130</v>
       </c>
       <c r="B67" t="n">
-        <v>79005</v>
+        <v>91256</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7058,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489414</v>
+        <v>489444</v>
       </c>
       <c r="R67" t="n">
-        <v>6818350</v>
+        <v>6818412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125728151</v>
+        <v>125728084</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7155,21 +7155,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489396</v>
+        <v>489414</v>
       </c>
       <c r="R68" t="n">
-        <v>6818028</v>
+        <v>6818350</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125728130</v>
+        <v>125728151</v>
       </c>
       <c r="B69" t="n">
-        <v>91252</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489444</v>
+        <v>489396</v>
       </c>
       <c r="R69" t="n">
-        <v>6818412</v>
+        <v>6818028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
         <v>125728160</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125728142</v>
+        <v>125728133</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489363</v>
+        <v>489386</v>
       </c>
       <c r="R71" t="n">
-        <v>6818235</v>
+        <v>6818081</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,6 +7506,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,10 +7537,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125728114</v>
+        <v>125728142</v>
       </c>
       <c r="B72" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7543,21 +7548,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7567,10 +7572,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489364</v>
+        <v>489363</v>
       </c>
       <c r="R72" t="n">
-        <v>6818169</v>
+        <v>6818235</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7629,10 +7634,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125728133</v>
+        <v>125728162</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7664,10 +7669,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489386</v>
+        <v>489460</v>
       </c>
       <c r="R73" t="n">
-        <v>6818081</v>
+        <v>6818444</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,11 +7705,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På minst 250 år gammal tall bland flera andra lika gamla tallar, alla utan hänsyn</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125728162</v>
+        <v>125728114</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489460</v>
+        <v>489364</v>
       </c>
       <c r="R74" t="n">
-        <v>6818444</v>
+        <v>6818169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7828,50 +7828,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125728100</v>
+        <v>125728179</v>
       </c>
       <c r="B75" t="n">
-        <v>57649</v>
+        <v>95201</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>2383</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489327</v>
+        <v>489412</v>
       </c>
       <c r="R75" t="n">
-        <v>6818047</v>
+        <v>6818351</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7930,32 +7925,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125728179</v>
+        <v>125728140</v>
       </c>
       <c r="B76" t="n">
-        <v>95197</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2383</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7965,10 +7960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489412</v>
+        <v>489337</v>
       </c>
       <c r="R76" t="n">
-        <v>6818351</v>
+        <v>6818236</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8027,10 +8022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125728140</v>
+        <v>125728145</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489337</v>
+        <v>489365</v>
       </c>
       <c r="R77" t="n">
-        <v>6818236</v>
+        <v>6818143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8124,32 +8119,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125728145</v>
+        <v>125728098</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8159,10 +8154,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489365</v>
+        <v>489262</v>
       </c>
       <c r="R78" t="n">
-        <v>6818143</v>
+        <v>6818039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8221,10 +8216,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125728098</v>
+        <v>125728097</v>
       </c>
       <c r="B79" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489262</v>
+        <v>489345</v>
       </c>
       <c r="R79" t="n">
-        <v>6818039</v>
+        <v>6818245</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8318,45 +8313,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125728097</v>
+        <v>125728100</v>
       </c>
       <c r="B80" t="n">
-        <v>80105</v>
+        <v>57653</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489345</v>
+        <v>489327</v>
       </c>
       <c r="R80" t="n">
-        <v>6818245</v>
+        <v>6818047</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8415,32 +8415,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125728123</v>
+        <v>125728148</v>
       </c>
       <c r="B81" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489494</v>
+        <v>489222</v>
       </c>
       <c r="R81" t="n">
-        <v>6818221</v>
+        <v>6818125</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8512,32 +8512,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125728148</v>
+        <v>125728123</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>80116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489222</v>
+        <v>489494</v>
       </c>
       <c r="R82" t="n">
-        <v>6818125</v>
+        <v>6818221</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8609,10 +8609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728077</v>
+        <v>125728102</v>
       </c>
       <c r="B83" t="n">
-        <v>75068</v>
+        <v>80081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8620,21 +8620,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489458</v>
+        <v>489338</v>
       </c>
       <c r="R83" t="n">
-        <v>6818455</v>
+        <v>6818240</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728099</v>
+        <v>125728077</v>
       </c>
       <c r="B84" t="n">
-        <v>80105</v>
+        <v>75072</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489306</v>
+        <v>489458</v>
       </c>
       <c r="R84" t="n">
-        <v>6818056</v>
+        <v>6818455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728125</v>
+        <v>125728117</v>
       </c>
       <c r="B85" t="n">
-        <v>80076</v>
+        <v>78736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489320</v>
+        <v>489409</v>
       </c>
       <c r="R85" t="n">
-        <v>6818042</v>
+        <v>6818054</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728102</v>
+        <v>125728099</v>
       </c>
       <c r="B86" t="n">
-        <v>80077</v>
+        <v>80109</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489338</v>
+        <v>489306</v>
       </c>
       <c r="R86" t="n">
-        <v>6818240</v>
+        <v>6818056</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728117</v>
+        <v>125728125</v>
       </c>
       <c r="B87" t="n">
-        <v>78732</v>
+        <v>80080</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489409</v>
+        <v>489320</v>
       </c>
       <c r="R87" t="n">
-        <v>6818054</v>
+        <v>6818042</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,10 +9094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728152</v>
+        <v>125728087</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489415</v>
+        <v>489343</v>
       </c>
       <c r="R88" t="n">
-        <v>6818087</v>
+        <v>6818374</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,32 +9191,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728087</v>
+        <v>125728094</v>
       </c>
       <c r="B89" t="n">
-        <v>79005</v>
+        <v>91207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489343</v>
+        <v>489357</v>
       </c>
       <c r="R89" t="n">
-        <v>6818374</v>
+        <v>6818380</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,32 +9288,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728094</v>
+        <v>125728152</v>
       </c>
       <c r="B90" t="n">
-        <v>91203</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489357</v>
+        <v>489415</v>
       </c>
       <c r="R90" t="n">
-        <v>6818380</v>
+        <v>6818087</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9388,7 +9388,7 @@
         <v>125728105</v>
       </c>
       <c r="B91" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>125728107</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>125728070</v>
       </c>
       <c r="B93" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728126</v>
+        <v>125728177</v>
       </c>
       <c r="B94" t="n">
-        <v>91604</v>
+        <v>78644</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2064</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489439</v>
+        <v>489452</v>
       </c>
       <c r="R94" t="n">
-        <v>6818162</v>
+        <v>6818167</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B95" t="n">
-        <v>78640</v>
+        <v>91608</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R95" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125728143</v>
+        <v>125728116</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9891,21 +9891,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489366</v>
+        <v>489187</v>
       </c>
       <c r="R96" t="n">
-        <v>6818215</v>
+        <v>6818091</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125728116</v>
+        <v>125728090</v>
       </c>
       <c r="B97" t="n">
-        <v>78732</v>
+        <v>91207</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489187</v>
+        <v>489418</v>
       </c>
       <c r="R97" t="n">
-        <v>6818091</v>
+        <v>6818094</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10074,32 +10074,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125728090</v>
+        <v>125728143</v>
       </c>
       <c r="B98" t="n">
-        <v>91203</v>
+        <v>78977</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>489418</v>
+        <v>489366</v>
       </c>
       <c r="R98" t="n">
-        <v>6818094</v>
+        <v>6818215</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125728129</v>
+        <v>125728173</v>
       </c>
       <c r="B99" t="n">
-        <v>91859</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>489370</v>
+        <v>489340</v>
       </c>
       <c r="R99" t="n">
-        <v>6818176</v>
+        <v>6818386</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125728173</v>
+        <v>125728172</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489340</v>
+        <v>489366</v>
       </c>
       <c r="R100" t="n">
-        <v>6818386</v>
+        <v>6818389</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125728172</v>
+        <v>125728127</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10376,21 +10376,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489366</v>
+        <v>489267</v>
       </c>
       <c r="R101" t="n">
-        <v>6818389</v>
+        <v>6818149</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125728139</v>
+        <v>125728129</v>
       </c>
       <c r="B102" t="n">
-        <v>78973</v>
+        <v>91863</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10473,21 +10473,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489360</v>
+        <v>489370</v>
       </c>
       <c r="R102" t="n">
-        <v>6818301</v>
+        <v>6818176</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125728127</v>
+        <v>125728139</v>
       </c>
       <c r="B103" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10570,21 +10570,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>489267</v>
+        <v>489360</v>
       </c>
       <c r="R103" t="n">
-        <v>6818149</v>
+        <v>6818301</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>125724971</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>125722899</v>
       </c>
       <c r="B106" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>125724254</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11063,10 +11063,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125723877</v>
+        <v>125723347</v>
       </c>
       <c r="B108" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>125725196</v>
       </c>
       <c r="B109" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>125724786</v>
       </c>
       <c r="B110" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>125722589</v>
       </c>
       <c r="B111" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>125723050</v>
       </c>
       <c r="B112" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11548,38 +11548,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125723419</v>
+        <v>125723678</v>
       </c>
       <c r="B113" t="n">
-        <v>57652</v>
+        <v>56848</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -11650,10 +11650,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125722694</v>
+        <v>125723419</v>
       </c>
       <c r="B114" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R114" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,11 +11726,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11757,38 +11752,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125723678</v>
+        <v>125722694</v>
       </c>
       <c r="B115" t="n">
-        <v>56844</v>
+        <v>57656</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11797,10 +11792,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R115" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11833,6 +11828,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11862,7 +11862,7 @@
         <v>125723960</v>
       </c>
       <c r="B116" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>125725272</v>
       </c>
       <c r="B117" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>125724536</v>
       </c>
       <c r="B118" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>125725082</v>
       </c>
       <c r="B119" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>125724111</v>
       </c>
       <c r="B120" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>125725006</v>
       </c>
       <c r="B121" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>125869116</v>
       </c>
       <c r="B122" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>125869111</v>
       </c>
       <c r="B123" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125869096</v>
       </c>
       <c r="B124" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>125869097</v>
       </c>
       <c r="B125" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>125869117</v>
       </c>
       <c r="B126" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>125869119</v>
       </c>
       <c r="B127" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>125869109</v>
       </c>
       <c r="B128" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>125869106</v>
       </c>
       <c r="B129" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>125869105</v>
       </c>
       <c r="B130" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>125869112</v>
       </c>
       <c r="B131" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>125869115</v>
       </c>
       <c r="B132" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>125869120</v>
       </c>
       <c r="B133" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>125869110</v>
       </c>
       <c r="B134" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,48 +13811,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125996241</v>
+        <v>125995667</v>
       </c>
       <c r="B135" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489437</v>
+        <v>489117</v>
       </c>
       <c r="R135" t="n">
-        <v>6818032</v>
+        <v>6818011</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,22 +13896,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996409</v>
+        <v>125996241</v>
       </c>
       <c r="B136" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489377</v>
+        <v>489437</v>
       </c>
       <c r="R136" t="n">
-        <v>6818145</v>
+        <v>6818032</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125995667</v>
+        <v>125996409</v>
       </c>
       <c r="B137" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489117</v>
+        <v>489377</v>
       </c>
       <c r="R137" t="n">
-        <v>6818011</v>
+        <v>6818145</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14105,7 +14105,7 @@
         <v>125996346</v>
       </c>
       <c r="B138" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>125996407</v>
       </c>
       <c r="B139" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>125995990</v>
       </c>
       <c r="B140" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125994090</v>
+        <v>125995142</v>
       </c>
       <c r="B141" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>488989</v>
+        <v>489041</v>
       </c>
       <c r="R141" t="n">
-        <v>6817941</v>
+        <v>6817951</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,22 +14478,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125995142</v>
+        <v>125994090</v>
       </c>
       <c r="B142" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>489041</v>
+        <v>488989</v>
       </c>
       <c r="R142" t="n">
-        <v>6817951</v>
+        <v>6817941</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,22 +14575,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125994790</v>
+        <v>125993642</v>
       </c>
       <c r="B143" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>488932</v>
+        <v>488965</v>
       </c>
       <c r="R143" t="n">
-        <v>6818043</v>
+        <v>6817938</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14684,10 +14684,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125993642</v>
+        <v>125994790</v>
       </c>
       <c r="B144" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14719,10 +14719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>488965</v>
+        <v>488932</v>
       </c>
       <c r="R144" t="n">
-        <v>6817938</v>
+        <v>6818043</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14784,7 +14784,7 @@
         <v>125993983</v>
       </c>
       <c r="B145" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>125996446</v>
       </c>
       <c r="B146" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>125996662</v>
       </c>
       <c r="B147" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125996237</v>
+        <v>125995957</v>
       </c>
       <c r="B148" t="n">
-        <v>79005</v>
+        <v>57816</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,21 +15088,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15112,10 +15112,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>489427</v>
+        <v>489236</v>
       </c>
       <c r="R148" t="n">
-        <v>6818004</v>
+        <v>6817991</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15150,6 +15150,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -15162,22 +15167,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125993318</v>
+        <v>125996237</v>
       </c>
       <c r="B149" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15185,34 +15190,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>488825</v>
+        <v>489427</v>
       </c>
       <c r="R149" t="n">
-        <v>6817957</v>
+        <v>6818004</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15271,10 +15276,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125995957</v>
+        <v>125993318</v>
       </c>
       <c r="B150" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15282,34 +15287,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>489236</v>
+        <v>488825</v>
       </c>
       <c r="R150" t="n">
-        <v>6817991</v>
+        <v>6817957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15344,11 +15349,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Fyra individer.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15361,12 +15361,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -15376,7 +15376,7 @@
         <v>125996385</v>
       </c>
       <c r="B151" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B152" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R152" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B153" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R153" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
         <v>125995381</v>
       </c>
       <c r="B154" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15761,10 +15761,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125996247</v>
+        <v>125996438</v>
       </c>
       <c r="B155" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,21 +15772,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>489487</v>
+        <v>489309</v>
       </c>
       <c r="R155" t="n">
-        <v>6818014</v>
+        <v>6818107</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125996438</v>
+        <v>125996247</v>
       </c>
       <c r="B156" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15869,21 +15869,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15893,13 +15893,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>489309</v>
+        <v>489487</v>
       </c>
       <c r="R156" t="n">
-        <v>6818107</v>
+        <v>6818014</v>
       </c>
       <c r="S156" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>125996286</v>
       </c>
       <c r="B157" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16052,48 +16052,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125992923</v>
+        <v>125996113</v>
       </c>
       <c r="B158" t="n">
-        <v>98366</v>
+        <v>79009</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>488811</v>
+        <v>489312</v>
       </c>
       <c r="R158" t="n">
-        <v>6817901</v>
+        <v>6817997</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16149,10 +16149,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125996113</v>
+        <v>125996114</v>
       </c>
       <c r="B159" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>489312</v>
+        <v>489329</v>
       </c>
       <c r="R159" t="n">
-        <v>6817997</v>
+        <v>6818006</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16246,48 +16246,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125996114</v>
+        <v>125992923</v>
       </c>
       <c r="B160" t="n">
-        <v>79005</v>
+        <v>98370</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>489329</v>
+        <v>488811</v>
       </c>
       <c r="R160" t="n">
-        <v>6818006</v>
+        <v>6817901</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>125996381</v>
       </c>
       <c r="B161" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125995149</v>
+        <v>125991267</v>
       </c>
       <c r="B162" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16451,21 +16451,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>489055</v>
+        <v>488729</v>
       </c>
       <c r="R162" t="n">
-        <v>6818041</v>
+        <v>6817882</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16537,10 +16537,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125991267</v>
+        <v>125996410</v>
       </c>
       <c r="B163" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16568,17 +16568,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>488729</v>
+        <v>489371</v>
       </c>
       <c r="R163" t="n">
-        <v>6817882</v>
+        <v>6818137</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16622,22 +16622,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125996410</v>
+        <v>125992967</v>
       </c>
       <c r="B164" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16665,14 +16665,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>489371</v>
+        <v>488808</v>
       </c>
       <c r="R164" t="n">
-        <v>6818137</v>
+        <v>6817936</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -16731,10 +16731,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125992967</v>
+        <v>125991520</v>
       </c>
       <c r="B165" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488808</v>
+        <v>488720</v>
       </c>
       <c r="R165" t="n">
-        <v>6817936</v>
+        <v>6817985</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -16828,10 +16828,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125991520</v>
+        <v>125995149</v>
       </c>
       <c r="B166" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,21 +16839,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16863,13 +16863,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>488720</v>
+        <v>489055</v>
       </c>
       <c r="R166" t="n">
-        <v>6817985</v>
+        <v>6818041</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -16913,12 +16913,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -16928,7 +16928,7 @@
         <v>125996631</v>
       </c>
       <c r="B167" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>125990421</v>
       </c>
       <c r="B168" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>125995740</v>
       </c>
       <c r="B169" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>125994323</v>
       </c>
       <c r="B170" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>125995059</v>
       </c>
       <c r="B171" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17410,10 +17410,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125994504</v>
+        <v>125996284</v>
       </c>
       <c r="B172" t="n">
-        <v>78732</v>
+        <v>79009</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17421,37 +17421,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>488931</v>
+        <v>489434</v>
       </c>
       <c r="R172" t="n">
-        <v>6818012</v>
+        <v>6818042</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17495,22 +17495,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125996284</v>
+        <v>125996703</v>
       </c>
       <c r="B173" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17518,21 +17518,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>489434</v>
+        <v>489239</v>
       </c>
       <c r="R173" t="n">
-        <v>6818042</v>
+        <v>6818065</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17592,22 +17592,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125996703</v>
+        <v>125994504</v>
       </c>
       <c r="B174" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17615,34 +17615,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>489239</v>
+        <v>488931</v>
       </c>
       <c r="R174" t="n">
-        <v>6818065</v>
+        <v>6818012</v>
       </c>
       <c r="S174" t="n">
         <v>15</v>
@@ -17704,7 +17704,7 @@
         <v>125995962</v>
       </c>
       <c r="B175" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17798,10 +17798,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125996386</v>
+        <v>125993566</v>
       </c>
       <c r="B176" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17829,17 +17829,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>489383</v>
+        <v>488920</v>
       </c>
       <c r="R176" t="n">
-        <v>6818097</v>
+        <v>6817948</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -17883,22 +17883,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125993566</v>
+        <v>125996386</v>
       </c>
       <c r="B177" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17926,17 +17926,17 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>488920</v>
+        <v>489383</v>
       </c>
       <c r="R177" t="n">
-        <v>6817948</v>
+        <v>6818097</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -17980,12 +17980,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -17995,7 +17995,7 @@
         <v>125996288</v>
       </c>
       <c r="B178" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>125993417</v>
       </c>
       <c r="B179" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>125993829</v>
       </c>
       <c r="B180" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>125994342</v>
       </c>
       <c r="B181" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>125996119</v>
       </c>
       <c r="B182" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>125996051</v>
       </c>
       <c r="B183" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>125993495</v>
       </c>
       <c r="B184" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>125996069</v>
       </c>
       <c r="B185" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18768,45 +18768,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125996514</v>
+        <v>125991445</v>
       </c>
       <c r="B186" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>489277</v>
+        <v>488712</v>
       </c>
       <c r="R186" t="n">
-        <v>6818090</v>
+        <v>6817879</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18853,22 +18853,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125993813</v>
+        <v>125995420</v>
       </c>
       <c r="B187" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>488933</v>
+        <v>489064</v>
       </c>
       <c r="R187" t="n">
-        <v>6817911</v>
+        <v>6817976</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18950,22 +18950,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125992179</v>
+        <v>125996514</v>
       </c>
       <c r="B188" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18993,17 +18993,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>488791</v>
+        <v>489277</v>
       </c>
       <c r="R188" t="n">
-        <v>6817820</v>
+        <v>6818090</v>
       </c>
       <c r="S188" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19047,22 +19047,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125995420</v>
+        <v>125993813</v>
       </c>
       <c r="B189" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>489064</v>
+        <v>488933</v>
       </c>
       <c r="R189" t="n">
-        <v>6817976</v>
+        <v>6817911</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19144,44 +19144,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125991445</v>
+        <v>125992179</v>
       </c>
       <c r="B190" t="n">
-        <v>98366</v>
+        <v>78977</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488712</v>
+        <v>488791</v>
       </c>
       <c r="R190" t="n">
-        <v>6817879</v>
+        <v>6817820</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>125996400</v>
       </c>
       <c r="B191" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>125996428</v>
       </c>
       <c r="B192" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>125995939</v>
       </c>
       <c r="B193" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19544,10 +19544,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125994510</v>
+        <v>125995904</v>
       </c>
       <c r="B194" t="n">
-        <v>96598</v>
+        <v>79009</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19555,37 +19555,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>488947</v>
+        <v>489185</v>
       </c>
       <c r="R194" t="n">
-        <v>6818000</v>
+        <v>6818003</v>
       </c>
       <c r="S194" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125995904</v>
+        <v>125994510</v>
       </c>
       <c r="B195" t="n">
-        <v>79005</v>
+        <v>96602</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19652,37 +19652,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>489185</v>
+        <v>488947</v>
       </c>
       <c r="R195" t="n">
-        <v>6818003</v>
+        <v>6818000</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>125995626</v>
       </c>
       <c r="B196" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>125994469</v>
       </c>
       <c r="B197" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>125995410</v>
       </c>
       <c r="B198" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>125996064</v>
       </c>
       <c r="B199" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20126,10 +20126,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125995830</v>
+        <v>125996865</v>
       </c>
       <c r="B200" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20161,10 +20161,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>489169</v>
+        <v>489208</v>
       </c>
       <c r="R200" t="n">
-        <v>6818007</v>
+        <v>6818043</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125996865</v>
+        <v>125995830</v>
       </c>
       <c r="B201" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>489208</v>
+        <v>489169</v>
       </c>
       <c r="R201" t="n">
-        <v>6818043</v>
+        <v>6818007</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125996970</v>
+        <v>125996240</v>
       </c>
       <c r="B202" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20355,10 +20355,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>489179</v>
+        <v>489466</v>
       </c>
       <c r="R202" t="n">
-        <v>6818027</v>
+        <v>6818007</v>
       </c>
       <c r="S202" t="n">
         <v>15</v>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125996240</v>
+        <v>125996970</v>
       </c>
       <c r="B203" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>489466</v>
+        <v>489179</v>
       </c>
       <c r="R203" t="n">
-        <v>6818007</v>
+        <v>6818027</v>
       </c>
       <c r="S203" t="n">
         <v>15</v>
@@ -20517,7 +20517,7 @@
         <v>125996494</v>
       </c>
       <c r="B204" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728079</v>
+        <v>125728095</v>
       </c>
       <c r="B24" t="n">
-        <v>79009</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,34 +2840,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489130</v>
+        <v>489341</v>
       </c>
       <c r="R24" t="n">
-        <v>6817993</v>
+        <v>6818044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2900,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2926,10 +2939,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125728176</v>
+        <v>125728079</v>
       </c>
       <c r="B25" t="n">
-        <v>78644</v>
+        <v>79009</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2950,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489383</v>
+        <v>489130</v>
       </c>
       <c r="R25" t="n">
-        <v>6818074</v>
+        <v>6817993</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3036,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125728081</v>
+        <v>125728176</v>
       </c>
       <c r="B26" t="n">
-        <v>79009</v>
+        <v>78644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3047,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3071,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489450</v>
+        <v>489383</v>
       </c>
       <c r="R26" t="n">
-        <v>6818184</v>
+        <v>6818074</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,32 +3133,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125728124</v>
+        <v>125728081</v>
       </c>
       <c r="B27" t="n">
-        <v>80116</v>
+        <v>79009</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489468</v>
+        <v>489450</v>
       </c>
       <c r="R27" t="n">
-        <v>6818461</v>
+        <v>6818184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3702,53 +3715,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728095</v>
+        <v>125728124</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489341</v>
+        <v>489468</v>
       </c>
       <c r="R33" t="n">
-        <v>6818044</v>
+        <v>6818461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,11 +3786,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125728071</v>
+        <v>125728156</v>
       </c>
       <c r="B43" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489452</v>
+        <v>489450</v>
       </c>
       <c r="R43" t="n">
-        <v>6818185</v>
+        <v>6818159</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728072</v>
+        <v>125728159</v>
       </c>
       <c r="B44" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489446</v>
+        <v>489463</v>
       </c>
       <c r="R44" t="n">
-        <v>6818191</v>
+        <v>6818200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728156</v>
+        <v>125728154</v>
       </c>
       <c r="B45" t="n">
         <v>78977</v>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489450</v>
+        <v>489424</v>
       </c>
       <c r="R45" t="n">
-        <v>6818159</v>
+        <v>6818132</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R46" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728154</v>
+        <v>125728072</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489424</v>
+        <v>489446</v>
       </c>
       <c r="R47" t="n">
-        <v>6818132</v>
+        <v>6818191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125728158</v>
+        <v>125728075</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>91164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489449</v>
+        <v>489292</v>
       </c>
       <c r="R49" t="n">
-        <v>6818184</v>
+        <v>6818151</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125728168</v>
+        <v>125728085</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489413</v>
+        <v>489411</v>
       </c>
       <c r="R50" t="n">
-        <v>6818350</v>
+        <v>6818380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125728171</v>
+        <v>125728158</v>
       </c>
       <c r="B51" t="n">
         <v>78977</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489374</v>
+        <v>489449</v>
       </c>
       <c r="R51" t="n">
-        <v>6818387</v>
+        <v>6818184</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125728075</v>
+        <v>125728168</v>
       </c>
       <c r="B52" t="n">
-        <v>91164</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489292</v>
+        <v>489413</v>
       </c>
       <c r="R52" t="n">
-        <v>6818151</v>
+        <v>6818350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728085</v>
+        <v>125728171</v>
       </c>
       <c r="B53" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489411</v>
+        <v>489374</v>
       </c>
       <c r="R53" t="n">
-        <v>6818380</v>
+        <v>6818387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,10 +5878,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728118</v>
+        <v>125728086</v>
       </c>
       <c r="B55" t="n">
-        <v>78736</v>
+        <v>79009</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,21 +5889,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489422</v>
+        <v>489365</v>
       </c>
       <c r="R55" t="n">
-        <v>6818130</v>
+        <v>6818390</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728086</v>
+        <v>125728088</v>
       </c>
       <c r="B56" t="n">
-        <v>79009</v>
+        <v>96602</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489365</v>
+        <v>489442</v>
       </c>
       <c r="R56" t="n">
-        <v>6818390</v>
+        <v>6818350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,32 +6072,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728088</v>
+        <v>125728109</v>
       </c>
       <c r="B57" t="n">
-        <v>96602</v>
+        <v>97227</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489442</v>
+        <v>489452</v>
       </c>
       <c r="R57" t="n">
-        <v>6818350</v>
+        <v>6818415</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728163</v>
+        <v>125728118</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489456</v>
+        <v>489422</v>
       </c>
       <c r="R58" t="n">
-        <v>6818471</v>
+        <v>6818130</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125728165</v>
+        <v>125728163</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489432</v>
+        <v>489456</v>
       </c>
       <c r="R59" t="n">
-        <v>6818365</v>
+        <v>6818471</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6363,32 +6363,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125728109</v>
+        <v>125728165</v>
       </c>
       <c r="B60" t="n">
-        <v>97227</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489452</v>
+        <v>489432</v>
       </c>
       <c r="R60" t="n">
-        <v>6818415</v>
+        <v>6818365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728078</v>
+        <v>125728115</v>
       </c>
       <c r="B63" t="n">
-        <v>79009</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489352</v>
+        <v>489204</v>
       </c>
       <c r="R63" t="n">
-        <v>6818362</v>
+        <v>6818104</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728153</v>
+        <v>125728078</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489420</v>
+        <v>489352</v>
       </c>
       <c r="R64" t="n">
-        <v>6818126</v>
+        <v>6818362</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728136</v>
+        <v>125728153</v>
       </c>
       <c r="B65" t="n">
         <v>78977</v>
@@ -6883,10 +6883,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489467</v>
+        <v>489420</v>
       </c>
       <c r="R65" t="n">
-        <v>6818200</v>
+        <v>6818126</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,11 +6919,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6950,10 +6945,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728115</v>
+        <v>125728136</v>
       </c>
       <c r="B66" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6961,21 +6956,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6985,10 +6980,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489204</v>
+        <v>489467</v>
       </c>
       <c r="R66" t="n">
-        <v>6818104</v>
+        <v>6818200</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7021,6 +7016,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8803,32 +8803,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728117</v>
+        <v>125728099</v>
       </c>
       <c r="B85" t="n">
-        <v>78736</v>
+        <v>80109</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489409</v>
+        <v>489306</v>
       </c>
       <c r="R85" t="n">
-        <v>6818054</v>
+        <v>6818056</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728099</v>
+        <v>125728125</v>
       </c>
       <c r="B86" t="n">
-        <v>80109</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489306</v>
+        <v>489320</v>
       </c>
       <c r="R86" t="n">
-        <v>6818056</v>
+        <v>6818042</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728125</v>
+        <v>125728117</v>
       </c>
       <c r="B87" t="n">
-        <v>80080</v>
+        <v>78736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489320</v>
+        <v>489409</v>
       </c>
       <c r="R87" t="n">
-        <v>6818042</v>
+        <v>6818054</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728087</v>
+        <v>125728105</v>
       </c>
       <c r="B88" t="n">
-        <v>79009</v>
+        <v>79984</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489343</v>
+        <v>489306</v>
       </c>
       <c r="R88" t="n">
-        <v>6818374</v>
+        <v>6818062</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,45 +9191,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728094</v>
+        <v>125728107</v>
       </c>
       <c r="B89" t="n">
-        <v>91207</v>
+        <v>57656</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489357</v>
+        <v>489359</v>
       </c>
       <c r="R89" t="n">
-        <v>6818380</v>
+        <v>6818332</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9262,6 +9267,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9288,10 +9298,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728152</v>
+        <v>125728087</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9299,21 +9309,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9323,10 +9333,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489415</v>
+        <v>489343</v>
       </c>
       <c r="R90" t="n">
-        <v>6818087</v>
+        <v>6818374</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9385,10 +9395,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728105</v>
+        <v>125728094</v>
       </c>
       <c r="B91" t="n">
-        <v>79984</v>
+        <v>91207</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9396,21 +9406,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9420,10 +9430,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R91" t="n">
-        <v>6818062</v>
+        <v>6818380</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9482,10 +9492,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728107</v>
+        <v>125728152</v>
       </c>
       <c r="B92" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9493,39 +9503,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489359</v>
+        <v>489415</v>
       </c>
       <c r="R92" t="n">
-        <v>6818332</v>
+        <v>6818087</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9558,11 +9563,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11548,38 +11548,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125723678</v>
+        <v>125723419</v>
       </c>
       <c r="B113" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -11650,7 +11650,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125723419</v>
+        <v>125722694</v>
       </c>
       <c r="B114" t="n">
         <v>57656</v>
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>489462</v>
+        <v>489388</v>
       </c>
       <c r="R114" t="n">
-        <v>6818341</v>
+        <v>6818360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11726,6 +11726,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11752,38 +11757,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125722694</v>
+        <v>125723678</v>
       </c>
       <c r="B115" t="n">
-        <v>57656</v>
+        <v>56848</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11792,10 +11797,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>489388</v>
+        <v>489462</v>
       </c>
       <c r="R115" t="n">
-        <v>6818360</v>
+        <v>6818341</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11828,11 +11833,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13811,48 +13811,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125995667</v>
+        <v>125996241</v>
       </c>
       <c r="B135" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>489117</v>
+        <v>489437</v>
       </c>
       <c r="R135" t="n">
-        <v>6818011</v>
+        <v>6818032</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13896,22 +13896,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125996241</v>
+        <v>125996409</v>
       </c>
       <c r="B136" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>489437</v>
+        <v>489377</v>
       </c>
       <c r="R136" t="n">
-        <v>6818032</v>
+        <v>6818145</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13993,57 +13993,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125996409</v>
+        <v>125995667</v>
       </c>
       <c r="B137" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>489377</v>
+        <v>489117</v>
       </c>
       <c r="R137" t="n">
-        <v>6818145</v>
+        <v>6818011</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125996346</v>
+        <v>125994090</v>
       </c>
       <c r="B138" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,34 +14113,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>489439</v>
+        <v>488989</v>
       </c>
       <c r="R138" t="n">
-        <v>6818061</v>
+        <v>6817941</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14199,7 +14199,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125996407</v>
+        <v>125996346</v>
       </c>
       <c r="B139" t="n">
         <v>79009</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>489391</v>
+        <v>489439</v>
       </c>
       <c r="R139" t="n">
-        <v>6818133</v>
+        <v>6818061</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125995990</v>
+        <v>125996407</v>
       </c>
       <c r="B140" t="n">
         <v>79009</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>489201</v>
+        <v>489391</v>
       </c>
       <c r="R140" t="n">
-        <v>6818003</v>
+        <v>6818133</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125995142</v>
+        <v>125995990</v>
       </c>
       <c r="B141" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14404,37 +14404,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>489041</v>
+        <v>489201</v>
       </c>
       <c r="R141" t="n">
-        <v>6817951</v>
+        <v>6818003</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14478,19 +14478,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125994090</v>
+        <v>125995142</v>
       </c>
       <c r="B142" t="n">
         <v>78977</v>
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>488989</v>
+        <v>489041</v>
       </c>
       <c r="R142" t="n">
-        <v>6817941</v>
+        <v>6817951</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125995957</v>
+        <v>125996237</v>
       </c>
       <c r="B148" t="n">
-        <v>57816</v>
+        <v>79009</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15088,21 +15088,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15112,10 +15112,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>489236</v>
+        <v>489427</v>
       </c>
       <c r="R148" t="n">
-        <v>6817991</v>
+        <v>6818004</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15150,11 +15150,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Fyra individer.</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -15167,22 +15162,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125996237</v>
+        <v>125993318</v>
       </c>
       <c r="B149" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15190,34 +15185,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>489427</v>
+        <v>488825</v>
       </c>
       <c r="R149" t="n">
-        <v>6818004</v>
+        <v>6817957</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15276,10 +15271,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125993318</v>
+        <v>125995957</v>
       </c>
       <c r="B150" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15287,34 +15282,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>488825</v>
+        <v>489236</v>
       </c>
       <c r="R150" t="n">
-        <v>6817957</v>
+        <v>6817991</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15349,6 +15344,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Fyra individer.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15361,12 +15361,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -15470,10 +15470,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125995781</v>
+        <v>125996392</v>
       </c>
       <c r="B152" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15481,34 +15481,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>489151</v>
+        <v>489380</v>
       </c>
       <c r="R152" t="n">
-        <v>6818027</v>
+        <v>6818117</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125996392</v>
+        <v>125995781</v>
       </c>
       <c r="B153" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15578,34 +15578,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>489380</v>
+        <v>489151</v>
       </c>
       <c r="R153" t="n">
-        <v>6818117</v>
+        <v>6818027</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16537,7 +16537,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125996410</v>
+        <v>125991520</v>
       </c>
       <c r="B163" t="n">
         <v>78977</v>
@@ -16568,14 +16568,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>489371</v>
+        <v>488720</v>
       </c>
       <c r="R163" t="n">
-        <v>6818137</v>
+        <v>6817985</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -16634,10 +16634,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125992967</v>
+        <v>125996631</v>
       </c>
       <c r="B164" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16645,34 +16645,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>488808</v>
+        <v>489259</v>
       </c>
       <c r="R164" t="n">
-        <v>6817936</v>
+        <v>6818066</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -16731,10 +16731,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125991520</v>
+        <v>125995149</v>
       </c>
       <c r="B165" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16742,21 +16742,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>488720</v>
+        <v>489055</v>
       </c>
       <c r="R165" t="n">
-        <v>6817985</v>
+        <v>6818041</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -16816,22 +16816,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125995149</v>
+        <v>125996410</v>
       </c>
       <c r="B166" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16839,37 +16839,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>489055</v>
+        <v>489371</v>
       </c>
       <c r="R166" t="n">
-        <v>6818041</v>
+        <v>6818137</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -16913,22 +16913,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125996631</v>
+        <v>125992967</v>
       </c>
       <c r="B167" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16936,34 +16936,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>489259</v>
+        <v>488808</v>
       </c>
       <c r="R167" t="n">
-        <v>6818066</v>
+        <v>6817936</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -18962,7 +18962,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125996514</v>
+        <v>125993813</v>
       </c>
       <c r="B188" t="n">
         <v>78977</v>
@@ -18993,14 +18993,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>489277</v>
+        <v>488933</v>
       </c>
       <c r="R188" t="n">
-        <v>6818090</v>
+        <v>6817911</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19047,19 +19047,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125993813</v>
+        <v>125992179</v>
       </c>
       <c r="B189" t="n">
         <v>78977</v>
@@ -19094,13 +19094,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>488933</v>
+        <v>488791</v>
       </c>
       <c r="R189" t="n">
-        <v>6817911</v>
+        <v>6817820</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125992179</v>
+        <v>125996514</v>
       </c>
       <c r="B190" t="n">
         <v>78977</v>
@@ -19187,17 +19187,17 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Vassbolugnet, Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>488791</v>
+        <v>489277</v>
       </c>
       <c r="R190" t="n">
-        <v>6817820</v>
+        <v>6818090</v>
       </c>
       <c r="S190" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 24219-2025 artfynd.xlsx
+++ b/artfynd/A 24219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125728101</v>
+        <v>125728110</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>92724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489357</v>
+        <v>489380</v>
       </c>
       <c r="R2" t="n">
-        <v>6818163</v>
+        <v>6818374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125728110</v>
+        <v>125728080</v>
       </c>
       <c r="B3" t="n">
-        <v>92724</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489380</v>
+        <v>489424</v>
       </c>
       <c r="R3" t="n">
-        <v>6818374</v>
+        <v>6818132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125728080</v>
+        <v>125728083</v>
       </c>
       <c r="B4" t="n">
         <v>79009</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489424</v>
+        <v>489470</v>
       </c>
       <c r="R4" t="n">
-        <v>6818132</v>
+        <v>6818266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125728083</v>
+        <v>125728150</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489470</v>
+        <v>489356</v>
       </c>
       <c r="R5" t="n">
-        <v>6818266</v>
+        <v>6818016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125728150</v>
+        <v>125728137</v>
       </c>
       <c r="B6" t="n">
         <v>78977</v>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489356</v>
+        <v>489352</v>
       </c>
       <c r="R6" t="n">
-        <v>6818016</v>
+        <v>6818366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125728137</v>
+        <v>125728174</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489352</v>
+        <v>489338</v>
       </c>
       <c r="R7" t="n">
-        <v>6818366</v>
+        <v>6818397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125728174</v>
+        <v>125728120</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489338</v>
+        <v>489345</v>
       </c>
       <c r="R8" t="n">
-        <v>6818397</v>
+        <v>6818246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125728120</v>
+        <v>125728121</v>
       </c>
       <c r="B9" t="n">
         <v>80116</v>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489345</v>
+        <v>489306</v>
       </c>
       <c r="R9" t="n">
-        <v>6818246</v>
+        <v>6818055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,45 +1451,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125728121</v>
+        <v>125728101</v>
       </c>
       <c r="B10" t="n">
-        <v>80116</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489306</v>
+        <v>489357</v>
       </c>
       <c r="R10" t="n">
-        <v>6818055</v>
+        <v>6818163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125728149</v>
+        <v>125728113</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489154</v>
+        <v>489363</v>
       </c>
       <c r="R12" t="n">
-        <v>6818070</v>
+        <v>6818242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125728091</v>
+        <v>125728149</v>
       </c>
       <c r="B13" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489452</v>
+        <v>489154</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125728113</v>
+        <v>125728091</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>91207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489363</v>
+        <v>489452</v>
       </c>
       <c r="R14" t="n">
-        <v>6818242</v>
+        <v>6818425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,45 +1946,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125728157</v>
+        <v>125728111</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489452</v>
+        <v>489223</v>
       </c>
       <c r="R15" t="n">
-        <v>6818179</v>
+        <v>6818133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125728146</v>
+        <v>125728069</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489261</v>
+        <v>489204</v>
       </c>
       <c r="R16" t="n">
-        <v>6818155</v>
+        <v>6818104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,7 +2145,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125728169</v>
+        <v>125728157</v>
       </c>
       <c r="B17" t="n">
         <v>78977</v>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489407</v>
+        <v>489452</v>
       </c>
       <c r="R17" t="n">
-        <v>6818356</v>
+        <v>6818179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125728155</v>
+        <v>125728146</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2272,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489417</v>
+        <v>489261</v>
       </c>
       <c r="R18" t="n">
-        <v>6818154</v>
+        <v>6818155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,7 +2339,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125728135</v>
+        <v>125728169</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489219</v>
+        <v>489407</v>
       </c>
       <c r="R19" t="n">
-        <v>6818132</v>
+        <v>6818356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,7 +2436,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125728161</v>
+        <v>125728155</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489439</v>
+        <v>489417</v>
       </c>
       <c r="R20" t="n">
-        <v>6818361</v>
+        <v>6818154</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125728069</v>
+        <v>125728068</v>
       </c>
       <c r="B21" t="n">
         <v>79595</v>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489204</v>
+        <v>489219</v>
       </c>
       <c r="R21" t="n">
-        <v>6818104</v>
+        <v>6818134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125728068</v>
+        <v>125728135</v>
       </c>
       <c r="B22" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         <v>489219</v>
       </c>
       <c r="R22" t="n">
-        <v>6818134</v>
+        <v>6818132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2727,50 +2732,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125728111</v>
+        <v>125728161</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489223</v>
+        <v>489439</v>
       </c>
       <c r="R23" t="n">
-        <v>6818133</v>
+        <v>6818361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,53 +2829,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125728095</v>
+        <v>125728124</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489341</v>
+        <v>489468</v>
       </c>
       <c r="R24" t="n">
-        <v>6818044</v>
+        <v>6818461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2908,11 +2900,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3715,45 +3702,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125728124</v>
+        <v>125728095</v>
       </c>
       <c r="B33" t="n">
-        <v>80116</v>
+        <v>57656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489468</v>
+        <v>489341</v>
       </c>
       <c r="R33" t="n">
-        <v>6818461</v>
+        <v>6818044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3786,6 +3781,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Troligen gamla bohål på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4315,7 +4315,7 @@
         <v>125728089</v>
       </c>
       <c r="B39" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125728159</v>
+        <v>125728071</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489463</v>
+        <v>489452</v>
       </c>
       <c r="R44" t="n">
-        <v>6818200</v>
+        <v>6818185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125728154</v>
+        <v>125728159</v>
       </c>
       <c r="B45" t="n">
         <v>78977</v>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489424</v>
+        <v>489463</v>
       </c>
       <c r="R45" t="n">
-        <v>6818132</v>
+        <v>6818200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125728071</v>
+        <v>125728072</v>
       </c>
       <c r="B46" t="n">
         <v>79595</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489452</v>
+        <v>489446</v>
       </c>
       <c r="R46" t="n">
-        <v>6818185</v>
+        <v>6818191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125728072</v>
+        <v>125728154</v>
       </c>
       <c r="B47" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489446</v>
+        <v>489424</v>
       </c>
       <c r="R47" t="n">
-        <v>6818191</v>
+        <v>6818132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125728171</v>
+        <v>125728073</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489374</v>
+        <v>489392</v>
       </c>
       <c r="R53" t="n">
-        <v>6818387</v>
+        <v>6818361</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125728073</v>
+        <v>125728171</v>
       </c>
       <c r="B54" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489392</v>
+        <v>489374</v>
       </c>
       <c r="R54" t="n">
-        <v>6818361</v>
+        <v>6818387</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125728086</v>
+        <v>125728109</v>
       </c>
       <c r="B55" t="n">
-        <v>79009</v>
+        <v>97230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489365</v>
+        <v>489452</v>
       </c>
       <c r="R55" t="n">
-        <v>6818390</v>
+        <v>6818415</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125728088</v>
+        <v>125728118</v>
       </c>
       <c r="B56" t="n">
-        <v>96602</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489442</v>
+        <v>489422</v>
       </c>
       <c r="R56" t="n">
-        <v>6818350</v>
+        <v>6818130</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6072,32 +6072,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125728109</v>
+        <v>125728086</v>
       </c>
       <c r="B57" t="n">
-        <v>97227</v>
+        <v>79009</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489452</v>
+        <v>489365</v>
       </c>
       <c r="R57" t="n">
-        <v>6818415</v>
+        <v>6818390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125728118</v>
+        <v>125728088</v>
       </c>
       <c r="B58" t="n">
-        <v>78736</v>
+        <v>96605</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489422</v>
+        <v>489442</v>
       </c>
       <c r="R58" t="n">
-        <v>6818130</v>
+        <v>6818350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125728115</v>
+        <v>125728153</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489204</v>
+        <v>489420</v>
       </c>
       <c r="R63" t="n">
-        <v>6818104</v>
+        <v>6818126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125728078</v>
+        <v>125728136</v>
       </c>
       <c r="B64" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489352</v>
+        <v>489467</v>
       </c>
       <c r="R64" t="n">
-        <v>6818362</v>
+        <v>6818200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6822,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6848,10 +6853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125728153</v>
+        <v>125728078</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6859,21 +6864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489420</v>
+        <v>489352</v>
       </c>
       <c r="R65" t="n">
-        <v>6818126</v>
+        <v>6818362</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6945,10 +6950,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125728136</v>
+        <v>125728115</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6956,21 +6961,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6980,10 +6985,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489467</v>
+        <v>489204</v>
       </c>
       <c r="R66" t="n">
-        <v>6818200</v>
+        <v>6818104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,11 +7021,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På grov gammal tall, utan hänsyn</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7831,7 +7831,7 @@
         <v>125728179</v>
       </c>
       <c r="B75" t="n">
-        <v>95201</v>
+        <v>95204</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8609,10 +8609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125728102</v>
+        <v>125728117</v>
       </c>
       <c r="B83" t="n">
-        <v>80081</v>
+        <v>78736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8620,21 +8620,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489338</v>
+        <v>489409</v>
       </c>
       <c r="R83" t="n">
-        <v>6818240</v>
+        <v>6818054</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8706,32 +8706,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125728077</v>
+        <v>125728099</v>
       </c>
       <c r="B84" t="n">
-        <v>75072</v>
+        <v>80109</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489458</v>
+        <v>489306</v>
       </c>
       <c r="R84" t="n">
-        <v>6818455</v>
+        <v>6818056</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125728099</v>
+        <v>125728125</v>
       </c>
       <c r="B85" t="n">
-        <v>80109</v>
+        <v>80080</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489306</v>
+        <v>489320</v>
       </c>
       <c r="R85" t="n">
-        <v>6818056</v>
+        <v>6818042</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125728125</v>
+        <v>125728102</v>
       </c>
       <c r="B86" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489320</v>
+        <v>489338</v>
       </c>
       <c r="R86" t="n">
-        <v>6818042</v>
+        <v>6818240</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125728117</v>
+        <v>125728077</v>
       </c>
       <c r="B87" t="n">
-        <v>78736</v>
+        <v>75072</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489409</v>
+        <v>489458</v>
       </c>
       <c r="R87" t="n">
-        <v>6818054</v>
+        <v>6818455</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125728105</v>
+        <v>125728087</v>
       </c>
       <c r="B88" t="n">
-        <v>79984</v>
+        <v>79009</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489306</v>
+        <v>489343</v>
       </c>
       <c r="R88" t="n">
-        <v>6818062</v>
+        <v>6818374</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9191,50 +9191,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125728107</v>
+        <v>125728094</v>
       </c>
       <c r="B89" t="n">
-        <v>57656</v>
+        <v>91207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489359</v>
+        <v>489357</v>
       </c>
       <c r="R89" t="n">
-        <v>6818332</v>
+        <v>6818380</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9267,11 +9262,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9298,10 +9288,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125728087</v>
+        <v>125728152</v>
       </c>
       <c r="B90" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9309,21 +9299,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9333,10 +9323,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489343</v>
+        <v>489415</v>
       </c>
       <c r="R90" t="n">
-        <v>6818374</v>
+        <v>6818087</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9395,10 +9385,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125728094</v>
+        <v>125728105</v>
       </c>
       <c r="B91" t="n">
-        <v>91207</v>
+        <v>79984</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9406,21 +9396,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9430,10 +9420,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489357</v>
+        <v>489306</v>
       </c>
       <c r="R91" t="n">
-        <v>6818380</v>
+        <v>6818062</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9492,10 +9482,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125728152</v>
+        <v>125728107</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9503,34 +9493,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489415</v>
+        <v>489359</v>
       </c>
       <c r="R92" t="n">
-        <v>6818087</v>
+        <v>6818332</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9563,6 +9558,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125728070</v>
+        <v>125728177</v>
       </c>
       <c r="B93" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>489185</v>
+        <v>489452</v>
       </c>
       <c r="R93" t="n">
-        <v>6818091</v>
+        <v>6818167</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125728177</v>
+        <v>125728126</v>
       </c>
       <c r="B94" t="n">
-        <v>78644</v>
+        <v>91608</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>2064</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>489452</v>
+        <v>489439</v>
       </c>
       <c r="R94" t="n">
-        <v>6818167</v>
+        <v>6818162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125728126</v>
+        <v>125728070</v>
       </c>
       <c r="B95" t="n">
-        <v>91608</v>
+        <v>79595</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9794,21 +9794,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2064</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489439</v>
+        <v>489185</v>
       </c>
       <c r="R95" t="n">
-        <v>6818162</v>
+        <v>6818091</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10659,7 +10659,7 @@
         <v>125728128</v>
       </c>
       <c r="B104" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12252,45 +12252,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724111</v>
+        <v>125725006</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>57478</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>489454</v>
+        <v>489428</v>
       </c>
       <c r="R120" t="n">
-        <v>6818106</v>
+        <v>6818139</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12349,50 +12354,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125725006</v>
+        <v>125724111</v>
       </c>
       <c r="B121" t="n">
-        <v>57478</v>
+        <v>78977</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Vassbolugnet, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>489428</v>
+        <v>489454</v>
       </c>
       <c r="R121" t="n">
-        <v>6818139</v>
+        <v>6818106</v>
       </c>
 